--- a/OBRAS.xlsx
+++ b/OBRAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\SISTEMA LVC WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DE80FC-6998-4FE5-B432-26BE96088888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F308364C-A012-4ADD-9B8E-A7A0D308436E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD94D340-EAD9-4641-9722-F4A49FD1A579}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD94D340-EAD9-4641-9722-F4A49FD1A579}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE OBRAS - GOVERNO ELMANO" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="425">
   <si>
     <t xml:space="preserve">LISTA DE OBRAS RODOVIÁRIAS - CEARÁ DE PONTA A PONTA </t>
   </si>
@@ -980,6 +980,433 @@
   </si>
   <si>
     <t>090ECE0050D0</t>
+  </si>
+  <si>
+    <t>OBRAS CONCLUÍDAS 2025</t>
+  </si>
+  <si>
+    <t>CE-603</t>
+  </si>
+  <si>
+    <t>ENTR. BR 020 (CARIDADE) - SÃO DOMINGOS</t>
+  </si>
+  <si>
+    <t>Caridade</t>
+  </si>
+  <si>
+    <t>SERTÃO DE CANINDÉ</t>
+  </si>
+  <si>
+    <t>CONCLUÍDO</t>
+  </si>
+  <si>
+    <t>0031/2024</t>
+  </si>
+  <si>
+    <t>DATERRA CONSTRUCOES 
+E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>Concluído, aguardando sinalização (DETRAN).</t>
+  </si>
+  <si>
+    <t>Apta O.S política</t>
+  </si>
+  <si>
+    <t>CE-493</t>
+  </si>
+  <si>
+    <t>BARRO BRANCO - SÍTIO SANTANA</t>
+  </si>
+  <si>
+    <t>0002/2024</t>
+  </si>
+  <si>
+    <t>CORAL CONSTRUTORA RODOVALHO ALENCAR LTDA</t>
+  </si>
+  <si>
+    <t>Falta Remenejamento de um poste (43022.009503/2024-81  - Of nº 083/2024-SEINFRA/SEXEC-ETE) e Sinalização (43022.000034/2025-15 - 06/01/2025)  - OBRA CONCLUÍDA EM ABR./2025</t>
+  </si>
+  <si>
+    <t>CE-176</t>
+  </si>
+  <si>
+    <t>ENTR. CE-240 (MIRAÍMA) – CARACARÁ</t>
+  </si>
+  <si>
+    <t>Miraíma e Sobral</t>
+  </si>
+  <si>
+    <t>LITORAL OESTE / VALE DO CURU
+SERTÃO DE SOBRAL</t>
+  </si>
+  <si>
+    <t>D.O. DE ITAPIPOCA / 
+D.O. DE SOBRAL</t>
+  </si>
+  <si>
+    <t>0308/2022</t>
+  </si>
+  <si>
+    <t>CONSÓRCIO E&amp;J/SS-ESTRADA MIRAIMA</t>
+  </si>
+  <si>
+    <t>Evento O.S: 06/09/2022</t>
+  </si>
+  <si>
+    <t>CE-449</t>
+  </si>
+  <si>
+    <t>ENTR. CE473 (NENELÂNDIA) – ENTR. CE-166 (CANHOTINHO)</t>
+  </si>
+  <si>
+    <t>Quixeramobim</t>
+  </si>
+  <si>
+    <t>0167/2023</t>
+  </si>
+  <si>
+    <t>Falta conclusão da concretagem do guarda-corpo de uma das pontes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evento O.S: 18/03/2022 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CE-189 E CE-265</t>
+  </si>
+  <si>
+    <t>EXECUÇÃO DA SUBSTITUIÇÃO DE DUAS PASSAGENS MOLHADAS EXISTENTES POR BUEIROS NO RIACHO CANABRAVA NA CE-189 NO TRECHO ARARENDÁ - IPAPORANGA E NA CE-265 NO TRECHO ARARENDÁ – PORANGA</t>
+  </si>
+  <si>
+    <t>Ararendá</t>
+  </si>
+  <si>
+    <t>0034/2024</t>
+  </si>
+  <si>
+    <t>SALINAS EMPREENDIMENTOS 
+E CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>Concluida</t>
+  </si>
+  <si>
+    <t>IMPLANTAÇÃO DA ROTATÓRIA DE ACESSO AO GATE 2 DO PORTO DO PECÉM NA CE-155</t>
+  </si>
+  <si>
+    <t>0035/2024</t>
+  </si>
+  <si>
+    <t>CCS CONSTRUÇÕES LTDA</t>
+  </si>
+  <si>
+    <t>Obra concluida 
+Aguardando sinalização (NUP 43022.004716/2025-05)</t>
+  </si>
+  <si>
+    <t>CE-060/CE-487</t>
+  </si>
+  <si>
+    <t>ILUMINAÇÃO PÚBLICA DAS CE-060 e CE- 487 NOS TRECHOS IV E V DO CONTORNO DE JUAZEIRO DO NORTE</t>
+  </si>
+  <si>
+    <t>Juazeiro do Norte</t>
+  </si>
+  <si>
+    <t>0053/2024</t>
+  </si>
+  <si>
+    <t>VIEIRA ALVES CONSTRUÇÃO LTDA</t>
+  </si>
+  <si>
+    <t>Solicitação de ligação junto a prefeitura</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">CAPACITAÇÃO E TREINAMENTO DE MULHERES NA OPERAÇÃO DE MÁQUINAS PESADAS, NO ÂMBITO DO PROGRAMA INFRARODOVIÁRIA CEARÁ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>- BID</t>
+    </r>
+  </si>
+  <si>
+    <t>Quixeré</t>
+  </si>
+  <si>
+    <t>0064/2024</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>FORNECEDORA ENGELOG</t>
+    </r>
+  </si>
+  <si>
+    <t>CE-487</t>
+  </si>
+  <si>
+    <t>PAVIMENTAÇÃO DO TRECHO V DA AVENIDA DO CONTORNO DE JUAZEIRO DO NORTE</t>
+  </si>
+  <si>
+    <t>0142/2021</t>
+  </si>
+  <si>
+    <t>Trecho concluído
+Aguardando sinalização do final do trecho (43022.009275/2024-49 - 04/09/2024)
+Iluminação sendo realizada pelo contrato nº 0053/2024 - SOP - Aguardando ligação da Enel</t>
+  </si>
+  <si>
+    <t>CE-371</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> ENTR. BR-230(A) (CARMELÓPOLIS) - ENTR. CE-187/BR-230(B) (CAMPOS SALES) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>- BID</t>
+    </r>
+  </si>
+  <si>
+    <t>Campos Sales</t>
+  </si>
+  <si>
+    <t>0028/2024</t>
+  </si>
+  <si>
+    <t>A.L. TEIXEIRA PINHEIRO LTDA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> ENTR. CE-176(A) p/ ASSARÉ (ANTONINA DO NORTE) - ENTR. BR-230(A) (CARMELÓPOLIS) -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> BID</t>
+    </r>
+  </si>
+  <si>
+    <t>Antonina do Norte e Campos Sales</t>
+  </si>
+  <si>
+    <t>0027/2024</t>
+  </si>
+  <si>
+    <t>CBC - CONSTRUTORA BATISTA 
+CAVALCANTE LTDA</t>
+  </si>
+  <si>
+    <t>CE-588</t>
+  </si>
+  <si>
+    <t>SANTANA DO CARIRI – PONTAL DE SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>Santana do Cariri</t>
+  </si>
+  <si>
+    <t>0335/2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A.L. TEIXEIRA PINHEIRO LTDA</t>
+  </si>
+  <si>
+    <t>Execução do calçamento e CBUQ</t>
+  </si>
+  <si>
+    <t>CE-192</t>
+  </si>
+  <si>
+    <t>LAGOA DAS PEDRAS - SANTANA</t>
+  </si>
+  <si>
+    <t>0119/2023</t>
+  </si>
+  <si>
+    <t>TSD + CALÇAMENTO</t>
+  </si>
+  <si>
+    <t>Drenagem superficial e mudança do calçamento para solo brita nos alargamentos</t>
+  </si>
+  <si>
+    <t>Evento O.S: 01/07/2023</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ENTR. CE-168/284 (B)(CRUZETA) - ENTR. CE-176 (ANTONINA DO NORTE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>- BID</t>
+    </r>
+  </si>
+  <si>
+    <t>Saboeiro e Antonina do Norte</t>
+  </si>
+  <si>
+    <t>D.O. DE IGUATU / D.O. DE TAUÁ</t>
+  </si>
+  <si>
+    <t>0026/2024</t>
+  </si>
+  <si>
+    <t>CORAL CONSTRUTORA RODOVALHO 
+ALENCAR LTDA</t>
+  </si>
+  <si>
+    <t>URBANIZAÇÃO DOS RIOS MARANGUAPINHO E COCÓ</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>0127/2022</t>
+  </si>
+  <si>
+    <t>FORTEKS ENGENHARIA E SERVIÇOS ESPECIAIS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhorou o ritmo mas continua lento
+</t>
+  </si>
+  <si>
+    <t>RECUPERAÇÃO DA PONTE SOBRE O RIO SÃO GONÇALO</t>
+  </si>
+  <si>
+    <t>807,84 m²</t>
+  </si>
+  <si>
+    <t>SÃO GONÇALO DO AMARANTE</t>
+  </si>
+  <si>
+    <t>0119/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSTRUTORA SAMARIA LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROC. DA LIC. 43022.004282/2025-35
+</t>
+  </si>
+  <si>
+    <t>TOTAL DE OBRAS CONCLUÍDAS EM 2025</t>
+  </si>
+  <si>
+    <t>603ECE0010S0</t>
+  </si>
+  <si>
+    <t>493ECE0070S0</t>
+  </si>
+  <si>
+    <t>176ECE0090S0</t>
+  </si>
+  <si>
+    <t>449ECE0010S0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4.752503°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40.831388°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.548216°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -38.815733°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -7.226079°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39.326630°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5.074284°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -37.990856°</t>
+  </si>
+  <si>
+    <t>487ECE0010E0</t>
+  </si>
+  <si>
+    <t>487ECE0010D0</t>
+  </si>
+  <si>
+    <t>371ECE0610S0</t>
+  </si>
+  <si>
+    <t>371ECE0590S0</t>
+  </si>
+  <si>
+    <t>588ECE0010S0</t>
+  </si>
+  <si>
+    <t>192ECE0240S0</t>
+  </si>
+  <si>
+    <t>371ECE0570S0</t>
+  </si>
+  <si>
+    <t>176ECE0400S0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.776425°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -38.593655°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.602600°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -38.973720°</t>
   </si>
 </sst>
 </file>
@@ -990,11 +1417,18 @@
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="165" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1038,6 +1472,38 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1225,184 +1691,198 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1622,3123 +2102,4579 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AS37"/>
+  <dimension ref="A1:AS55"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="15" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="15"/>
-    <col min="18" max="18" width="39.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="51" style="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.5703125" style="15" customWidth="1"/>
-    <col min="21" max="21" width="18" style="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="17.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" style="15" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="17.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18" style="15" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="17" style="15" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17" style="15" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17" style="15" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="14.42578125" style="15"/>
+    <col min="1" max="1" width="4.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" style="13" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="13" customWidth="1"/>
+    <col min="10" max="10" width="15" style="13" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="13" customWidth="1"/>
+    <col min="12" max="12" width="25.5703125" style="13" customWidth="1"/>
+    <col min="13" max="13" width="10" style="13" customWidth="1"/>
+    <col min="14" max="14" width="15" style="13" customWidth="1"/>
+    <col min="15" max="15" width="8" style="13" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" style="13" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="13" customWidth="1"/>
+    <col min="18" max="18" width="39.5703125" style="13" customWidth="1"/>
+    <col min="19" max="19" width="51" style="13" customWidth="1"/>
+    <col min="20" max="20" width="42.5703125" style="13" customWidth="1"/>
+    <col min="21" max="21" width="18" style="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18" style="13" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="17.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18" style="13" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="17" style="13" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17" style="13" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17" style="13" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="14.42578125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="49"/>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="50"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="52"/>
     </row>
     <row r="3" spans="1:45" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="44" t="s">
+      <c r="U3" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="45"/>
-      <c r="AM3" s="45"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="45"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="45"/>
-      <c r="AR3" s="6"/>
-      <c r="AS3" s="6"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="40"/>
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="40"/>
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="40"/>
+      <c r="AK3" s="40"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40"/>
+      <c r="AO3" s="40"/>
+      <c r="AP3" s="40"/>
+      <c r="AQ3" s="40"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="54"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="54"/>
-      <c r="AH4" s="54"/>
-      <c r="AI4" s="54"/>
-      <c r="AJ4" s="54"/>
-      <c r="AK4" s="54"/>
-      <c r="AL4" s="54"/>
-      <c r="AM4" s="54"/>
-      <c r="AN4" s="54"/>
-      <c r="AO4" s="54"/>
-      <c r="AP4" s="54"/>
-      <c r="AQ4" s="54"/>
-      <c r="AR4" s="6"/>
-      <c r="AS4" s="6"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="42"/>
+      <c r="Z4" s="42"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="42"/>
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="42"/>
+      <c r="AH4" s="42"/>
+      <c r="AI4" s="42"/>
+      <c r="AJ4" s="42"/>
+      <c r="AK4" s="42"/>
+      <c r="AL4" s="42"/>
+      <c r="AM4" s="42"/>
+      <c r="AN4" s="42"/>
+      <c r="AO4" s="42"/>
+      <c r="AP4" s="42"/>
+      <c r="AQ4" s="42"/>
+      <c r="AR4" s="5"/>
+      <c r="AS4" s="5"/>
     </row>
     <row r="5" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <v>19.399999999999999</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="10">
         <v>44202</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="11">
         <v>44977</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="12">
         <v>25241358.190000001</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="6">
         <v>100</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="6">
         <v>701</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="9" t="s">
+      <c r="R5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="9"/>
-      <c r="T5" s="38" t="s">
+      <c r="S5" s="7"/>
+      <c r="T5" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="U5" s="42" t="s">
+      <c r="U5" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="V5" s="42" t="s">
+      <c r="V5" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="W5" s="42"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="42"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="42"/>
-      <c r="AB5" s="42"/>
-      <c r="AC5" s="43"/>
-      <c r="AD5" s="43"/>
-      <c r="AE5" s="43"/>
-      <c r="AF5" s="43"/>
-      <c r="AG5" s="43"/>
-      <c r="AH5" s="43"/>
-      <c r="AI5" s="43"/>
-      <c r="AJ5" s="43"/>
-      <c r="AK5" s="43"/>
-      <c r="AL5" s="43"/>
-      <c r="AM5" s="43"/>
-      <c r="AN5" s="43"/>
-      <c r="AO5" s="43"/>
-      <c r="AP5" s="43"/>
-      <c r="AQ5" s="43"/>
-      <c r="AR5" s="16"/>
-      <c r="AS5" s="16"/>
+      <c r="W5" s="37"/>
+      <c r="X5" s="37"/>
+      <c r="Y5" s="37"/>
+      <c r="Z5" s="37"/>
+      <c r="AA5" s="37"/>
+      <c r="AB5" s="37"/>
+      <c r="AC5" s="38"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="38"/>
+      <c r="AG5" s="38"/>
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="38"/>
+      <c r="AK5" s="38"/>
+      <c r="AL5" s="38"/>
+      <c r="AM5" s="38"/>
+      <c r="AN5" s="38"/>
+      <c r="AO5" s="38"/>
+      <c r="AP5" s="38"/>
+      <c r="AQ5" s="38"/>
+      <c r="AR5" s="14"/>
+      <c r="AS5" s="14"/>
     </row>
     <row r="6" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <f t="shared" ref="A6:A15" si="0">A5+1</f>
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>1.44</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="10">
         <v>44476</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="11">
         <v>45001</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="12">
         <v>10309408.66</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="6">
         <v>100</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="6">
         <v>1343</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="17" t="s">
+      <c r="Q6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="9"/>
-      <c r="T6" s="38" t="s">
+      <c r="S6" s="7"/>
+      <c r="T6" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="U6" s="42" t="s">
+      <c r="U6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="V6" s="42"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="42"/>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="42"/>
-      <c r="AB6" s="42"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="43"/>
-      <c r="AG6" s="43"/>
-      <c r="AH6" s="43"/>
-      <c r="AI6" s="43"/>
-      <c r="AJ6" s="43"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="43"/>
-      <c r="AM6" s="43"/>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="43"/>
-      <c r="AP6" s="43"/>
-      <c r="AQ6" s="43"/>
-      <c r="AR6" s="16"/>
-      <c r="AS6" s="16"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="37"/>
+      <c r="Y6" s="37"/>
+      <c r="Z6" s="37"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="37"/>
+      <c r="AC6" s="38"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="38"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="38"/>
+      <c r="AK6" s="38"/>
+      <c r="AL6" s="38"/>
+      <c r="AM6" s="38"/>
+      <c r="AN6" s="38"/>
+      <c r="AO6" s="38"/>
+      <c r="AP6" s="38"/>
+      <c r="AQ6" s="38"/>
+      <c r="AR6" s="14"/>
+      <c r="AS6" s="14"/>
     </row>
     <row r="7" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>9.19</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="10">
         <v>44739</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="11">
         <v>44974</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="12">
         <v>4488234.5</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="6">
         <v>100</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="6">
         <v>1459</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="R7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S7" s="9"/>
-      <c r="T7" s="38" t="s">
+      <c r="S7" s="7"/>
+      <c r="T7" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="U7" s="42" t="s">
+      <c r="U7" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="V7" s="42"/>
-      <c r="W7" s="42"/>
-      <c r="X7" s="42"/>
-      <c r="Y7" s="42"/>
-      <c r="Z7" s="42"/>
-      <c r="AA7" s="42"/>
-      <c r="AB7" s="42"/>
-      <c r="AC7" s="42"/>
-      <c r="AD7" s="42"/>
-      <c r="AE7" s="42"/>
-      <c r="AF7" s="42"/>
-      <c r="AG7" s="42"/>
-      <c r="AH7" s="42"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="42"/>
-      <c r="AK7" s="42"/>
-      <c r="AL7" s="42"/>
-      <c r="AM7" s="42"/>
-      <c r="AN7" s="42"/>
-      <c r="AO7" s="42"/>
-      <c r="AP7" s="42"/>
-      <c r="AQ7" s="42"/>
-      <c r="AR7" s="16"/>
-      <c r="AS7" s="16"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="37"/>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="37"/>
+      <c r="AC7" s="37"/>
+      <c r="AD7" s="37"/>
+      <c r="AE7" s="37"/>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="37"/>
+      <c r="AN7" s="37"/>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="37"/>
+      <c r="AR7" s="14"/>
+      <c r="AS7" s="14"/>
     </row>
     <row r="8" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>31.89</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="11">
         <v>44117</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="11">
         <v>45005</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="12">
         <v>30968183.440000001</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="6">
         <v>100</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="6">
         <v>532</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="P8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="Q8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="R8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S8" s="9"/>
-      <c r="T8" s="38" t="s">
+      <c r="S8" s="7"/>
+      <c r="T8" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="U8" s="42" t="s">
+      <c r="U8" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="V8" s="42" t="s">
+      <c r="V8" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="W8" s="42" t="s">
+      <c r="W8" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="42"/>
-      <c r="Z8" s="42"/>
-      <c r="AA8" s="42"/>
-      <c r="AB8" s="42"/>
-      <c r="AC8" s="42"/>
-      <c r="AD8" s="42"/>
-      <c r="AE8" s="42"/>
-      <c r="AF8" s="42"/>
-      <c r="AG8" s="42"/>
-      <c r="AH8" s="42"/>
-      <c r="AI8" s="42"/>
-      <c r="AJ8" s="42"/>
-      <c r="AK8" s="42"/>
-      <c r="AL8" s="42"/>
-      <c r="AM8" s="42"/>
-      <c r="AN8" s="42"/>
-      <c r="AO8" s="42"/>
-      <c r="AP8" s="42"/>
-      <c r="AQ8" s="42"/>
-      <c r="AR8" s="16"/>
-      <c r="AS8" s="16"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="37"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="37"/>
+      <c r="AD8" s="37"/>
+      <c r="AE8" s="37"/>
+      <c r="AF8" s="37"/>
+      <c r="AG8" s="37"/>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="37"/>
+      <c r="AJ8" s="37"/>
+      <c r="AK8" s="37"/>
+      <c r="AL8" s="37"/>
+      <c r="AM8" s="37"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="37"/>
+      <c r="AP8" s="37"/>
+      <c r="AQ8" s="37"/>
+      <c r="AR8" s="14"/>
+      <c r="AS8" s="14"/>
     </row>
     <row r="9" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <v>12.64</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="11">
         <v>45046</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="12">
         <v>13747621.09</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="6">
         <v>100</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="6">
         <v>564</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="R9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="S9" s="9"/>
-      <c r="T9" s="38" t="s">
+      <c r="S9" s="7"/>
+      <c r="T9" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="U9" s="42" t="s">
+      <c r="U9" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="V9" s="42"/>
-      <c r="W9" s="42"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="42"/>
-      <c r="Z9" s="42"/>
-      <c r="AA9" s="42"/>
-      <c r="AB9" s="42"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="43"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="43"/>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="43"/>
-      <c r="AM9" s="43"/>
-      <c r="AN9" s="43"/>
-      <c r="AO9" s="43"/>
-      <c r="AP9" s="43"/>
-      <c r="AQ9" s="43"/>
-      <c r="AR9" s="16"/>
-      <c r="AS9" s="16"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="38"/>
+      <c r="AD9" s="38"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="38"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="38"/>
+      <c r="AJ9" s="38"/>
+      <c r="AK9" s="38"/>
+      <c r="AL9" s="38"/>
+      <c r="AM9" s="38"/>
+      <c r="AN9" s="38"/>
+      <c r="AO9" s="38"/>
+      <c r="AP9" s="38"/>
+      <c r="AQ9" s="38"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
     </row>
     <row r="10" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>7.9</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="10">
         <v>44662</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="11">
         <v>45172</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="12">
         <v>5172732.1399999997</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="6">
         <v>100</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="6">
         <v>1906</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="Q10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="R10" s="8" t="s">
+      <c r="R10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="S10" s="19"/>
-      <c r="T10" s="38" t="s">
+      <c r="S10" s="17"/>
+      <c r="T10" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="U10" s="42" t="s">
+      <c r="U10" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="V10" s="42"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="42"/>
-      <c r="AA10" s="42"/>
-      <c r="AB10" s="42"/>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="43"/>
-      <c r="AF10" s="43"/>
-      <c r="AG10" s="43"/>
-      <c r="AH10" s="43"/>
-      <c r="AI10" s="43"/>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43"/>
-      <c r="AL10" s="43"/>
-      <c r="AM10" s="43"/>
-      <c r="AN10" s="43"/>
-      <c r="AO10" s="43"/>
-      <c r="AP10" s="43"/>
-      <c r="AQ10" s="43"/>
-      <c r="AR10" s="16"/>
-      <c r="AS10" s="16"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="37"/>
+      <c r="Z10" s="37"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="37"/>
+      <c r="AC10" s="38"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
+      <c r="AK10" s="38"/>
+      <c r="AL10" s="38"/>
+      <c r="AM10" s="38"/>
+      <c r="AN10" s="38"/>
+      <c r="AO10" s="38"/>
+      <c r="AP10" s="38"/>
+      <c r="AQ10" s="38"/>
+      <c r="AR10" s="14"/>
+      <c r="AS10" s="14"/>
     </row>
     <row r="11" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>8.9499999999999993</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="10">
         <v>44756</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="11">
         <v>45103</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="12">
         <v>6909282.04</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="6">
         <v>100</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="6">
         <v>1420</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="P11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="R11" s="8" t="s">
+      <c r="R11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="S11" s="19"/>
-      <c r="T11" s="38" t="s">
+      <c r="S11" s="17"/>
+      <c r="T11" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="U11" s="42" t="s">
+      <c r="U11" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="V11" s="42"/>
-      <c r="W11" s="42"/>
-      <c r="X11" s="42"/>
-      <c r="Y11" s="42"/>
-      <c r="Z11" s="42"/>
-      <c r="AA11" s="42"/>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="43"/>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="43"/>
-      <c r="AM11" s="43"/>
-      <c r="AN11" s="43"/>
-      <c r="AO11" s="43"/>
-      <c r="AP11" s="43"/>
-      <c r="AQ11" s="43"/>
-      <c r="AR11" s="16"/>
-      <c r="AS11" s="16"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="37"/>
+      <c r="Z11" s="37"/>
+      <c r="AA11" s="37"/>
+      <c r="AB11" s="37"/>
+      <c r="AC11" s="38"/>
+      <c r="AD11" s="38"/>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="38"/>
+      <c r="AG11" s="38"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="38"/>
+      <c r="AJ11" s="38"/>
+      <c r="AK11" s="38"/>
+      <c r="AL11" s="38"/>
+      <c r="AM11" s="38"/>
+      <c r="AN11" s="38"/>
+      <c r="AO11" s="38"/>
+      <c r="AP11" s="38"/>
+      <c r="AQ11" s="38"/>
+      <c r="AR11" s="14"/>
+      <c r="AS11" s="14"/>
     </row>
     <row r="12" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>23.42</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="10">
         <v>44803</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="11">
         <v>45169</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="12">
         <v>14968145.01</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="6">
         <v>100</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="6">
         <v>1409</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="P12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="R12" s="8" t="s">
+      <c r="R12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="S12" s="19"/>
-      <c r="T12" s="38" t="s">
+      <c r="S12" s="17"/>
+      <c r="T12" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="U12" s="42" t="s">
+      <c r="U12" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="V12" s="42"/>
-      <c r="W12" s="42"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="42"/>
-      <c r="AB12" s="42"/>
-      <c r="AC12" s="43"/>
-      <c r="AD12" s="43"/>
-      <c r="AE12" s="43"/>
-      <c r="AF12" s="43"/>
-      <c r="AG12" s="43"/>
-      <c r="AH12" s="43"/>
-      <c r="AI12" s="43"/>
-      <c r="AJ12" s="43"/>
-      <c r="AK12" s="43"/>
-      <c r="AL12" s="43"/>
-      <c r="AM12" s="43"/>
-      <c r="AN12" s="43"/>
-      <c r="AO12" s="43"/>
-      <c r="AP12" s="43"/>
-      <c r="AQ12" s="43"/>
-      <c r="AR12" s="16"/>
-      <c r="AS12" s="16"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="37"/>
+      <c r="Z12" s="37"/>
+      <c r="AA12" s="37"/>
+      <c r="AB12" s="37"/>
+      <c r="AC12" s="38"/>
+      <c r="AD12" s="38"/>
+      <c r="AE12" s="38"/>
+      <c r="AF12" s="38"/>
+      <c r="AG12" s="38"/>
+      <c r="AH12" s="38"/>
+      <c r="AI12" s="38"/>
+      <c r="AJ12" s="38"/>
+      <c r="AK12" s="38"/>
+      <c r="AL12" s="38"/>
+      <c r="AM12" s="38"/>
+      <c r="AN12" s="38"/>
+      <c r="AO12" s="38"/>
+      <c r="AP12" s="38"/>
+      <c r="AQ12" s="38"/>
+      <c r="AR12" s="14"/>
+      <c r="AS12" s="14"/>
     </row>
     <row r="13" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <v>29.13</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="10">
         <v>44438</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="11">
         <v>45038</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="12">
         <v>28491100.920000002</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="6">
         <v>100</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="N13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="6">
         <v>853</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="P13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q13" s="8" t="s">
+      <c r="Q13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="R13" s="8" t="s">
+      <c r="R13" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="S13" s="19"/>
-      <c r="T13" s="38" t="s">
+      <c r="S13" s="17"/>
+      <c r="T13" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="U13" s="42" t="s">
+      <c r="U13" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="V13" s="42" t="s">
+      <c r="V13" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="W13" s="42"/>
-      <c r="X13" s="42"/>
-      <c r="Y13" s="42"/>
-      <c r="Z13" s="42"/>
-      <c r="AA13" s="42"/>
-      <c r="AB13" s="42"/>
-      <c r="AC13" s="43"/>
-      <c r="AD13" s="43"/>
-      <c r="AE13" s="43"/>
-      <c r="AF13" s="43"/>
-      <c r="AG13" s="43"/>
-      <c r="AH13" s="43"/>
-      <c r="AI13" s="43"/>
-      <c r="AJ13" s="43"/>
-      <c r="AK13" s="43"/>
-      <c r="AL13" s="43"/>
-      <c r="AM13" s="43"/>
-      <c r="AN13" s="43"/>
-      <c r="AO13" s="43"/>
-      <c r="AP13" s="43"/>
-      <c r="AQ13" s="43"/>
-      <c r="AR13" s="16"/>
-      <c r="AS13" s="16"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="37"/>
+      <c r="Y13" s="37"/>
+      <c r="Z13" s="37"/>
+      <c r="AA13" s="37"/>
+      <c r="AB13" s="37"/>
+      <c r="AC13" s="38"/>
+      <c r="AD13" s="38"/>
+      <c r="AE13" s="38"/>
+      <c r="AF13" s="38"/>
+      <c r="AG13" s="38"/>
+      <c r="AH13" s="38"/>
+      <c r="AI13" s="38"/>
+      <c r="AJ13" s="38"/>
+      <c r="AK13" s="38"/>
+      <c r="AL13" s="38"/>
+      <c r="AM13" s="38"/>
+      <c r="AN13" s="38"/>
+      <c r="AO13" s="38"/>
+      <c r="AP13" s="38"/>
+      <c r="AQ13" s="38"/>
+      <c r="AR13" s="14"/>
+      <c r="AS13" s="14"/>
     </row>
     <row r="14" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <v>20.100000000000001</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>43696</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="11">
         <v>45127</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="12">
         <v>79590696</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="6">
         <v>100</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="6">
         <v>316</v>
       </c>
-      <c r="P14" s="8" t="s">
+      <c r="P14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q14" s="8" t="s">
+      <c r="Q14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="R14" s="8" t="s">
+      <c r="R14" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="S14" s="19"/>
-      <c r="T14" s="38" t="s">
+      <c r="S14" s="17"/>
+      <c r="T14" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="U14" s="42" t="s">
+      <c r="U14" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="V14" s="42" t="s">
+      <c r="V14" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="W14" s="42" t="s">
+      <c r="W14" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="X14" s="42" t="s">
+      <c r="X14" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="Y14" s="42" t="s">
+      <c r="Y14" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="Z14" s="42" t="s">
+      <c r="Z14" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="AA14" s="42" t="s">
+      <c r="AA14" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="AB14" s="42" t="s">
+      <c r="AB14" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="AC14" s="43"/>
-      <c r="AD14" s="43"/>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="43"/>
-      <c r="AG14" s="43"/>
-      <c r="AH14" s="43"/>
-      <c r="AI14" s="43"/>
-      <c r="AJ14" s="43"/>
-      <c r="AK14" s="43"/>
-      <c r="AL14" s="43"/>
-      <c r="AM14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
-      <c r="AQ14" s="43"/>
-      <c r="AR14" s="16"/>
-      <c r="AS14" s="16"/>
+      <c r="AC14" s="38"/>
+      <c r="AD14" s="38"/>
+      <c r="AE14" s="38"/>
+      <c r="AF14" s="38"/>
+      <c r="AG14" s="38"/>
+      <c r="AH14" s="38"/>
+      <c r="AI14" s="38"/>
+      <c r="AJ14" s="38"/>
+      <c r="AK14" s="38"/>
+      <c r="AL14" s="38"/>
+      <c r="AM14" s="38"/>
+      <c r="AN14" s="38"/>
+      <c r="AO14" s="38"/>
+      <c r="AP14" s="38"/>
+      <c r="AQ14" s="38"/>
+      <c r="AR14" s="14"/>
+      <c r="AS14" s="14"/>
     </row>
     <row r="15" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <v>15</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="10">
         <v>43896</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="11">
         <v>45036</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="12">
         <v>15356889.92</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="6">
         <v>100</v>
       </c>
-      <c r="N15" s="8" t="s">
+      <c r="N15" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="6">
         <v>639</v>
       </c>
-      <c r="P15" s="8" t="s">
+      <c r="P15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q15" s="8" t="s">
+      <c r="Q15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="R15" s="8" t="s">
+      <c r="R15" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="S15" s="19"/>
-      <c r="T15" s="38" t="s">
+      <c r="S15" s="17"/>
+      <c r="T15" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="U15" s="42" t="s">
+      <c r="U15" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="V15" s="42" t="s">
+      <c r="V15" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="W15" s="42"/>
-      <c r="X15" s="42"/>
-      <c r="Y15" s="42"/>
-      <c r="Z15" s="42"/>
-      <c r="AA15" s="42"/>
-      <c r="AB15" s="42"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="43"/>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="43"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="43"/>
-      <c r="AM15" s="43"/>
-      <c r="AN15" s="43"/>
-      <c r="AO15" s="43"/>
-      <c r="AP15" s="43"/>
-      <c r="AQ15" s="43"/>
-      <c r="AR15" s="16"/>
-      <c r="AS15" s="16"/>
+      <c r="W15" s="37"/>
+      <c r="X15" s="37"/>
+      <c r="Y15" s="37"/>
+      <c r="Z15" s="37"/>
+      <c r="AA15" s="37"/>
+      <c r="AB15" s="37"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="38"/>
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="38"/>
+      <c r="AK15" s="38"/>
+      <c r="AL15" s="38"/>
+      <c r="AM15" s="38"/>
+      <c r="AN15" s="38"/>
+      <c r="AO15" s="38"/>
+      <c r="AP15" s="38"/>
+      <c r="AQ15" s="38"/>
+      <c r="AR15" s="14"/>
+      <c r="AS15" s="14"/>
     </row>
     <row r="16" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="23">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="20">
         <f>SUM(E5:E15)</f>
         <v>179.06</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21">
         <f>SUM(L5:L15)</f>
         <v>235243651.91</v>
       </c>
-      <c r="M16" s="57" t="s">
+      <c r="M16" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="58"/>
-      <c r="W16" s="58"/>
-      <c r="X16" s="58"/>
-      <c r="Y16" s="58"/>
-      <c r="Z16" s="58"/>
-      <c r="AA16" s="58"/>
-      <c r="AB16" s="58"/>
-      <c r="AC16" s="58"/>
-      <c r="AD16" s="58"/>
-      <c r="AE16" s="58"/>
-      <c r="AF16" s="58"/>
-      <c r="AG16" s="58"/>
-      <c r="AH16" s="58"/>
-      <c r="AI16" s="58"/>
-      <c r="AJ16" s="58"/>
-      <c r="AK16" s="58"/>
-      <c r="AL16" s="58"/>
-      <c r="AM16" s="58"/>
-      <c r="AN16" s="58"/>
-      <c r="AO16" s="58"/>
-      <c r="AP16" s="58"/>
-      <c r="AQ16" s="58"/>
-      <c r="AR16" s="16"/>
-      <c r="AS16" s="16"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="44"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="44"/>
+      <c r="Z16" s="44"/>
+      <c r="AA16" s="44"/>
+      <c r="AB16" s="44"/>
+      <c r="AC16" s="44"/>
+      <c r="AD16" s="44"/>
+      <c r="AE16" s="44"/>
+      <c r="AF16" s="44"/>
+      <c r="AG16" s="44"/>
+      <c r="AH16" s="44"/>
+      <c r="AI16" s="44"/>
+      <c r="AJ16" s="44"/>
+      <c r="AK16" s="44"/>
+      <c r="AL16" s="44"/>
+      <c r="AM16" s="44"/>
+      <c r="AN16" s="44"/>
+      <c r="AO16" s="44"/>
+      <c r="AP16" s="44"/>
+      <c r="AQ16" s="44"/>
+      <c r="AR16" s="14"/>
+      <c r="AS16" s="14"/>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="56"/>
-      <c r="K17" s="56"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="56"/>
-      <c r="P17" s="56"/>
-      <c r="Q17" s="56"/>
-      <c r="R17" s="56"/>
-      <c r="S17" s="56"/>
-      <c r="T17" s="56"/>
-      <c r="U17" s="56"/>
-      <c r="V17" s="56"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="56"/>
-      <c r="Y17" s="56"/>
-      <c r="Z17" s="56"/>
-      <c r="AA17" s="56"/>
-      <c r="AB17" s="56"/>
-      <c r="AC17" s="56"/>
-      <c r="AD17" s="56"/>
-      <c r="AE17" s="56"/>
-      <c r="AF17" s="56"/>
-      <c r="AG17" s="56"/>
-      <c r="AH17" s="56"/>
-      <c r="AI17" s="56"/>
-      <c r="AJ17" s="56"/>
-      <c r="AK17" s="56"/>
-      <c r="AL17" s="56"/>
-      <c r="AM17" s="56"/>
-      <c r="AN17" s="56"/>
-      <c r="AO17" s="56"/>
-      <c r="AP17" s="56"/>
-      <c r="AQ17" s="56"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="46"/>
+      <c r="AA17" s="46"/>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="46"/>
+      <c r="AF17" s="46"/>
+      <c r="AG17" s="46"/>
+      <c r="AH17" s="46"/>
+      <c r="AI17" s="46"/>
+      <c r="AJ17" s="46"/>
+      <c r="AK17" s="46"/>
+      <c r="AL17" s="46"/>
+      <c r="AM17" s="46"/>
+      <c r="AN17" s="46"/>
+      <c r="AO17" s="46"/>
+      <c r="AP17" s="46"/>
+      <c r="AQ17" s="46"/>
     </row>
     <row r="18" spans="1:43" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <v>12</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <v>24.29</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="11">
         <v>43686</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="11">
         <v>45367</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="22">
         <v>66589935.5</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="6">
         <v>100</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="N18" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="6">
         <v>559</v>
       </c>
-      <c r="P18" s="8" t="s">
+      <c r="P18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" s="8" t="s">
+      <c r="Q18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="R18" s="8" t="s">
+      <c r="R18" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="S18" s="9" t="s">
+      <c r="S18" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="T18" s="38" t="s">
+      <c r="T18" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="U18" s="42" t="s">
+      <c r="U18" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="V18" s="42" t="s">
+      <c r="V18" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="W18" s="42" t="s">
+      <c r="W18" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="X18" s="42" t="s">
+      <c r="X18" s="37" t="s">
         <v>265</v>
       </c>
-      <c r="Y18" s="42" t="s">
+      <c r="Y18" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="Z18" s="42" t="s">
+      <c r="Z18" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="AA18" s="42"/>
-      <c r="AB18" s="42"/>
-      <c r="AC18" s="42"/>
-      <c r="AD18" s="42"/>
-      <c r="AE18" s="42"/>
-      <c r="AF18" s="42"/>
-      <c r="AG18" s="42"/>
-      <c r="AH18" s="42"/>
-      <c r="AI18" s="42"/>
-      <c r="AJ18" s="42"/>
-      <c r="AK18" s="42"/>
-      <c r="AL18" s="42"/>
-      <c r="AM18" s="42"/>
-      <c r="AN18" s="42"/>
-      <c r="AO18" s="42"/>
-      <c r="AP18" s="42"/>
-      <c r="AQ18" s="42"/>
+      <c r="AA18" s="37"/>
+      <c r="AB18" s="37"/>
+      <c r="AC18" s="37"/>
+      <c r="AD18" s="37"/>
+      <c r="AE18" s="37"/>
+      <c r="AF18" s="37"/>
+      <c r="AG18" s="37"/>
+      <c r="AH18" s="37"/>
+      <c r="AI18" s="37"/>
+      <c r="AJ18" s="37"/>
+      <c r="AK18" s="37"/>
+      <c r="AL18" s="37"/>
+      <c r="AM18" s="37"/>
+      <c r="AN18" s="37"/>
+      <c r="AO18" s="37"/>
+      <c r="AP18" s="37"/>
+      <c r="AQ18" s="37"/>
     </row>
     <row r="19" spans="1:43" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <f t="shared" ref="A19:A36" si="1">A18+1</f>
         <v>13</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="9">
         <v>15.7</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="11">
         <v>44033</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="11">
         <v>45340</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="12">
         <v>13271002.029999999</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="6">
         <v>100</v>
       </c>
-      <c r="N19" s="8" t="s">
+      <c r="N19" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="6">
         <v>747</v>
       </c>
-      <c r="P19" s="8" t="s">
+      <c r="P19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q19" s="8" t="s">
+      <c r="Q19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="R19" s="8" t="s">
+      <c r="R19" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="S19" s="9" t="s">
+      <c r="S19" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="T19" s="38" t="s">
+      <c r="T19" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="U19" s="42" t="s">
+      <c r="U19" s="37" t="s">
         <v>268</v>
       </c>
-      <c r="V19" s="42" t="s">
+      <c r="V19" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="42"/>
-      <c r="AA19" s="42"/>
-      <c r="AB19" s="42"/>
-      <c r="AC19" s="42"/>
-      <c r="AD19" s="42"/>
-      <c r="AE19" s="42"/>
-      <c r="AF19" s="42"/>
-      <c r="AG19" s="42"/>
-      <c r="AH19" s="42"/>
-      <c r="AI19" s="42"/>
-      <c r="AJ19" s="42"/>
-      <c r="AK19" s="42"/>
-      <c r="AL19" s="42"/>
-      <c r="AM19" s="42"/>
-      <c r="AN19" s="42"/>
-      <c r="AO19" s="42"/>
-      <c r="AP19" s="42"/>
-      <c r="AQ19" s="42"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="37"/>
+      <c r="Y19" s="37"/>
+      <c r="Z19" s="37"/>
+      <c r="AA19" s="37"/>
+      <c r="AB19" s="37"/>
+      <c r="AC19" s="37"/>
+      <c r="AD19" s="37"/>
+      <c r="AE19" s="37"/>
+      <c r="AF19" s="37"/>
+      <c r="AG19" s="37"/>
+      <c r="AH19" s="37"/>
+      <c r="AI19" s="37"/>
+      <c r="AJ19" s="37"/>
+      <c r="AK19" s="37"/>
+      <c r="AL19" s="37"/>
+      <c r="AM19" s="37"/>
+      <c r="AN19" s="37"/>
+      <c r="AO19" s="37"/>
+      <c r="AP19" s="37"/>
+      <c r="AQ19" s="37"/>
     </row>
     <row r="20" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="6">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="9">
         <v>8.66</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="10">
         <v>44825</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="11">
         <v>45345</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="12">
         <v>5893058.8600000003</v>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="6">
         <v>100</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="N20" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="6">
         <v>1375</v>
       </c>
-      <c r="P20" s="8" t="s">
+      <c r="P20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="Q20" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="R20" s="8" t="s">
+      <c r="R20" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="S20" s="9" t="s">
+      <c r="S20" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="T20" s="38" t="s">
+      <c r="T20" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="U20" s="42" t="s">
+      <c r="U20" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="42"/>
-      <c r="Z20" s="42"/>
-      <c r="AA20" s="42"/>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="42"/>
-      <c r="AF20" s="42"/>
-      <c r="AG20" s="42"/>
-      <c r="AH20" s="42"/>
-      <c r="AI20" s="42"/>
-      <c r="AJ20" s="42"/>
-      <c r="AK20" s="42"/>
-      <c r="AL20" s="42"/>
-      <c r="AM20" s="42"/>
-      <c r="AN20" s="42"/>
-      <c r="AO20" s="42"/>
-      <c r="AP20" s="42"/>
-      <c r="AQ20" s="42"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="37"/>
+      <c r="X20" s="37"/>
+      <c r="Y20" s="37"/>
+      <c r="Z20" s="37"/>
+      <c r="AA20" s="37"/>
+      <c r="AB20" s="37"/>
+      <c r="AC20" s="37"/>
+      <c r="AD20" s="37"/>
+      <c r="AE20" s="37"/>
+      <c r="AF20" s="37"/>
+      <c r="AG20" s="37"/>
+      <c r="AH20" s="37"/>
+      <c r="AI20" s="37"/>
+      <c r="AJ20" s="37"/>
+      <c r="AK20" s="37"/>
+      <c r="AL20" s="37"/>
+      <c r="AM20" s="37"/>
+      <c r="AN20" s="37"/>
+      <c r="AO20" s="37"/>
+      <c r="AP20" s="37"/>
+      <c r="AQ20" s="37"/>
     </row>
     <row r="21" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="25">
         <v>47.9</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="26">
         <v>44930</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="27">
         <v>45330</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="28">
         <v>27102187.760000002</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="6">
         <v>100</v>
       </c>
-      <c r="N21" s="27" t="s">
+      <c r="N21" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="O21" s="27">
+      <c r="O21" s="23">
         <v>1771</v>
       </c>
-      <c r="P21" s="27" t="s">
+      <c r="P21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q21" s="27" t="s">
+      <c r="Q21" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="R21" s="27" t="s">
+      <c r="R21" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="S21" s="33"/>
-      <c r="T21" s="39" t="s">
+      <c r="S21" s="29"/>
+      <c r="T21" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="U21" s="42" t="s">
+      <c r="U21" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="V21" s="42" t="s">
+      <c r="V21" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="W21" s="42" t="s">
+      <c r="W21" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="X21" s="42" t="s">
+      <c r="X21" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="Y21" s="42" t="s">
+      <c r="Y21" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="Z21" s="42" t="s">
+      <c r="Z21" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="AA21" s="42" t="s">
+      <c r="AA21" s="37" t="s">
         <v>277</v>
       </c>
-      <c r="AB21" s="42" t="s">
+      <c r="AB21" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="AC21" s="42" t="s">
+      <c r="AC21" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="AD21" s="42" t="s">
+      <c r="AD21" s="37" t="s">
         <v>280</v>
       </c>
-      <c r="AE21" s="42" t="s">
+      <c r="AE21" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="AF21" s="42" t="s">
+      <c r="AF21" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="AG21" s="42" t="s">
+      <c r="AG21" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="AH21" s="42" t="s">
+      <c r="AH21" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="AI21" s="42" t="s">
+      <c r="AI21" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="AJ21" s="42" t="s">
+      <c r="AJ21" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="AK21" s="42" t="s">
+      <c r="AK21" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="AL21" s="42" t="s">
+      <c r="AL21" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="AM21" s="42" t="s">
+      <c r="AM21" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="AN21" s="42" t="s">
+      <c r="AN21" s="37" t="s">
         <v>290</v>
       </c>
-      <c r="AO21" s="42"/>
-      <c r="AP21" s="42"/>
-      <c r="AQ21" s="42"/>
+      <c r="AO21" s="37"/>
+      <c r="AP21" s="37"/>
+      <c r="AQ21" s="37"/>
     </row>
     <row r="22" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="6">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="25">
         <v>0.97</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="26">
         <v>45146</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="26">
         <v>45508</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="K22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="28">
         <v>2815978.8</v>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="6">
         <v>100</v>
       </c>
-      <c r="N22" s="27" t="s">
+      <c r="N22" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="O22" s="27">
+      <c r="O22" s="23">
         <v>2188</v>
       </c>
-      <c r="P22" s="27" t="s">
+      <c r="P22" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="28" t="s">
+      <c r="Q22" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="R22" s="28" t="s">
+      <c r="R22" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="S22" s="9" t="s">
+      <c r="S22" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="T22" s="40" t="s">
+      <c r="T22" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="U22" s="42" t="s">
+      <c r="U22" s="37" t="s">
         <v>291</v>
       </c>
-      <c r="V22" s="42"/>
-      <c r="W22" s="42"/>
-      <c r="X22" s="42"/>
-      <c r="Y22" s="42"/>
-      <c r="Z22" s="42"/>
-      <c r="AA22" s="42"/>
-      <c r="AB22" s="42"/>
-      <c r="AC22" s="42"/>
-      <c r="AD22" s="42"/>
-      <c r="AE22" s="42"/>
-      <c r="AF22" s="42"/>
-      <c r="AG22" s="42"/>
-      <c r="AH22" s="42"/>
-      <c r="AI22" s="42"/>
-      <c r="AJ22" s="42"/>
-      <c r="AK22" s="42"/>
-      <c r="AL22" s="42"/>
-      <c r="AM22" s="42"/>
-      <c r="AN22" s="42"/>
-      <c r="AO22" s="42"/>
-      <c r="AP22" s="42"/>
-      <c r="AQ22" s="42"/>
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="37"/>
+      <c r="Y22" s="37"/>
+      <c r="Z22" s="37"/>
+      <c r="AA22" s="37"/>
+      <c r="AB22" s="37"/>
+      <c r="AC22" s="37"/>
+      <c r="AD22" s="37"/>
+      <c r="AE22" s="37"/>
+      <c r="AF22" s="37"/>
+      <c r="AG22" s="37"/>
+      <c r="AH22" s="37"/>
+      <c r="AI22" s="37"/>
+      <c r="AJ22" s="37"/>
+      <c r="AK22" s="37"/>
+      <c r="AL22" s="37"/>
+      <c r="AM22" s="37"/>
+      <c r="AN22" s="37"/>
+      <c r="AO22" s="37"/>
+      <c r="AP22" s="37"/>
+      <c r="AQ22" s="37"/>
     </row>
     <row r="23" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="6">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="25">
         <v>8.4</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="26">
         <v>44623</v>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="27">
         <v>45513</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="K23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="32">
+      <c r="L23" s="28">
         <v>31587295.43</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="6">
         <v>100</v>
       </c>
-      <c r="N23" s="27" t="s">
+      <c r="N23" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="23">
         <v>1860</v>
       </c>
-      <c r="P23" s="27" t="s">
+      <c r="P23" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q23" s="28" t="s">
+      <c r="Q23" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="R23" s="28" t="s">
+      <c r="R23" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="S23" s="28" t="s">
+      <c r="S23" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="T23" s="38" t="s">
+      <c r="T23" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="U23" s="42" t="s">
+      <c r="U23" s="37" t="s">
         <v>292</v>
       </c>
-      <c r="V23" s="42" t="s">
+      <c r="V23" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="W23" s="42" t="s">
+      <c r="W23" s="37" t="s">
         <v>294</v>
       </c>
-      <c r="X23" s="42"/>
-      <c r="Y23" s="42"/>
-      <c r="Z23" s="42"/>
-      <c r="AA23" s="42"/>
-      <c r="AB23" s="42"/>
-      <c r="AC23" s="42"/>
-      <c r="AD23" s="42"/>
-      <c r="AE23" s="42"/>
-      <c r="AF23" s="42"/>
-      <c r="AG23" s="42"/>
-      <c r="AH23" s="42"/>
-      <c r="AI23" s="42"/>
-      <c r="AJ23" s="42"/>
-      <c r="AK23" s="42"/>
-      <c r="AL23" s="42"/>
-      <c r="AM23" s="42"/>
-      <c r="AN23" s="42"/>
-      <c r="AO23" s="42"/>
-      <c r="AP23" s="42"/>
-      <c r="AQ23" s="42"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="37"/>
+      <c r="Z23" s="37"/>
+      <c r="AA23" s="37"/>
+      <c r="AB23" s="37"/>
+      <c r="AC23" s="37"/>
+      <c r="AD23" s="37"/>
+      <c r="AE23" s="37"/>
+      <c r="AF23" s="37"/>
+      <c r="AG23" s="37"/>
+      <c r="AH23" s="37"/>
+      <c r="AI23" s="37"/>
+      <c r="AJ23" s="37"/>
+      <c r="AK23" s="37"/>
+      <c r="AL23" s="37"/>
+      <c r="AM23" s="37"/>
+      <c r="AN23" s="37"/>
+      <c r="AO23" s="37"/>
+      <c r="AP23" s="37"/>
+      <c r="AQ23" s="37"/>
     </row>
     <row r="24" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="25">
         <v>25.1</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="26">
         <v>44383</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="27">
         <v>45471</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="K24" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="28">
         <v>19638413.100000001</v>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="6">
         <v>100</v>
       </c>
-      <c r="N24" s="27" t="s">
+      <c r="N24" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="23">
         <v>702</v>
       </c>
-      <c r="P24" s="27" t="s">
+      <c r="P24" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q24" s="28" t="s">
+      <c r="Q24" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="R24" s="28" t="s">
+      <c r="R24" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="S24" s="28"/>
-      <c r="T24" s="38" t="s">
+      <c r="S24" s="24"/>
+      <c r="T24" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="U24" s="42" t="s">
+      <c r="U24" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="V24" s="42" t="s">
+      <c r="V24" s="37" t="s">
         <v>296</v>
       </c>
-      <c r="W24" s="42"/>
-      <c r="X24" s="42"/>
-      <c r="Y24" s="42"/>
-      <c r="Z24" s="42"/>
-      <c r="AA24" s="42"/>
-      <c r="AB24" s="42"/>
-      <c r="AC24" s="42"/>
-      <c r="AD24" s="42"/>
-      <c r="AE24" s="42"/>
-      <c r="AF24" s="42"/>
-      <c r="AG24" s="42"/>
-      <c r="AH24" s="42"/>
-      <c r="AI24" s="42"/>
-      <c r="AJ24" s="42"/>
-      <c r="AK24" s="42"/>
-      <c r="AL24" s="42"/>
-      <c r="AM24" s="42"/>
-      <c r="AN24" s="42"/>
-      <c r="AO24" s="42"/>
-      <c r="AP24" s="42"/>
-      <c r="AQ24" s="42"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="37"/>
+      <c r="Y24" s="37"/>
+      <c r="Z24" s="37"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="37"/>
+      <c r="AE24" s="37"/>
+      <c r="AF24" s="37"/>
+      <c r="AG24" s="37"/>
+      <c r="AH24" s="37"/>
+      <c r="AI24" s="37"/>
+      <c r="AJ24" s="37"/>
+      <c r="AK24" s="37"/>
+      <c r="AL24" s="37"/>
+      <c r="AM24" s="37"/>
+      <c r="AN24" s="37"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="37"/>
+      <c r="AQ24" s="37"/>
     </row>
     <row r="25" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="25">
         <v>30.34</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="26">
         <v>44593</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="27">
         <v>45524</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="K25" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="28">
         <v>22469055.489999998</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="6">
         <v>100</v>
       </c>
-      <c r="N25" s="27" t="s">
+      <c r="N25" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="O25" s="27">
+      <c r="O25" s="23">
         <v>686</v>
       </c>
-      <c r="P25" s="27" t="s">
+      <c r="P25" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q25" s="28" t="s">
+      <c r="Q25" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="R25" s="28" t="s">
+      <c r="R25" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="S25" s="28" t="s">
+      <c r="S25" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="T25" s="38" t="s">
+      <c r="T25" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="U25" s="42" t="s">
+      <c r="U25" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="V25" s="42"/>
-      <c r="W25" s="42"/>
-      <c r="X25" s="42"/>
-      <c r="Y25" s="42"/>
-      <c r="Z25" s="42"/>
-      <c r="AA25" s="42"/>
-      <c r="AB25" s="42"/>
-      <c r="AC25" s="42"/>
-      <c r="AD25" s="42"/>
-      <c r="AE25" s="42"/>
-      <c r="AF25" s="42"/>
-      <c r="AG25" s="42"/>
-      <c r="AH25" s="42"/>
-      <c r="AI25" s="42"/>
-      <c r="AJ25" s="42"/>
-      <c r="AK25" s="42"/>
-      <c r="AL25" s="42"/>
-      <c r="AM25" s="42"/>
-      <c r="AN25" s="42"/>
-      <c r="AO25" s="42"/>
-      <c r="AP25" s="42"/>
-      <c r="AQ25" s="42"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="37"/>
+      <c r="Y25" s="37"/>
+      <c r="Z25" s="37"/>
+      <c r="AA25" s="37"/>
+      <c r="AB25" s="37"/>
+      <c r="AC25" s="37"/>
+      <c r="AD25" s="37"/>
+      <c r="AE25" s="37"/>
+      <c r="AF25" s="37"/>
+      <c r="AG25" s="37"/>
+      <c r="AH25" s="37"/>
+      <c r="AI25" s="37"/>
+      <c r="AJ25" s="37"/>
+      <c r="AK25" s="37"/>
+      <c r="AL25" s="37"/>
+      <c r="AM25" s="37"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="37"/>
+      <c r="AP25" s="37"/>
+      <c r="AQ25" s="37"/>
     </row>
     <row r="26" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="6">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="26">
         <v>44972</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="26">
         <v>45578</v>
       </c>
-      <c r="K26" s="14" t="s">
+      <c r="K26" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L26" s="32">
+      <c r="L26" s="28">
         <v>3014653.83</v>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="6">
         <v>100</v>
       </c>
-      <c r="N26" s="27" t="s">
+      <c r="N26" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="O26" s="27">
+      <c r="O26" s="23">
         <v>1621</v>
       </c>
-      <c r="P26" s="27" t="s">
+      <c r="P26" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q26" s="34" t="s">
+      <c r="Q26" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="R26" s="28" t="s">
+      <c r="R26" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="S26" s="28" t="s">
+      <c r="S26" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="T26" s="41"/>
-      <c r="U26" s="42" t="s">
+      <c r="T26" s="36"/>
+      <c r="U26" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="V26" s="42" t="s">
+      <c r="V26" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="W26" s="42"/>
-      <c r="X26" s="42"/>
-      <c r="Y26" s="42"/>
-      <c r="Z26" s="42"/>
-      <c r="AA26" s="42"/>
-      <c r="AB26" s="42"/>
-      <c r="AC26" s="42"/>
-      <c r="AD26" s="42"/>
-      <c r="AE26" s="42"/>
-      <c r="AF26" s="42"/>
-      <c r="AG26" s="42"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="42"/>
-      <c r="AL26" s="42"/>
-      <c r="AM26" s="42"/>
-      <c r="AN26" s="42"/>
-      <c r="AO26" s="42"/>
-      <c r="AP26" s="42"/>
-      <c r="AQ26" s="42"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="37"/>
+      <c r="Y26" s="37"/>
+      <c r="Z26" s="37"/>
+      <c r="AA26" s="37"/>
+      <c r="AB26" s="37"/>
+      <c r="AC26" s="37"/>
+      <c r="AD26" s="37"/>
+      <c r="AE26" s="37"/>
+      <c r="AF26" s="37"/>
+      <c r="AG26" s="37"/>
+      <c r="AH26" s="37"/>
+      <c r="AI26" s="37"/>
+      <c r="AJ26" s="37"/>
+      <c r="AK26" s="37"/>
+      <c r="AL26" s="37"/>
+      <c r="AM26" s="37"/>
+      <c r="AN26" s="37"/>
+      <c r="AO26" s="37"/>
+      <c r="AP26" s="37"/>
+      <c r="AQ26" s="37"/>
     </row>
     <row r="27" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="25">
         <v>16.600000000000001</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="10">
         <v>45054</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="27">
         <v>45533</v>
       </c>
-      <c r="K27" s="14" t="s">
+      <c r="K27" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="28">
         <v>14394574.65</v>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="6">
         <v>100</v>
       </c>
-      <c r="N27" s="27" t="s">
+      <c r="N27" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="O27" s="27">
+      <c r="O27" s="23">
         <v>1390</v>
       </c>
-      <c r="P27" s="27" t="s">
+      <c r="P27" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="27" t="s">
+      <c r="Q27" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="R27" s="27" t="s">
+      <c r="R27" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="S27" s="28" t="s">
+      <c r="S27" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="T27" s="38" t="s">
+      <c r="T27" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="U27" s="42" t="s">
+      <c r="U27" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="V27" s="42"/>
-      <c r="W27" s="42"/>
-      <c r="X27" s="42"/>
-      <c r="Y27" s="42"/>
-      <c r="Z27" s="42"/>
-      <c r="AA27" s="42"/>
-      <c r="AB27" s="42"/>
-      <c r="AC27" s="42"/>
-      <c r="AD27" s="42"/>
-      <c r="AE27" s="42"/>
-      <c r="AF27" s="42"/>
-      <c r="AG27" s="42"/>
-      <c r="AH27" s="42"/>
-      <c r="AI27" s="42"/>
-      <c r="AJ27" s="42"/>
-      <c r="AK27" s="42"/>
-      <c r="AL27" s="42"/>
-      <c r="AM27" s="42"/>
-      <c r="AN27" s="42"/>
-      <c r="AO27" s="42"/>
-      <c r="AP27" s="42"/>
-      <c r="AQ27" s="42"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="37"/>
+      <c r="X27" s="37"/>
+      <c r="Y27" s="37"/>
+      <c r="Z27" s="37"/>
+      <c r="AA27" s="37"/>
+      <c r="AB27" s="37"/>
+      <c r="AC27" s="37"/>
+      <c r="AD27" s="37"/>
+      <c r="AE27" s="37"/>
+      <c r="AF27" s="37"/>
+      <c r="AG27" s="37"/>
+      <c r="AH27" s="37"/>
+      <c r="AI27" s="37"/>
+      <c r="AJ27" s="37"/>
+      <c r="AK27" s="37"/>
+      <c r="AL27" s="37"/>
+      <c r="AM27" s="37"/>
+      <c r="AN27" s="37"/>
+      <c r="AO27" s="37"/>
+      <c r="AP27" s="37"/>
+      <c r="AQ27" s="37"/>
     </row>
     <row r="28" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="6">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="25">
         <v>5.86</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="10">
         <v>44882</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="27">
         <v>45482</v>
       </c>
-      <c r="K28" s="14" t="s">
+      <c r="K28" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="28">
         <v>4965906.38</v>
       </c>
-      <c r="M28" s="8">
+      <c r="M28" s="6">
         <v>100</v>
       </c>
-      <c r="N28" s="27" t="s">
+      <c r="N28" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="O28" s="27">
+      <c r="O28" s="23">
         <v>1378</v>
       </c>
-      <c r="P28" s="27" t="s">
+      <c r="P28" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q28" s="28" t="s">
+      <c r="Q28" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="R28" s="35" t="s">
+      <c r="R28" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="S28" s="28" t="s">
+      <c r="S28" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="T28" s="40" t="s">
+      <c r="T28" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="U28" s="42" t="s">
+      <c r="U28" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="V28" s="42" t="s">
+      <c r="V28" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="W28" s="42"/>
-      <c r="X28" s="42"/>
-      <c r="Y28" s="42"/>
-      <c r="Z28" s="42"/>
-      <c r="AA28" s="42"/>
-      <c r="AB28" s="42"/>
-      <c r="AC28" s="42"/>
-      <c r="AD28" s="42"/>
-      <c r="AE28" s="42"/>
-      <c r="AF28" s="42"/>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
-      <c r="AM28" s="42"/>
-      <c r="AN28" s="42"/>
-      <c r="AO28" s="42"/>
-      <c r="AP28" s="42"/>
-      <c r="AQ28" s="42"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="37"/>
+      <c r="AA28" s="37"/>
+      <c r="AB28" s="37"/>
+      <c r="AC28" s="37"/>
+      <c r="AD28" s="37"/>
+      <c r="AE28" s="37"/>
+      <c r="AF28" s="37"/>
+      <c r="AG28" s="37"/>
+      <c r="AH28" s="37"/>
+      <c r="AI28" s="37"/>
+      <c r="AJ28" s="37"/>
+      <c r="AK28" s="37"/>
+      <c r="AL28" s="37"/>
+      <c r="AM28" s="37"/>
+      <c r="AN28" s="37"/>
+      <c r="AO28" s="37"/>
+      <c r="AP28" s="37"/>
+      <c r="AQ28" s="37"/>
     </row>
     <row r="29" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="6">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="25">
         <v>16.82</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="G29" s="28" t="s">
+      <c r="G29" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I29" s="30">
+      <c r="I29" s="26">
         <v>44627</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="26">
         <v>45604</v>
       </c>
-      <c r="K29" s="14" t="s">
+      <c r="K29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="28">
         <v>8303874.0599999996</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="6">
         <v>100</v>
       </c>
-      <c r="N29" s="27" t="s">
+      <c r="N29" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="23">
         <v>1340</v>
       </c>
-      <c r="P29" s="27" t="s">
+      <c r="P29" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q29" s="27" t="s">
+      <c r="Q29" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="R29" s="27" t="s">
+      <c r="R29" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="S29" s="28" t="s">
+      <c r="S29" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="T29" s="38" t="s">
+      <c r="T29" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="U29" s="42" t="s">
+      <c r="U29" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="V29" s="42"/>
-      <c r="W29" s="42"/>
-      <c r="X29" s="42"/>
-      <c r="Y29" s="42"/>
-      <c r="Z29" s="42"/>
-      <c r="AA29" s="42"/>
-      <c r="AB29" s="42"/>
-      <c r="AC29" s="42"/>
-      <c r="AD29" s="42"/>
-      <c r="AE29" s="42"/>
-      <c r="AF29" s="42"/>
-      <c r="AG29" s="42"/>
-      <c r="AH29" s="42"/>
-      <c r="AI29" s="42"/>
-      <c r="AJ29" s="42"/>
-      <c r="AK29" s="42"/>
-      <c r="AL29" s="42"/>
-      <c r="AM29" s="42"/>
-      <c r="AN29" s="42"/>
-      <c r="AO29" s="42"/>
-      <c r="AP29" s="42"/>
-      <c r="AQ29" s="42"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="37"/>
+      <c r="Y29" s="37"/>
+      <c r="Z29" s="37"/>
+      <c r="AA29" s="37"/>
+      <c r="AB29" s="37"/>
+      <c r="AC29" s="37"/>
+      <c r="AD29" s="37"/>
+      <c r="AE29" s="37"/>
+      <c r="AF29" s="37"/>
+      <c r="AG29" s="37"/>
+      <c r="AH29" s="37"/>
+      <c r="AI29" s="37"/>
+      <c r="AJ29" s="37"/>
+      <c r="AK29" s="37"/>
+      <c r="AL29" s="37"/>
+      <c r="AM29" s="37"/>
+      <c r="AN29" s="37"/>
+      <c r="AO29" s="37"/>
+      <c r="AP29" s="37"/>
+      <c r="AQ29" s="37"/>
     </row>
     <row r="30" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="D30" s="33" t="str">
+      <c r="D30" s="29" t="str">
         <f>UPPER("Iluminação do Acesso ao Geossítio Cachoeira ")</f>
         <v xml:space="preserve">ILUMINAÇÃO DO ACESSO AO GEOSSÍTIO CACHOEIRA </v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="10">
         <v>45224</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="10">
         <v>45559</v>
       </c>
-      <c r="K30" s="14" t="s">
+      <c r="K30" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="28">
         <v>524070.01</v>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="6">
         <v>100</v>
       </c>
-      <c r="N30" s="27" t="s">
+      <c r="N30" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="23">
         <v>2133</v>
       </c>
-      <c r="P30" s="27" t="s">
+      <c r="P30" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q30" s="28" t="s">
+      <c r="Q30" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="R30" s="28" t="s">
+      <c r="R30" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="S30" s="28"/>
-      <c r="T30" s="40"/>
-      <c r="U30" s="42" t="s">
+      <c r="S30" s="24"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="V30" s="42"/>
-      <c r="W30" s="42"/>
-      <c r="X30" s="42"/>
-      <c r="Y30" s="42"/>
-      <c r="Z30" s="42"/>
-      <c r="AA30" s="42"/>
-      <c r="AB30" s="42"/>
-      <c r="AC30" s="42"/>
-      <c r="AD30" s="42"/>
-      <c r="AE30" s="42"/>
-      <c r="AF30" s="42"/>
-      <c r="AG30" s="42"/>
-      <c r="AH30" s="42"/>
-      <c r="AI30" s="42"/>
-      <c r="AJ30" s="42"/>
-      <c r="AK30" s="42"/>
-      <c r="AL30" s="42"/>
-      <c r="AM30" s="42"/>
-      <c r="AN30" s="42"/>
-      <c r="AO30" s="42"/>
-      <c r="AP30" s="42"/>
-      <c r="AQ30" s="42"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="37"/>
+      <c r="Y30" s="37"/>
+      <c r="Z30" s="37"/>
+      <c r="AA30" s="37"/>
+      <c r="AB30" s="37"/>
+      <c r="AC30" s="37"/>
+      <c r="AD30" s="37"/>
+      <c r="AE30" s="37"/>
+      <c r="AF30" s="37"/>
+      <c r="AG30" s="37"/>
+      <c r="AH30" s="37"/>
+      <c r="AI30" s="37"/>
+      <c r="AJ30" s="37"/>
+      <c r="AK30" s="37"/>
+      <c r="AL30" s="37"/>
+      <c r="AM30" s="37"/>
+      <c r="AN30" s="37"/>
+      <c r="AO30" s="37"/>
+      <c r="AP30" s="37"/>
+      <c r="AQ30" s="37"/>
     </row>
     <row r="31" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="6">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="25">
         <v>4.7</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="10">
         <v>44490</v>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="10">
         <v>45588</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="K31" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="28">
         <v>25687719.870000001</v>
       </c>
-      <c r="M31" s="8">
+      <c r="M31" s="6">
         <v>100</v>
       </c>
-      <c r="N31" s="27" t="s">
+      <c r="N31" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="23">
         <v>831</v>
       </c>
-      <c r="P31" s="27" t="s">
+      <c r="P31" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="28" t="s">
+      <c r="Q31" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="R31" s="28" t="s">
+      <c r="R31" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="S31" s="28" t="s">
+      <c r="S31" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="T31" s="40" t="s">
+      <c r="T31" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="U31" s="42" t="s">
+      <c r="U31" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="V31" s="42" t="s">
+      <c r="V31" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="W31" s="42"/>
-      <c r="X31" s="42"/>
-      <c r="Y31" s="42"/>
-      <c r="Z31" s="42"/>
-      <c r="AA31" s="42"/>
-      <c r="AB31" s="42"/>
-      <c r="AC31" s="42"/>
-      <c r="AD31" s="42"/>
-      <c r="AE31" s="42"/>
-      <c r="AF31" s="42"/>
-      <c r="AG31" s="42"/>
-      <c r="AH31" s="42"/>
-      <c r="AI31" s="42"/>
-      <c r="AJ31" s="42"/>
-      <c r="AK31" s="42"/>
-      <c r="AL31" s="42"/>
-      <c r="AM31" s="42"/>
-      <c r="AN31" s="42"/>
-      <c r="AO31" s="42"/>
-      <c r="AP31" s="42"/>
-      <c r="AQ31" s="42"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="37"/>
+      <c r="Y31" s="37"/>
+      <c r="Z31" s="37"/>
+      <c r="AA31" s="37"/>
+      <c r="AB31" s="37"/>
+      <c r="AC31" s="37"/>
+      <c r="AD31" s="37"/>
+      <c r="AE31" s="37"/>
+      <c r="AF31" s="37"/>
+      <c r="AG31" s="37"/>
+      <c r="AH31" s="37"/>
+      <c r="AI31" s="37"/>
+      <c r="AJ31" s="37"/>
+      <c r="AK31" s="37"/>
+      <c r="AL31" s="37"/>
+      <c r="AM31" s="37"/>
+      <c r="AN31" s="37"/>
+      <c r="AO31" s="37"/>
+      <c r="AP31" s="37"/>
+      <c r="AQ31" s="37"/>
     </row>
     <row r="32" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="6">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="25">
         <v>2.6</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="10">
         <v>45194</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="10">
         <v>45519</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="K32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L32" s="36">
+      <c r="L32" s="31">
         <v>8203250.1699999999</v>
       </c>
-      <c r="M32" s="8">
+      <c r="M32" s="6">
         <v>100</v>
       </c>
-      <c r="N32" s="27" t="s">
+      <c r="N32" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="O32" s="27">
+      <c r="O32" s="23">
         <v>1418</v>
       </c>
-      <c r="P32" s="27" t="s">
+      <c r="P32" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q32" s="28" t="s">
+      <c r="Q32" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="R32" s="28" t="s">
+      <c r="R32" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="S32" s="28" t="s">
+      <c r="S32" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="T32" s="40" t="s">
+      <c r="T32" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="U32" s="42" t="s">
+      <c r="U32" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="V32" s="42"/>
-      <c r="W32" s="42"/>
-      <c r="X32" s="42"/>
-      <c r="Y32" s="42"/>
-      <c r="Z32" s="42"/>
-      <c r="AA32" s="42"/>
-      <c r="AB32" s="42"/>
-      <c r="AC32" s="42"/>
-      <c r="AD32" s="42"/>
-      <c r="AE32" s="42"/>
-      <c r="AF32" s="42"/>
-      <c r="AG32" s="42"/>
-      <c r="AH32" s="42"/>
-      <c r="AI32" s="42"/>
-      <c r="AJ32" s="42"/>
-      <c r="AK32" s="42"/>
-      <c r="AL32" s="42"/>
-      <c r="AM32" s="42"/>
-      <c r="AN32" s="42"/>
-      <c r="AO32" s="42"/>
-      <c r="AP32" s="42"/>
-      <c r="AQ32" s="42"/>
+      <c r="V32" s="37"/>
+      <c r="W32" s="37"/>
+      <c r="X32" s="37"/>
+      <c r="Y32" s="37"/>
+      <c r="Z32" s="37"/>
+      <c r="AA32" s="37"/>
+      <c r="AB32" s="37"/>
+      <c r="AC32" s="37"/>
+      <c r="AD32" s="37"/>
+      <c r="AE32" s="37"/>
+      <c r="AF32" s="37"/>
+      <c r="AG32" s="37"/>
+      <c r="AH32" s="37"/>
+      <c r="AI32" s="37"/>
+      <c r="AJ32" s="37"/>
+      <c r="AK32" s="37"/>
+      <c r="AL32" s="37"/>
+      <c r="AM32" s="37"/>
+      <c r="AN32" s="37"/>
+      <c r="AO32" s="37"/>
+      <c r="AP32" s="37"/>
+      <c r="AQ32" s="37"/>
     </row>
     <row r="33" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="6">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="25">
         <v>28.64</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="10">
         <v>44672</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="10">
         <v>45556</v>
       </c>
-      <c r="K33" s="14" t="s">
+      <c r="K33" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="31">
         <v>21929959.289999999</v>
       </c>
-      <c r="M33" s="8">
+      <c r="M33" s="6">
         <v>100</v>
       </c>
-      <c r="N33" s="27" t="s">
+      <c r="N33" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="O33" s="27">
+      <c r="O33" s="23">
         <v>707</v>
       </c>
-      <c r="P33" s="27" t="s">
+      <c r="P33" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q33" s="28" t="s">
+      <c r="Q33" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="R33" s="28" t="s">
+      <c r="R33" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="S33" s="28" t="s">
+      <c r="S33" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="T33" s="40" t="s">
+      <c r="T33" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="U33" s="42" t="s">
+      <c r="U33" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="V33" s="42" t="s">
+      <c r="V33" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="W33" s="42"/>
-      <c r="X33" s="42"/>
-      <c r="Y33" s="42"/>
-      <c r="Z33" s="42"/>
-      <c r="AA33" s="42"/>
-      <c r="AB33" s="42"/>
-      <c r="AC33" s="42"/>
-      <c r="AD33" s="42"/>
-      <c r="AE33" s="42"/>
-      <c r="AF33" s="42"/>
-      <c r="AG33" s="42"/>
-      <c r="AH33" s="42"/>
-      <c r="AI33" s="42"/>
-      <c r="AJ33" s="42"/>
-      <c r="AK33" s="42"/>
-      <c r="AL33" s="42"/>
-      <c r="AM33" s="42"/>
-      <c r="AN33" s="42"/>
-      <c r="AO33" s="42"/>
-      <c r="AP33" s="42"/>
-      <c r="AQ33" s="42"/>
+      <c r="W33" s="37"/>
+      <c r="X33" s="37"/>
+      <c r="Y33" s="37"/>
+      <c r="Z33" s="37"/>
+      <c r="AA33" s="37"/>
+      <c r="AB33" s="37"/>
+      <c r="AC33" s="37"/>
+      <c r="AD33" s="37"/>
+      <c r="AE33" s="37"/>
+      <c r="AF33" s="37"/>
+      <c r="AG33" s="37"/>
+      <c r="AH33" s="37"/>
+      <c r="AI33" s="37"/>
+      <c r="AJ33" s="37"/>
+      <c r="AK33" s="37"/>
+      <c r="AL33" s="37"/>
+      <c r="AM33" s="37"/>
+      <c r="AN33" s="37"/>
+      <c r="AO33" s="37"/>
+      <c r="AP33" s="37"/>
+      <c r="AQ33" s="37"/>
     </row>
     <row r="34" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="6">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="25">
         <v>1.42</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="10">
         <v>44916</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="10">
         <v>45516</v>
       </c>
-      <c r="K34" s="14" t="s">
+      <c r="K34" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L34" s="36">
+      <c r="L34" s="31">
         <v>5521746</v>
       </c>
-      <c r="M34" s="8">
+      <c r="M34" s="6">
         <v>100</v>
       </c>
-      <c r="N34" s="27" t="s">
+      <c r="N34" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="O34" s="27">
+      <c r="O34" s="23">
         <v>2169</v>
       </c>
-      <c r="P34" s="27" t="s">
+      <c r="P34" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q34" s="28" t="s">
+      <c r="Q34" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="R34" s="28" t="s">
+      <c r="R34" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="S34" s="37" t="s">
+      <c r="S34" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="T34" s="40"/>
-      <c r="U34" s="42" t="s">
+      <c r="T34" s="35"/>
+      <c r="U34" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="V34" s="42" t="s">
+      <c r="V34" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="W34" s="42"/>
-      <c r="X34" s="42"/>
-      <c r="Y34" s="42"/>
-      <c r="Z34" s="42"/>
-      <c r="AA34" s="42"/>
-      <c r="AB34" s="42"/>
-      <c r="AC34" s="42"/>
-      <c r="AD34" s="42"/>
-      <c r="AE34" s="42"/>
-      <c r="AF34" s="42"/>
-      <c r="AG34" s="42"/>
-      <c r="AH34" s="42"/>
-      <c r="AI34" s="42"/>
-      <c r="AJ34" s="42"/>
-      <c r="AK34" s="42"/>
-      <c r="AL34" s="42"/>
-      <c r="AM34" s="42"/>
-      <c r="AN34" s="42"/>
-      <c r="AO34" s="42"/>
-      <c r="AP34" s="42"/>
-      <c r="AQ34" s="42"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="37"/>
+      <c r="Y34" s="37"/>
+      <c r="Z34" s="37"/>
+      <c r="AA34" s="37"/>
+      <c r="AB34" s="37"/>
+      <c r="AC34" s="37"/>
+      <c r="AD34" s="37"/>
+      <c r="AE34" s="37"/>
+      <c r="AF34" s="37"/>
+      <c r="AG34" s="37"/>
+      <c r="AH34" s="37"/>
+      <c r="AI34" s="37"/>
+      <c r="AJ34" s="37"/>
+      <c r="AK34" s="37"/>
+      <c r="AL34" s="37"/>
+      <c r="AM34" s="37"/>
+      <c r="AN34" s="37"/>
+      <c r="AO34" s="37"/>
+      <c r="AP34" s="37"/>
+      <c r="AQ34" s="37"/>
     </row>
     <row r="35" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35" s="6">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="25">
         <f>220/1000</f>
         <v>0.22</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F35" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="10">
         <v>45190</v>
       </c>
-      <c r="J35" s="12">
+      <c r="J35" s="10">
         <v>45581</v>
       </c>
-      <c r="K35" s="14" t="s">
+      <c r="K35" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="31">
         <v>2769121.2</v>
       </c>
-      <c r="M35" s="8">
+      <c r="M35" s="6">
         <v>100</v>
       </c>
-      <c r="N35" s="27" t="s">
+      <c r="N35" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="O35" s="27">
+      <c r="O35" s="23">
         <v>1100</v>
       </c>
-      <c r="P35" s="27" t="s">
+      <c r="P35" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q35" s="28" t="s">
+      <c r="Q35" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="R35" s="28" t="s">
+      <c r="R35" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="S35" s="28" t="s">
+      <c r="S35" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="T35" s="40"/>
-      <c r="U35" s="42" t="s">
+      <c r="T35" s="35"/>
+      <c r="U35" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="V35" s="42" t="s">
+      <c r="V35" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="W35" s="42"/>
-      <c r="X35" s="42"/>
-      <c r="Y35" s="42"/>
-      <c r="Z35" s="42"/>
-      <c r="AA35" s="42"/>
-      <c r="AB35" s="42"/>
-      <c r="AC35" s="42"/>
-      <c r="AD35" s="42"/>
-      <c r="AE35" s="42"/>
-      <c r="AF35" s="42"/>
-      <c r="AG35" s="42"/>
-      <c r="AH35" s="42"/>
-      <c r="AI35" s="42"/>
-      <c r="AJ35" s="42"/>
-      <c r="AK35" s="42"/>
-      <c r="AL35" s="42"/>
-      <c r="AM35" s="42"/>
-      <c r="AN35" s="42"/>
-      <c r="AO35" s="42"/>
-      <c r="AP35" s="42"/>
-      <c r="AQ35" s="42"/>
+      <c r="W35" s="37"/>
+      <c r="X35" s="37"/>
+      <c r="Y35" s="37"/>
+      <c r="Z35" s="37"/>
+      <c r="AA35" s="37"/>
+      <c r="AB35" s="37"/>
+      <c r="AC35" s="37"/>
+      <c r="AD35" s="37"/>
+      <c r="AE35" s="37"/>
+      <c r="AF35" s="37"/>
+      <c r="AG35" s="37"/>
+      <c r="AH35" s="37"/>
+      <c r="AI35" s="37"/>
+      <c r="AJ35" s="37"/>
+      <c r="AK35" s="37"/>
+      <c r="AL35" s="37"/>
+      <c r="AM35" s="37"/>
+      <c r="AN35" s="37"/>
+      <c r="AO35" s="37"/>
+      <c r="AP35" s="37"/>
+      <c r="AQ35" s="37"/>
     </row>
     <row r="36" spans="1:45" ht="60" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36" s="6">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="C36" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="D36" s="33" t="s">
+      <c r="D36" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="25">
         <v>6.57</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="10">
         <v>45006</v>
       </c>
-      <c r="J36" s="12">
+      <c r="J36" s="10">
         <v>45546</v>
       </c>
-      <c r="K36" s="14" t="s">
+      <c r="K36" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="31">
         <v>47366423.520000003</v>
       </c>
-      <c r="M36" s="8">
+      <c r="M36" s="6">
         <v>100</v>
       </c>
-      <c r="N36" s="27" t="s">
+      <c r="N36" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="O36" s="27">
+      <c r="O36" s="23">
         <v>785</v>
       </c>
-      <c r="P36" s="27" t="s">
+      <c r="P36" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q36" s="28" t="s">
+      <c r="Q36" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="R36" s="28" t="s">
+      <c r="R36" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="S36" s="28" t="s">
+      <c r="S36" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="T36" s="40" t="s">
+      <c r="T36" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="U36" s="42" t="s">
+      <c r="U36" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="V36" s="42" t="s">
+      <c r="V36" s="37" t="s">
         <v>309</v>
       </c>
-      <c r="W36" s="42"/>
-      <c r="X36" s="42"/>
-      <c r="Y36" s="42"/>
-      <c r="Z36" s="42"/>
-      <c r="AA36" s="42"/>
-      <c r="AB36" s="42"/>
-      <c r="AC36" s="42"/>
-      <c r="AD36" s="42"/>
-      <c r="AE36" s="42"/>
-      <c r="AF36" s="42"/>
-      <c r="AG36" s="42"/>
-      <c r="AH36" s="42"/>
-      <c r="AI36" s="42"/>
-      <c r="AJ36" s="42"/>
-      <c r="AK36" s="42"/>
-      <c r="AL36" s="42"/>
-      <c r="AM36" s="42"/>
-      <c r="AN36" s="42"/>
-      <c r="AO36" s="42"/>
-      <c r="AP36" s="42"/>
-      <c r="AQ36" s="42"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="37"/>
+      <c r="Y36" s="37"/>
+      <c r="Z36" s="37"/>
+      <c r="AA36" s="37"/>
+      <c r="AB36" s="37"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="37"/>
+      <c r="AE36" s="37"/>
+      <c r="AF36" s="37"/>
+      <c r="AG36" s="37"/>
+      <c r="AH36" s="37"/>
+      <c r="AI36" s="37"/>
+      <c r="AJ36" s="37"/>
+      <c r="AK36" s="37"/>
+      <c r="AL36" s="37"/>
+      <c r="AM36" s="37"/>
+      <c r="AN36" s="37"/>
+      <c r="AO36" s="37"/>
+      <c r="AP36" s="37"/>
+      <c r="AQ36" s="37"/>
     </row>
     <row r="37" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="56" t="s">
         <v>254</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="23">
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="20">
         <f>SUM(E18:E36)</f>
         <v>244.78999999999996</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24">
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21">
         <f>SUM(L18:L36)</f>
         <v>332048225.94999999</v>
       </c>
-      <c r="M37" s="57" t="s">
+      <c r="M37" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="N37" s="58"/>
-      <c r="O37" s="58"/>
-      <c r="P37" s="58"/>
-      <c r="Q37" s="58"/>
-      <c r="R37" s="58"/>
-      <c r="S37" s="58"/>
-      <c r="T37" s="58"/>
-      <c r="U37" s="58"/>
-      <c r="V37" s="58"/>
-      <c r="W37" s="58"/>
-      <c r="X37" s="58"/>
-      <c r="Y37" s="58"/>
-      <c r="Z37" s="58"/>
-      <c r="AA37" s="58"/>
-      <c r="AB37" s="58"/>
-      <c r="AC37" s="58"/>
-      <c r="AD37" s="58"/>
-      <c r="AE37" s="58"/>
-      <c r="AF37" s="58"/>
-      <c r="AG37" s="58"/>
-      <c r="AH37" s="58"/>
-      <c r="AI37" s="58"/>
-      <c r="AJ37" s="58"/>
-      <c r="AK37" s="58"/>
-      <c r="AL37" s="58"/>
-      <c r="AM37" s="58"/>
-      <c r="AN37" s="58"/>
-      <c r="AO37" s="58"/>
-      <c r="AP37" s="58"/>
-      <c r="AQ37" s="59"/>
-      <c r="AR37" s="16"/>
-      <c r="AS37" s="16"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="44"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="44"/>
+      <c r="V37" s="44"/>
+      <c r="W37" s="44"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="44"/>
+      <c r="Z37" s="44"/>
+      <c r="AA37" s="44"/>
+      <c r="AB37" s="44"/>
+      <c r="AC37" s="44"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="44"/>
+      <c r="AF37" s="44"/>
+      <c r="AG37" s="44"/>
+      <c r="AH37" s="44"/>
+      <c r="AI37" s="44"/>
+      <c r="AJ37" s="44"/>
+      <c r="AK37" s="44"/>
+      <c r="AL37" s="44"/>
+      <c r="AM37" s="44"/>
+      <c r="AN37" s="44"/>
+      <c r="AO37" s="44"/>
+      <c r="AP37" s="44"/>
+      <c r="AQ37" s="57"/>
+      <c r="AR37" s="14"/>
+      <c r="AS37" s="14"/>
+    </row>
+    <row r="38" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="59"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="59"/>
+      <c r="M38" s="59"/>
+      <c r="N38" s="59"/>
+      <c r="O38" s="59"/>
+      <c r="P38" s="59"/>
+      <c r="Q38" s="59"/>
+      <c r="R38" s="59"/>
+      <c r="S38" s="59"/>
+      <c r="T38" s="59"/>
+    </row>
+    <row r="39" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>31</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="E39" s="25">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="26">
+        <v>45467</v>
+      </c>
+      <c r="J39" s="26">
+        <v>45767</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L39" s="28">
+        <v>8410358.8900000006</v>
+      </c>
+      <c r="M39" s="6">
+        <v>1</v>
+      </c>
+      <c r="N39" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="O39" s="23">
+        <v>2601</v>
+      </c>
+      <c r="P39" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q39" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="R39" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="S39" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="T39" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="U39" s="65" t="s">
+        <v>401</v>
+      </c>
+      <c r="V39" s="37"/>
+      <c r="W39" s="37"/>
+      <c r="X39" s="37"/>
+      <c r="Y39" s="37"/>
+      <c r="Z39" s="37"/>
+      <c r="AA39" s="37"/>
+      <c r="AB39" s="37"/>
+      <c r="AC39" s="37"/>
+      <c r="AD39" s="37"/>
+      <c r="AE39" s="37"/>
+      <c r="AF39" s="37"/>
+      <c r="AG39" s="37"/>
+      <c r="AH39" s="37"/>
+      <c r="AI39" s="37"/>
+      <c r="AJ39" s="37"/>
+      <c r="AK39" s="37"/>
+      <c r="AL39" s="37"/>
+      <c r="AM39" s="37"/>
+      <c r="AN39" s="37"/>
+      <c r="AO39" s="37"/>
+      <c r="AP39" s="37"/>
+      <c r="AQ39" s="37"/>
+    </row>
+    <row r="40" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <f t="shared" ref="A40:A54" si="2">A39+1</f>
+        <v>32</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="E40" s="25">
+        <v>3.52</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G40" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="26">
+        <v>45450</v>
+      </c>
+      <c r="J40" s="26">
+        <v>45690</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L40" s="28">
+        <v>5895663.1699999999</v>
+      </c>
+      <c r="M40" s="6">
+        <v>1</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="O40" s="23">
+        <v>2280</v>
+      </c>
+      <c r="P40" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q40" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="R40" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="S40" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="T40" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="U40" s="65" t="s">
+        <v>402</v>
+      </c>
+      <c r="V40" s="37"/>
+      <c r="W40" s="37"/>
+      <c r="X40" s="37"/>
+      <c r="Y40" s="37"/>
+      <c r="Z40" s="37"/>
+      <c r="AA40" s="37"/>
+      <c r="AB40" s="37"/>
+      <c r="AC40" s="37"/>
+      <c r="AD40" s="37"/>
+      <c r="AE40" s="37"/>
+      <c r="AF40" s="37"/>
+      <c r="AG40" s="37"/>
+      <c r="AH40" s="37"/>
+      <c r="AI40" s="37"/>
+      <c r="AJ40" s="37"/>
+      <c r="AK40" s="37"/>
+      <c r="AL40" s="37"/>
+      <c r="AM40" s="37"/>
+      <c r="AN40" s="37"/>
+      <c r="AO40" s="37"/>
+      <c r="AP40" s="37"/>
+      <c r="AQ40" s="37"/>
+    </row>
+    <row r="41" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E41" s="25">
+        <v>20.16</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="G41" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="I41" s="26">
+        <v>44837</v>
+      </c>
+      <c r="J41" s="26">
+        <v>45707</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L41" s="28">
+        <v>23556493.370000001</v>
+      </c>
+      <c r="M41" s="6">
+        <v>1</v>
+      </c>
+      <c r="N41" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="O41" s="23">
+        <v>2190</v>
+      </c>
+      <c r="P41" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q41" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="R41" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="S41" s="24"/>
+      <c r="T41" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="U41" s="65" t="s">
+        <v>403</v>
+      </c>
+      <c r="V41" s="37"/>
+      <c r="W41" s="37"/>
+      <c r="X41" s="37"/>
+      <c r="Y41" s="37"/>
+      <c r="Z41" s="37"/>
+      <c r="AA41" s="37"/>
+      <c r="AB41" s="37"/>
+      <c r="AC41" s="37"/>
+      <c r="AD41" s="37"/>
+      <c r="AE41" s="37"/>
+      <c r="AF41" s="37"/>
+      <c r="AG41" s="37"/>
+      <c r="AH41" s="37"/>
+      <c r="AI41" s="37"/>
+      <c r="AJ41" s="37"/>
+      <c r="AK41" s="37"/>
+      <c r="AL41" s="37"/>
+      <c r="AM41" s="37"/>
+      <c r="AN41" s="37"/>
+      <c r="AO41" s="37"/>
+      <c r="AP41" s="37"/>
+      <c r="AQ41" s="37"/>
+    </row>
+    <row r="42" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="E42" s="25">
+        <v>23.2</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I42" s="26">
+        <v>45222</v>
+      </c>
+      <c r="J42" s="26">
+        <v>45792</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L42" s="28">
+        <v>30980268.039999999</v>
+      </c>
+      <c r="M42" s="6">
+        <v>1</v>
+      </c>
+      <c r="N42" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="O42" s="23">
+        <v>1431</v>
+      </c>
+      <c r="P42" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q42" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="R42" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="S42" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="T42" s="33" t="s">
+        <v>338</v>
+      </c>
+      <c r="U42" s="65" t="s">
+        <v>404</v>
+      </c>
+      <c r="V42" s="37"/>
+      <c r="W42" s="37"/>
+      <c r="X42" s="37"/>
+      <c r="Y42" s="37"/>
+      <c r="Z42" s="37"/>
+      <c r="AA42" s="37"/>
+      <c r="AB42" s="37"/>
+      <c r="AC42" s="37"/>
+      <c r="AD42" s="37"/>
+      <c r="AE42" s="37"/>
+      <c r="AF42" s="37"/>
+      <c r="AG42" s="37"/>
+      <c r="AH42" s="37"/>
+      <c r="AI42" s="37"/>
+      <c r="AJ42" s="37"/>
+      <c r="AK42" s="37"/>
+      <c r="AL42" s="37"/>
+      <c r="AM42" s="37"/>
+      <c r="AN42" s="37"/>
+      <c r="AO42" s="37"/>
+      <c r="AP42" s="37"/>
+      <c r="AQ42" s="37"/>
+    </row>
+    <row r="43" spans="1:45" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="E43" s="25">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G43" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="26">
+        <v>45495</v>
+      </c>
+      <c r="J43" s="26">
+        <v>45782</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L43" s="28">
+        <v>3008187.68</v>
+      </c>
+      <c r="M43" s="6">
+        <v>1</v>
+      </c>
+      <c r="N43" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="O43" s="23">
+        <v>2521</v>
+      </c>
+      <c r="P43" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q43" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="R43" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="S43" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="T43" s="33"/>
+      <c r="U43" s="65" t="s">
+        <v>405</v>
+      </c>
+      <c r="V43" s="65" t="s">
+        <v>406</v>
+      </c>
+      <c r="W43" s="37"/>
+      <c r="X43" s="37"/>
+      <c r="Y43" s="37"/>
+      <c r="Z43" s="37"/>
+      <c r="AA43" s="37"/>
+      <c r="AB43" s="37"/>
+      <c r="AC43" s="37"/>
+      <c r="AD43" s="37"/>
+      <c r="AE43" s="37"/>
+      <c r="AF43" s="37"/>
+      <c r="AG43" s="37"/>
+      <c r="AH43" s="37"/>
+      <c r="AI43" s="37"/>
+      <c r="AJ43" s="37"/>
+      <c r="AK43" s="37"/>
+      <c r="AL43" s="37"/>
+      <c r="AM43" s="37"/>
+      <c r="AN43" s="37"/>
+      <c r="AO43" s="37"/>
+      <c r="AP43" s="37"/>
+      <c r="AQ43" s="37"/>
+    </row>
+    <row r="44" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="E44" s="25">
+        <v>0.24</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="G44" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I44" s="26">
+        <v>45527</v>
+      </c>
+      <c r="J44" s="26">
+        <v>45708</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L44" s="28">
+        <v>3555318.56</v>
+      </c>
+      <c r="M44" s="6">
+        <v>1</v>
+      </c>
+      <c r="N44" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="O44" s="23">
+        <v>2351</v>
+      </c>
+      <c r="P44" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q44" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="R44" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="S44" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="T44" s="33"/>
+      <c r="U44" s="65" t="s">
+        <v>407</v>
+      </c>
+      <c r="V44" s="65" t="s">
+        <v>408</v>
+      </c>
+      <c r="W44" s="37"/>
+      <c r="X44" s="37"/>
+      <c r="Y44" s="37"/>
+      <c r="Z44" s="37"/>
+      <c r="AA44" s="37"/>
+      <c r="AB44" s="37"/>
+      <c r="AC44" s="37"/>
+      <c r="AD44" s="37"/>
+      <c r="AE44" s="37"/>
+      <c r="AF44" s="37"/>
+      <c r="AG44" s="37"/>
+      <c r="AH44" s="37"/>
+      <c r="AI44" s="37"/>
+      <c r="AJ44" s="37"/>
+      <c r="AK44" s="37"/>
+      <c r="AL44" s="37"/>
+      <c r="AM44" s="37"/>
+      <c r="AN44" s="37"/>
+      <c r="AO44" s="37"/>
+      <c r="AP44" s="37"/>
+      <c r="AQ44" s="37"/>
+    </row>
+    <row r="45" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="G45" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="26">
+        <v>45559</v>
+      </c>
+      <c r="J45" s="26">
+        <v>45859</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L45" s="28">
+        <v>766987.87</v>
+      </c>
+      <c r="M45" s="6">
+        <v>1</v>
+      </c>
+      <c r="N45" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="O45" s="23">
+        <v>2404</v>
+      </c>
+      <c r="P45" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q45" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="R45" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="S45" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="T45" s="33"/>
+      <c r="U45" s="65" t="s">
+        <v>409</v>
+      </c>
+      <c r="V45" s="65" t="s">
+        <v>410</v>
+      </c>
+      <c r="W45" s="37"/>
+      <c r="X45" s="37"/>
+      <c r="Y45" s="37"/>
+      <c r="Z45" s="37"/>
+      <c r="AA45" s="37"/>
+      <c r="AB45" s="37"/>
+      <c r="AC45" s="37"/>
+      <c r="AD45" s="37"/>
+      <c r="AE45" s="37"/>
+      <c r="AF45" s="37"/>
+      <c r="AG45" s="37"/>
+      <c r="AH45" s="37"/>
+      <c r="AI45" s="37"/>
+      <c r="AJ45" s="37"/>
+      <c r="AK45" s="37"/>
+      <c r="AL45" s="37"/>
+      <c r="AM45" s="37"/>
+      <c r="AN45" s="37"/>
+      <c r="AO45" s="37"/>
+      <c r="AP45" s="37"/>
+      <c r="AQ45" s="37"/>
+    </row>
+    <row r="46" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" s="26">
+        <v>45691</v>
+      </c>
+      <c r="J46" s="26">
+        <v>45872</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L46" s="28">
+        <v>449911.64</v>
+      </c>
+      <c r="M46" s="6">
+        <v>1</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="O46" s="23">
+        <v>2897</v>
+      </c>
+      <c r="P46" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q46" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="R46" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="S46" s="24"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="65" t="s">
+        <v>411</v>
+      </c>
+      <c r="V46" s="65" t="s">
+        <v>412</v>
+      </c>
+      <c r="W46" s="37"/>
+      <c r="X46" s="37"/>
+      <c r="Y46" s="37"/>
+      <c r="Z46" s="37"/>
+      <c r="AA46" s="37"/>
+      <c r="AB46" s="37"/>
+      <c r="AC46" s="37"/>
+      <c r="AD46" s="37"/>
+      <c r="AE46" s="37"/>
+      <c r="AF46" s="37"/>
+      <c r="AG46" s="37"/>
+      <c r="AH46" s="37"/>
+      <c r="AI46" s="37"/>
+      <c r="AJ46" s="37"/>
+      <c r="AK46" s="37"/>
+      <c r="AL46" s="37"/>
+      <c r="AM46" s="37"/>
+      <c r="AN46" s="37"/>
+      <c r="AO46" s="37"/>
+      <c r="AP46" s="37"/>
+      <c r="AQ46" s="37"/>
+    </row>
+    <row r="47" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="E47" s="25">
+        <v>6.88</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="G47" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="26">
+        <v>44445</v>
+      </c>
+      <c r="J47" s="26">
+        <v>45728</v>
+      </c>
+      <c r="K47" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L47" s="28">
+        <v>25807464.879999999</v>
+      </c>
+      <c r="M47" s="6">
+        <v>1</v>
+      </c>
+      <c r="N47" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="O47" s="23">
+        <v>1174</v>
+      </c>
+      <c r="P47" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q47" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="R47" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="S47" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="T47" s="33"/>
+      <c r="U47" s="65" t="s">
+        <v>413</v>
+      </c>
+      <c r="V47" s="65" t="s">
+        <v>414</v>
+      </c>
+      <c r="W47" s="37"/>
+      <c r="X47" s="37"/>
+      <c r="Y47" s="37"/>
+      <c r="Z47" s="37"/>
+      <c r="AA47" s="37"/>
+      <c r="AB47" s="37"/>
+      <c r="AC47" s="37"/>
+      <c r="AD47" s="37"/>
+      <c r="AE47" s="37"/>
+      <c r="AF47" s="37"/>
+      <c r="AG47" s="37"/>
+      <c r="AH47" s="37"/>
+      <c r="AI47" s="37"/>
+      <c r="AJ47" s="37"/>
+      <c r="AK47" s="37"/>
+      <c r="AL47" s="37"/>
+      <c r="AM47" s="37"/>
+      <c r="AN47" s="37"/>
+      <c r="AO47" s="37"/>
+      <c r="AP47" s="37"/>
+      <c r="AQ47" s="37"/>
+    </row>
+    <row r="48" spans="1:45" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="E48" s="25">
+        <v>33.01</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="I48" s="26">
+        <v>45441</v>
+      </c>
+      <c r="J48" s="26">
+        <v>45861</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L48" s="28">
+        <v>45465195.979999997</v>
+      </c>
+      <c r="M48" s="6">
+        <v>1</v>
+      </c>
+      <c r="N48" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="O48" s="23">
+        <v>2692</v>
+      </c>
+      <c r="P48" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q48" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="R48" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="S48" s="24"/>
+      <c r="T48" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="U48" s="65" t="s">
+        <v>415</v>
+      </c>
+      <c r="V48" s="37"/>
+      <c r="W48" s="37"/>
+      <c r="X48" s="37"/>
+      <c r="Y48" s="37"/>
+      <c r="Z48" s="37"/>
+      <c r="AA48" s="37"/>
+      <c r="AB48" s="37"/>
+      <c r="AC48" s="37"/>
+      <c r="AD48" s="37"/>
+      <c r="AE48" s="37"/>
+      <c r="AF48" s="37"/>
+      <c r="AG48" s="37"/>
+      <c r="AH48" s="37"/>
+      <c r="AI48" s="37"/>
+      <c r="AJ48" s="37"/>
+      <c r="AK48" s="37"/>
+      <c r="AL48" s="37"/>
+      <c r="AM48" s="37"/>
+      <c r="AN48" s="37"/>
+      <c r="AO48" s="37"/>
+      <c r="AP48" s="37"/>
+      <c r="AQ48" s="37"/>
+    </row>
+    <row r="49" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="E49" s="25">
+        <v>24.64</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="G49" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="I49" s="26">
+        <v>45441</v>
+      </c>
+      <c r="J49" s="26">
+        <v>45891</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L49" s="28">
+        <v>31059366.289999999</v>
+      </c>
+      <c r="M49" s="6">
+        <v>1</v>
+      </c>
+      <c r="N49" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="O49" s="23">
+        <v>2691</v>
+      </c>
+      <c r="P49" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q49" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="R49" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="S49" s="24"/>
+      <c r="T49" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="U49" s="65" t="s">
+        <v>416</v>
+      </c>
+      <c r="V49" s="37"/>
+      <c r="W49" s="37"/>
+      <c r="X49" s="37"/>
+      <c r="Y49" s="37"/>
+      <c r="Z49" s="37"/>
+      <c r="AA49" s="37"/>
+      <c r="AB49" s="37"/>
+      <c r="AC49" s="37"/>
+      <c r="AD49" s="37"/>
+      <c r="AE49" s="37"/>
+      <c r="AF49" s="37"/>
+      <c r="AG49" s="37"/>
+      <c r="AH49" s="37"/>
+      <c r="AI49" s="37"/>
+      <c r="AJ49" s="37"/>
+      <c r="AK49" s="37"/>
+      <c r="AL49" s="37"/>
+      <c r="AM49" s="37"/>
+      <c r="AN49" s="37"/>
+      <c r="AO49" s="37"/>
+      <c r="AP49" s="37"/>
+      <c r="AQ49" s="37"/>
+    </row>
+    <row r="50" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="E50" s="25">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="G50" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" s="26">
+        <v>45338</v>
+      </c>
+      <c r="J50" s="26">
+        <v>45878</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L50" s="28">
+        <v>5558156.6900000004</v>
+      </c>
+      <c r="M50" s="6">
+        <v>1</v>
+      </c>
+      <c r="N50" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="O50" s="23">
+        <v>1436</v>
+      </c>
+      <c r="P50" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q50" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="R50" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="S50" s="24" t="s">
+        <v>377</v>
+      </c>
+      <c r="T50" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="U50" s="65" t="s">
+        <v>417</v>
+      </c>
+      <c r="V50" s="37"/>
+      <c r="W50" s="37"/>
+      <c r="X50" s="37"/>
+      <c r="Y50" s="37"/>
+      <c r="Z50" s="37"/>
+      <c r="AA50" s="37"/>
+      <c r="AB50" s="37"/>
+      <c r="AC50" s="37"/>
+      <c r="AD50" s="37"/>
+      <c r="AE50" s="37"/>
+      <c r="AF50" s="37"/>
+      <c r="AG50" s="37"/>
+      <c r="AH50" s="37"/>
+      <c r="AI50" s="37"/>
+      <c r="AJ50" s="37"/>
+      <c r="AK50" s="37"/>
+      <c r="AL50" s="37"/>
+      <c r="AM50" s="37"/>
+      <c r="AN50" s="37"/>
+      <c r="AO50" s="37"/>
+      <c r="AP50" s="37"/>
+      <c r="AQ50" s="37"/>
+    </row>
+    <row r="51" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="E51" s="25">
+        <v>17.96</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="I51" s="26">
+        <v>45128</v>
+      </c>
+      <c r="J51" s="26">
+        <v>45914</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L51" s="28">
+        <v>13610903.73</v>
+      </c>
+      <c r="M51" s="6">
+        <v>1</v>
+      </c>
+      <c r="N51" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="O51" s="23">
+        <v>2282</v>
+      </c>
+      <c r="P51" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q51" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="R51" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="S51" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="T51" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="U51" s="65" t="s">
+        <v>418</v>
+      </c>
+      <c r="V51" s="37"/>
+      <c r="W51" s="37"/>
+      <c r="X51" s="37"/>
+      <c r="Y51" s="37"/>
+      <c r="Z51" s="37"/>
+      <c r="AA51" s="37"/>
+      <c r="AB51" s="37"/>
+      <c r="AC51" s="37"/>
+      <c r="AD51" s="37"/>
+      <c r="AE51" s="37"/>
+      <c r="AF51" s="37"/>
+      <c r="AG51" s="37"/>
+      <c r="AH51" s="37"/>
+      <c r="AI51" s="37"/>
+      <c r="AJ51" s="37"/>
+      <c r="AK51" s="37"/>
+      <c r="AL51" s="37"/>
+      <c r="AM51" s="37"/>
+      <c r="AN51" s="37"/>
+      <c r="AO51" s="37"/>
+      <c r="AP51" s="37"/>
+      <c r="AQ51" s="37"/>
+    </row>
+    <row r="52" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>384</v>
+      </c>
+      <c r="E52" s="25">
+        <v>26.64</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="I52" s="26">
+        <v>45446</v>
+      </c>
+      <c r="J52" s="26">
+        <v>45896</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L52" s="28">
+        <v>33263573.260000002</v>
+      </c>
+      <c r="M52" s="6">
+        <v>1</v>
+      </c>
+      <c r="N52" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="O52" s="23">
+        <v>2690</v>
+      </c>
+      <c r="P52" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q52" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="R52" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="S52" s="24"/>
+      <c r="T52" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="U52" s="65" t="s">
+        <v>419</v>
+      </c>
+      <c r="V52" s="65" t="s">
+        <v>420</v>
+      </c>
+      <c r="W52" s="37"/>
+      <c r="X52" s="37"/>
+      <c r="Y52" s="37"/>
+      <c r="Z52" s="37"/>
+      <c r="AA52" s="37"/>
+      <c r="AB52" s="37"/>
+      <c r="AC52" s="37"/>
+      <c r="AD52" s="37"/>
+      <c r="AE52" s="37"/>
+      <c r="AF52" s="37"/>
+      <c r="AG52" s="37"/>
+      <c r="AH52" s="37"/>
+      <c r="AI52" s="37"/>
+      <c r="AJ52" s="37"/>
+      <c r="AK52" s="37"/>
+      <c r="AL52" s="37"/>
+      <c r="AM52" s="37"/>
+      <c r="AN52" s="37"/>
+      <c r="AO52" s="37"/>
+      <c r="AP52" s="37"/>
+      <c r="AQ52" s="37"/>
+    </row>
+    <row r="53" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="E53" s="25">
+        <v>5.16</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I53" s="26">
+        <v>44672</v>
+      </c>
+      <c r="J53" s="26">
+        <v>45979</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L53" s="28">
+        <v>5692584.3499999996</v>
+      </c>
+      <c r="M53" s="6">
+        <v>1</v>
+      </c>
+      <c r="N53" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="O53" s="23">
+        <v>1752</v>
+      </c>
+      <c r="P53" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q53" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="R53" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="S53" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="T53" s="33"/>
+      <c r="U53" s="65" t="s">
+        <v>421</v>
+      </c>
+      <c r="V53" s="65" t="s">
+        <v>422</v>
+      </c>
+      <c r="W53" s="37"/>
+      <c r="X53" s="37"/>
+      <c r="Y53" s="37"/>
+      <c r="Z53" s="37"/>
+      <c r="AA53" s="37"/>
+      <c r="AB53" s="37"/>
+      <c r="AC53" s="37"/>
+      <c r="AD53" s="37"/>
+      <c r="AE53" s="37"/>
+      <c r="AF53" s="37"/>
+      <c r="AG53" s="37"/>
+      <c r="AH53" s="37"/>
+      <c r="AI53" s="37"/>
+      <c r="AJ53" s="37"/>
+      <c r="AK53" s="37"/>
+      <c r="AL53" s="37"/>
+      <c r="AM53" s="37"/>
+      <c r="AN53" s="37"/>
+      <c r="AO53" s="37"/>
+      <c r="AP53" s="37"/>
+      <c r="AQ53" s="37"/>
+    </row>
+    <row r="54" spans="1:43" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I54" s="26">
+        <v>45842</v>
+      </c>
+      <c r="J54" s="26">
+        <v>46022</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="L54" s="28">
+        <v>2670688.4300000002</v>
+      </c>
+      <c r="M54" s="6">
+        <v>0.99419999999999997</v>
+      </c>
+      <c r="N54" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="O54" s="23">
+        <v>3156</v>
+      </c>
+      <c r="P54" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q54" s="23"/>
+      <c r="R54" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="S54" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="T54" s="33"/>
+      <c r="U54" s="65" t="s">
+        <v>423</v>
+      </c>
+      <c r="V54" s="65" t="s">
+        <v>424</v>
+      </c>
+      <c r="W54" s="37"/>
+      <c r="X54" s="37"/>
+      <c r="Y54" s="37"/>
+      <c r="Z54" s="37"/>
+      <c r="AA54" s="37"/>
+      <c r="AB54" s="37"/>
+      <c r="AC54" s="37"/>
+      <c r="AD54" s="37"/>
+      <c r="AE54" s="37"/>
+      <c r="AF54" s="37"/>
+      <c r="AG54" s="37"/>
+      <c r="AH54" s="37"/>
+      <c r="AI54" s="37"/>
+      <c r="AJ54" s="37"/>
+      <c r="AK54" s="37"/>
+      <c r="AL54" s="37"/>
+      <c r="AM54" s="37"/>
+      <c r="AN54" s="37"/>
+      <c r="AO54" s="37"/>
+      <c r="AP54" s="37"/>
+      <c r="AQ54" s="37"/>
+    </row>
+    <row r="55" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="60" t="s">
+        <v>400</v>
+      </c>
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="62">
+        <f>SUM(E39:E54)</f>
+        <v>176.05499999999998</v>
+      </c>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="64"/>
+      <c r="L55" s="64">
+        <f>SUM(L39:L54)</f>
+        <v>239751122.82999998</v>
+      </c>
+      <c r="M55" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="N55" s="59"/>
+      <c r="O55" s="59"/>
+      <c r="P55" s="59"/>
+      <c r="Q55" s="59"/>
+      <c r="R55" s="59"/>
+      <c r="S55" s="59"/>
+      <c r="T55" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="M37:AQ37"/>
+    <mergeCell ref="A38:T38"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="M55:T55"/>
     <mergeCell ref="U3:AQ3"/>
     <mergeCell ref="A4:AQ4"/>
     <mergeCell ref="M16:AQ16"/>
     <mergeCell ref="A17:AQ17"/>
     <mergeCell ref="A1:T2"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="M37:AQ37"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/OBRAS.xlsx
+++ b/OBRAS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\SISTEMA LVC WEB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85AE520-4E59-4156-BC30-43C8FD629E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53529B91-60A1-4858-81EF-660881AE85FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AD94D340-EAD9-4641-9722-F4A49FD1A579}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{AD94D340-EAD9-4641-9722-F4A49FD1A579}"/>
   </bookViews>
   <sheets>
     <sheet name="OBRAS 2023" sheetId="1" r:id="rId1"/>
@@ -1939,7 +1939,7 @@
     <numFmt numFmtId="167" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="168" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="169" formatCode="0.00&quot;%&quot;"/>
-    <numFmt numFmtId="181" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -2258,7 +2258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2372,26 +2372,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2407,9 +2392,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2503,7 +2485,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2636,190 +2618,38 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="1" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE599"/>
-          <bgColor rgb="FFFFE599"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEA9999"/>
-          <bgColor rgb="FFEA9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -2919,10 +2749,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3169,51 +2995,51 @@
     <col min="41" max="16384" width="14.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:45" ht="15" customHeight="1">
+      <c r="A1" s="128" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="46"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="41"/>
     </row>
     <row r="2" spans="1:45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="49"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
     </row>
     <row r="3" spans="1:45" ht="45">
       <c r="A3" s="1" t="s">
@@ -3276,80 +3102,80 @@
       <c r="T3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="40" t="s">
+      <c r="U3" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="123"/>
+      <c r="AA3" s="123"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="123"/>
+      <c r="AD3" s="123"/>
+      <c r="AE3" s="123"/>
+      <c r="AF3" s="123"/>
+      <c r="AG3" s="123"/>
+      <c r="AH3" s="123"/>
+      <c r="AI3" s="123"/>
+      <c r="AJ3" s="123"/>
+      <c r="AK3" s="123"/>
+      <c r="AL3" s="123"/>
+      <c r="AM3" s="123"/>
+      <c r="AN3" s="123"/>
+      <c r="AO3" s="123"/>
+      <c r="AP3" s="123"/>
+      <c r="AQ3" s="123"/>
       <c r="AR3" s="5"/>
       <c r="AS3" s="5"/>
     </row>
     <row r="4" spans="1:45">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="43"/>
-      <c r="AA4" s="43"/>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="43"/>
-      <c r="AD4" s="43"/>
-      <c r="AE4" s="43"/>
-      <c r="AF4" s="43"/>
-      <c r="AG4" s="43"/>
-      <c r="AH4" s="43"/>
-      <c r="AI4" s="43"/>
-      <c r="AJ4" s="43"/>
-      <c r="AK4" s="43"/>
-      <c r="AL4" s="43"/>
-      <c r="AM4" s="43"/>
-      <c r="AN4" s="43"/>
-      <c r="AO4" s="43"/>
-      <c r="AP4" s="43"/>
-      <c r="AQ4" s="43"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="125"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="125"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="125"/>
+      <c r="T4" s="125"/>
+      <c r="U4" s="125"/>
+      <c r="V4" s="125"/>
+      <c r="W4" s="125"/>
+      <c r="X4" s="125"/>
+      <c r="Y4" s="125"/>
+      <c r="Z4" s="125"/>
+      <c r="AA4" s="125"/>
+      <c r="AB4" s="125"/>
+      <c r="AC4" s="125"/>
+      <c r="AD4" s="125"/>
+      <c r="AE4" s="125"/>
+      <c r="AF4" s="125"/>
+      <c r="AG4" s="125"/>
+      <c r="AH4" s="125"/>
+      <c r="AI4" s="125"/>
+      <c r="AJ4" s="125"/>
+      <c r="AK4" s="125"/>
+      <c r="AL4" s="125"/>
+      <c r="AM4" s="125"/>
+      <c r="AN4" s="125"/>
+      <c r="AO4" s="125"/>
+      <c r="AP4" s="125"/>
+      <c r="AQ4" s="125"/>
       <c r="AR4" s="5"/>
       <c r="AS4" s="5"/>
     </row>
@@ -3412,33 +3238,33 @@
       <c r="T5" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="U5" s="51" t="s">
+      <c r="U5" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="51" t="s">
+      <c r="V5" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="W5" s="51"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="51"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="52"/>
-      <c r="AD5" s="52"/>
-      <c r="AE5" s="52"/>
-      <c r="AF5" s="52"/>
-      <c r="AG5" s="52"/>
-      <c r="AH5" s="52"/>
-      <c r="AI5" s="52"/>
-      <c r="AJ5" s="52"/>
-      <c r="AK5" s="52"/>
-      <c r="AL5" s="52"/>
-      <c r="AM5" s="52"/>
-      <c r="AN5" s="52"/>
-      <c r="AO5" s="52"/>
-      <c r="AP5" s="52"/>
-      <c r="AQ5" s="52"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
+      <c r="Z5" s="45"/>
+      <c r="AA5" s="45"/>
+      <c r="AB5" s="45"/>
+      <c r="AC5" s="46"/>
+      <c r="AD5" s="46"/>
+      <c r="AE5" s="46"/>
+      <c r="AF5" s="46"/>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="46"/>
+      <c r="AI5" s="46"/>
+      <c r="AJ5" s="46"/>
+      <c r="AK5" s="46"/>
+      <c r="AL5" s="46"/>
+      <c r="AM5" s="46"/>
+      <c r="AN5" s="46"/>
+      <c r="AO5" s="46"/>
+      <c r="AP5" s="46"/>
+      <c r="AQ5" s="46"/>
       <c r="AR5" s="14"/>
       <c r="AS5" s="14"/>
     </row>
@@ -3501,31 +3327,31 @@
       <c r="T6" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="U6" s="51" t="s">
+      <c r="U6" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="51"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="52"/>
-      <c r="AD6" s="52"/>
-      <c r="AE6" s="52"/>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="52"/>
-      <c r="AH6" s="52"/>
-      <c r="AI6" s="52"/>
-      <c r="AJ6" s="52"/>
-      <c r="AK6" s="52"/>
-      <c r="AL6" s="52"/>
-      <c r="AM6" s="52"/>
-      <c r="AN6" s="52"/>
-      <c r="AO6" s="52"/>
-      <c r="AP6" s="52"/>
-      <c r="AQ6" s="52"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
+      <c r="Z6" s="45"/>
+      <c r="AA6" s="45"/>
+      <c r="AB6" s="45"/>
+      <c r="AC6" s="46"/>
+      <c r="AD6" s="46"/>
+      <c r="AE6" s="46"/>
+      <c r="AF6" s="46"/>
+      <c r="AG6" s="46"/>
+      <c r="AH6" s="46"/>
+      <c r="AI6" s="46"/>
+      <c r="AJ6" s="46"/>
+      <c r="AK6" s="46"/>
+      <c r="AL6" s="46"/>
+      <c r="AM6" s="46"/>
+      <c r="AN6" s="46"/>
+      <c r="AO6" s="46"/>
+      <c r="AP6" s="46"/>
+      <c r="AQ6" s="46"/>
       <c r="AR6" s="14"/>
       <c r="AS6" s="14"/>
     </row>
@@ -3588,31 +3414,31 @@
       <c r="T7" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="U7" s="51" t="s">
+      <c r="U7" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="51"/>
-      <c r="AE7" s="51"/>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
-      <c r="AI7" s="51"/>
-      <c r="AJ7" s="51"/>
-      <c r="AK7" s="51"/>
-      <c r="AL7" s="51"/>
-      <c r="AM7" s="51"/>
-      <c r="AN7" s="51"/>
-      <c r="AO7" s="51"/>
-      <c r="AP7" s="51"/>
-      <c r="AQ7" s="51"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="45"/>
+      <c r="Y7" s="45"/>
+      <c r="Z7" s="45"/>
+      <c r="AA7" s="45"/>
+      <c r="AB7" s="45"/>
+      <c r="AC7" s="45"/>
+      <c r="AD7" s="45"/>
+      <c r="AE7" s="45"/>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="45"/>
+      <c r="AH7" s="45"/>
+      <c r="AI7" s="45"/>
+      <c r="AJ7" s="45"/>
+      <c r="AK7" s="45"/>
+      <c r="AL7" s="45"/>
+      <c r="AM7" s="45"/>
+      <c r="AN7" s="45"/>
+      <c r="AO7" s="45"/>
+      <c r="AP7" s="45"/>
+      <c r="AQ7" s="45"/>
       <c r="AR7" s="14"/>
       <c r="AS7" s="14"/>
     </row>
@@ -3675,35 +3501,35 @@
       <c r="T8" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="U8" s="51" t="s">
+      <c r="U8" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="V8" s="51" t="s">
+      <c r="V8" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="W8" s="51" t="s">
+      <c r="W8" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="51"/>
-      <c r="AI8" s="51"/>
-      <c r="AJ8" s="51"/>
-      <c r="AK8" s="51"/>
-      <c r="AL8" s="51"/>
-      <c r="AM8" s="51"/>
-      <c r="AN8" s="51"/>
-      <c r="AO8" s="51"/>
-      <c r="AP8" s="51"/>
-      <c r="AQ8" s="51"/>
+      <c r="X8" s="45"/>
+      <c r="Y8" s="45"/>
+      <c r="Z8" s="45"/>
+      <c r="AA8" s="45"/>
+      <c r="AB8" s="45"/>
+      <c r="AC8" s="45"/>
+      <c r="AD8" s="45"/>
+      <c r="AE8" s="45"/>
+      <c r="AF8" s="45"/>
+      <c r="AG8" s="45"/>
+      <c r="AH8" s="45"/>
+      <c r="AI8" s="45"/>
+      <c r="AJ8" s="45"/>
+      <c r="AK8" s="45"/>
+      <c r="AL8" s="45"/>
+      <c r="AM8" s="45"/>
+      <c r="AN8" s="45"/>
+      <c r="AO8" s="45"/>
+      <c r="AP8" s="45"/>
+      <c r="AQ8" s="45"/>
       <c r="AR8" s="14"/>
       <c r="AS8" s="14"/>
     </row>
@@ -3766,31 +3592,31 @@
       <c r="T9" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="U9" s="51" t="s">
+      <c r="U9" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="52"/>
-      <c r="AD9" s="52"/>
-      <c r="AE9" s="52"/>
-      <c r="AF9" s="52"/>
-      <c r="AG9" s="52"/>
-      <c r="AH9" s="52"/>
-      <c r="AI9" s="52"/>
-      <c r="AJ9" s="52"/>
-      <c r="AK9" s="52"/>
-      <c r="AL9" s="52"/>
-      <c r="AM9" s="52"/>
-      <c r="AN9" s="52"/>
-      <c r="AO9" s="52"/>
-      <c r="AP9" s="52"/>
-      <c r="AQ9" s="52"/>
+      <c r="V9" s="45"/>
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="45"/>
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="46"/>
+      <c r="AD9" s="46"/>
+      <c r="AE9" s="46"/>
+      <c r="AF9" s="46"/>
+      <c r="AG9" s="46"/>
+      <c r="AH9" s="46"/>
+      <c r="AI9" s="46"/>
+      <c r="AJ9" s="46"/>
+      <c r="AK9" s="46"/>
+      <c r="AL9" s="46"/>
+      <c r="AM9" s="46"/>
+      <c r="AN9" s="46"/>
+      <c r="AO9" s="46"/>
+      <c r="AP9" s="46"/>
+      <c r="AQ9" s="46"/>
       <c r="AR9" s="14"/>
       <c r="AS9" s="14"/>
     </row>
@@ -3853,31 +3679,31 @@
       <c r="T10" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="U10" s="51" t="s">
+      <c r="U10" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="51"/>
-      <c r="Z10" s="51"/>
-      <c r="AA10" s="51"/>
-      <c r="AB10" s="51"/>
-      <c r="AC10" s="52"/>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="52"/>
-      <c r="AF10" s="52"/>
-      <c r="AG10" s="52"/>
-      <c r="AH10" s="52"/>
-      <c r="AI10" s="52"/>
-      <c r="AJ10" s="52"/>
-      <c r="AK10" s="52"/>
-      <c r="AL10" s="52"/>
-      <c r="AM10" s="52"/>
-      <c r="AN10" s="52"/>
-      <c r="AO10" s="52"/>
-      <c r="AP10" s="52"/>
-      <c r="AQ10" s="52"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="45"/>
+      <c r="X10" s="45"/>
+      <c r="Y10" s="45"/>
+      <c r="Z10" s="45"/>
+      <c r="AA10" s="45"/>
+      <c r="AB10" s="45"/>
+      <c r="AC10" s="46"/>
+      <c r="AD10" s="46"/>
+      <c r="AE10" s="46"/>
+      <c r="AF10" s="46"/>
+      <c r="AG10" s="46"/>
+      <c r="AH10" s="46"/>
+      <c r="AI10" s="46"/>
+      <c r="AJ10" s="46"/>
+      <c r="AK10" s="46"/>
+      <c r="AL10" s="46"/>
+      <c r="AM10" s="46"/>
+      <c r="AN10" s="46"/>
+      <c r="AO10" s="46"/>
+      <c r="AP10" s="46"/>
+      <c r="AQ10" s="46"/>
       <c r="AR10" s="14"/>
       <c r="AS10" s="14"/>
     </row>
@@ -3940,31 +3766,31 @@
       <c r="T11" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="U11" s="51" t="s">
+      <c r="U11" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="51"/>
-      <c r="AA11" s="51"/>
-      <c r="AB11" s="51"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52"/>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="52"/>
-      <c r="AL11" s="52"/>
-      <c r="AM11" s="52"/>
-      <c r="AN11" s="52"/>
-      <c r="AO11" s="52"/>
-      <c r="AP11" s="52"/>
-      <c r="AQ11" s="52"/>
+      <c r="V11" s="45"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="45"/>
+      <c r="Y11" s="45"/>
+      <c r="Z11" s="45"/>
+      <c r="AA11" s="45"/>
+      <c r="AB11" s="45"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="46"/>
+      <c r="AM11" s="46"/>
+      <c r="AN11" s="46"/>
+      <c r="AO11" s="46"/>
+      <c r="AP11" s="46"/>
+      <c r="AQ11" s="46"/>
       <c r="AR11" s="14"/>
       <c r="AS11" s="14"/>
     </row>
@@ -4027,31 +3853,31 @@
       <c r="T12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="U12" s="51" t="s">
+      <c r="U12" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="51"/>
-      <c r="AA12" s="51"/>
-      <c r="AB12" s="51"/>
-      <c r="AC12" s="52"/>
-      <c r="AD12" s="52"/>
-      <c r="AE12" s="52"/>
-      <c r="AF12" s="52"/>
-      <c r="AG12" s="52"/>
-      <c r="AH12" s="52"/>
-      <c r="AI12" s="52"/>
-      <c r="AJ12" s="52"/>
-      <c r="AK12" s="52"/>
-      <c r="AL12" s="52"/>
-      <c r="AM12" s="52"/>
-      <c r="AN12" s="52"/>
-      <c r="AO12" s="52"/>
-      <c r="AP12" s="52"/>
-      <c r="AQ12" s="52"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="46"/>
+      <c r="AD12" s="46"/>
+      <c r="AE12" s="46"/>
+      <c r="AF12" s="46"/>
+      <c r="AG12" s="46"/>
+      <c r="AH12" s="46"/>
+      <c r="AI12" s="46"/>
+      <c r="AJ12" s="46"/>
+      <c r="AK12" s="46"/>
+      <c r="AL12" s="46"/>
+      <c r="AM12" s="46"/>
+      <c r="AN12" s="46"/>
+      <c r="AO12" s="46"/>
+      <c r="AP12" s="46"/>
+      <c r="AQ12" s="46"/>
       <c r="AR12" s="14"/>
       <c r="AS12" s="14"/>
     </row>
@@ -4114,33 +3940,33 @@
       <c r="T13" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="U13" s="51" t="s">
+      <c r="U13" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="V13" s="51" t="s">
+      <c r="V13" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="W13" s="51"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="51"/>
-      <c r="AA13" s="51"/>
-      <c r="AB13" s="51"/>
-      <c r="AC13" s="52"/>
-      <c r="AD13" s="52"/>
-      <c r="AE13" s="52"/>
-      <c r="AF13" s="52"/>
-      <c r="AG13" s="52"/>
-      <c r="AH13" s="52"/>
-      <c r="AI13" s="52"/>
-      <c r="AJ13" s="52"/>
-      <c r="AK13" s="52"/>
-      <c r="AL13" s="52"/>
-      <c r="AM13" s="52"/>
-      <c r="AN13" s="52"/>
-      <c r="AO13" s="52"/>
-      <c r="AP13" s="52"/>
-      <c r="AQ13" s="52"/>
+      <c r="W13" s="45"/>
+      <c r="X13" s="45"/>
+      <c r="Y13" s="45"/>
+      <c r="Z13" s="45"/>
+      <c r="AA13" s="45"/>
+      <c r="AB13" s="45"/>
+      <c r="AC13" s="46"/>
+      <c r="AD13" s="46"/>
+      <c r="AE13" s="46"/>
+      <c r="AF13" s="46"/>
+      <c r="AG13" s="46"/>
+      <c r="AH13" s="46"/>
+      <c r="AI13" s="46"/>
+      <c r="AJ13" s="46"/>
+      <c r="AK13" s="46"/>
+      <c r="AL13" s="46"/>
+      <c r="AM13" s="46"/>
+      <c r="AN13" s="46"/>
+      <c r="AO13" s="46"/>
+      <c r="AP13" s="46"/>
+      <c r="AQ13" s="46"/>
       <c r="AR13" s="14"/>
       <c r="AS13" s="14"/>
     </row>
@@ -4203,45 +4029,45 @@
       <c r="T14" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="U14" s="51" t="s">
+      <c r="U14" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="V14" s="51" t="s">
+      <c r="V14" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="W14" s="51" t="s">
+      <c r="W14" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="X14" s="51" t="s">
+      <c r="X14" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="Y14" s="51" t="s">
+      <c r="Y14" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="Z14" s="51" t="s">
+      <c r="Z14" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="AA14" s="51" t="s">
+      <c r="AA14" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="AB14" s="51" t="s">
+      <c r="AB14" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="AC14" s="52"/>
-      <c r="AD14" s="52"/>
-      <c r="AE14" s="52"/>
-      <c r="AF14" s="52"/>
-      <c r="AG14" s="52"/>
-      <c r="AH14" s="52"/>
-      <c r="AI14" s="52"/>
-      <c r="AJ14" s="52"/>
-      <c r="AK14" s="52"/>
-      <c r="AL14" s="52"/>
-      <c r="AM14" s="52"/>
-      <c r="AN14" s="52"/>
-      <c r="AO14" s="52"/>
-      <c r="AP14" s="52"/>
-      <c r="AQ14" s="52"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="46"/>
+      <c r="AE14" s="46"/>
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="46"/>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="46"/>
+      <c r="AJ14" s="46"/>
+      <c r="AK14" s="46"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="46"/>
+      <c r="AN14" s="46"/>
+      <c r="AO14" s="46"/>
+      <c r="AP14" s="46"/>
+      <c r="AQ14" s="46"/>
       <c r="AR14" s="14"/>
       <c r="AS14" s="14"/>
     </row>
@@ -4304,38 +4130,38 @@
       <c r="T15" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="U15" s="51" t="s">
+      <c r="U15" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="V15" s="51" t="s">
+      <c r="V15" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="W15" s="51"/>
-      <c r="X15" s="51"/>
-      <c r="Y15" s="51"/>
-      <c r="Z15" s="51"/>
-      <c r="AA15" s="51"/>
-      <c r="AB15" s="51"/>
-      <c r="AC15" s="52"/>
-      <c r="AD15" s="52"/>
-      <c r="AE15" s="52"/>
-      <c r="AF15" s="52"/>
-      <c r="AG15" s="52"/>
-      <c r="AH15" s="52"/>
-      <c r="AI15" s="52"/>
-      <c r="AJ15" s="52"/>
-      <c r="AK15" s="52"/>
-      <c r="AL15" s="52"/>
-      <c r="AM15" s="52"/>
-      <c r="AN15" s="52"/>
-      <c r="AO15" s="52"/>
-      <c r="AP15" s="52"/>
-      <c r="AQ15" s="52"/>
+      <c r="W15" s="45"/>
+      <c r="X15" s="45"/>
+      <c r="Y15" s="45"/>
+      <c r="Z15" s="45"/>
+      <c r="AA15" s="45"/>
+      <c r="AB15" s="45"/>
+      <c r="AC15" s="46"/>
+      <c r="AD15" s="46"/>
+      <c r="AE15" s="46"/>
+      <c r="AF15" s="46"/>
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="46"/>
+      <c r="AI15" s="46"/>
+      <c r="AJ15" s="46"/>
+      <c r="AK15" s="46"/>
+      <c r="AL15" s="46"/>
+      <c r="AM15" s="46"/>
+      <c r="AN15" s="46"/>
+      <c r="AO15" s="46"/>
+      <c r="AP15" s="46"/>
+      <c r="AQ15" s="46"/>
       <c r="AR15" s="14"/>
       <c r="AS15" s="14"/>
     </row>
     <row r="16" spans="1:45" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="129" t="s">
         <v>128</v>
       </c>
       <c r="B16" s="36"/>
@@ -4355,50 +4181,43 @@
         <f>SUM(L5:L15)</f>
         <v>235243651.91</v>
       </c>
-      <c r="M16" s="38" t="s">
+      <c r="M16" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="39"/>
-      <c r="S16" s="39"/>
-      <c r="T16" s="39"/>
-      <c r="U16" s="39"/>
-      <c r="V16" s="39"/>
-      <c r="W16" s="39"/>
-      <c r="X16" s="39"/>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="39"/>
-      <c r="AA16" s="39"/>
-      <c r="AB16" s="39"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="39"/>
-      <c r="AE16" s="39"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="39"/>
-      <c r="AH16" s="39"/>
-      <c r="AI16" s="39"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="39"/>
-      <c r="AL16" s="39"/>
-      <c r="AM16" s="39"/>
-      <c r="AN16" s="39"/>
-      <c r="AO16" s="39"/>
-      <c r="AP16" s="39"/>
-      <c r="AQ16" s="39"/>
+      <c r="N16" s="127"/>
+      <c r="O16" s="127"/>
+      <c r="P16" s="127"/>
+      <c r="Q16" s="127"/>
+      <c r="R16" s="127"/>
+      <c r="S16" s="127"/>
+      <c r="T16" s="127"/>
+      <c r="U16" s="127"/>
+      <c r="V16" s="127"/>
+      <c r="W16" s="127"/>
+      <c r="X16" s="127"/>
+      <c r="Y16" s="127"/>
+      <c r="Z16" s="127"/>
+      <c r="AA16" s="127"/>
+      <c r="AB16" s="127"/>
+      <c r="AC16" s="127"/>
+      <c r="AD16" s="127"/>
+      <c r="AE16" s="127"/>
+      <c r="AF16" s="127"/>
+      <c r="AG16" s="127"/>
+      <c r="AH16" s="127"/>
+      <c r="AI16" s="127"/>
+      <c r="AJ16" s="127"/>
+      <c r="AK16" s="127"/>
+      <c r="AL16" s="127"/>
+      <c r="AM16" s="127"/>
+      <c r="AN16" s="127"/>
+      <c r="AO16" s="127"/>
+      <c r="AP16" s="127"/>
+      <c r="AQ16" s="127"/>
       <c r="AR16" s="14"/>
       <c r="AS16" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="U3:AQ3"/>
-    <mergeCell ref="A4:AQ4"/>
-    <mergeCell ref="M16:AQ16"/>
-    <mergeCell ref="A1:T2"/>
-    <mergeCell ref="A16:D16"/>
-  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -4408,91 +4227,91 @@
   <dimension ref="A1:AS24"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="56" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="56" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="56" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="56" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="56" customWidth="1"/>
-    <col min="10" max="10" width="15" style="56" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="56" customWidth="1"/>
-    <col min="12" max="12" width="25.5703125" style="56" customWidth="1"/>
-    <col min="13" max="13" width="10" style="56" customWidth="1"/>
-    <col min="14" max="14" width="15" style="56" customWidth="1"/>
-    <col min="15" max="15" width="8" style="56" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" style="56" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="56"/>
-    <col min="18" max="18" width="39.5703125" style="56" customWidth="1"/>
-    <col min="19" max="19" width="51" style="56" customWidth="1"/>
-    <col min="20" max="20" width="42.5703125" style="56" customWidth="1"/>
-    <col min="21" max="21" width="18" style="56" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="17.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="17.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18" style="56" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="17" style="56" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17" style="56" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17" style="56" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="14.42578125" style="56"/>
+    <col min="1" max="1" width="4.28515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="50" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" style="50" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="50" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="50" customWidth="1"/>
+    <col min="10" max="10" width="15" style="50" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="50" customWidth="1"/>
+    <col min="12" max="12" width="25.5703125" style="50" customWidth="1"/>
+    <col min="13" max="13" width="10" style="50" customWidth="1"/>
+    <col min="14" max="14" width="15" style="50" customWidth="1"/>
+    <col min="15" max="15" width="8" style="50" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" style="50" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="50"/>
+    <col min="18" max="18" width="39.5703125" style="50" customWidth="1"/>
+    <col min="19" max="19" width="51" style="50" customWidth="1"/>
+    <col min="20" max="20" width="42.5703125" style="50" customWidth="1"/>
+    <col min="21" max="21" width="18" style="50" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18" style="50" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="17.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18" style="50" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="17" style="50" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17" style="50" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17" style="50" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="14.42578125" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:45" ht="15" customHeight="1">
+      <c r="A1" s="47" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="55"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="49"/>
     </row>
     <row r="2" spans="1:45">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="59"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="53"/>
     </row>
     <row r="3" spans="1:45" ht="45">
       <c r="A3" s="4" t="s">
@@ -4555,80 +4374,80 @@
       <c r="T3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="40" t="s">
+      <c r="U3" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
       <c r="AR3" s="15"/>
       <c r="AS3" s="15"/>
     </row>
-    <row r="4" spans="1:45">
-      <c r="A4" s="60" t="s">
+    <row r="4" spans="1:45" ht="15" customHeight="1">
+      <c r="A4" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
-      <c r="V4" s="61"/>
-      <c r="W4" s="61"/>
-      <c r="X4" s="61"/>
-      <c r="Y4" s="61"/>
-      <c r="Z4" s="61"/>
-      <c r="AA4" s="61"/>
-      <c r="AB4" s="61"/>
-      <c r="AC4" s="61"/>
-      <c r="AD4" s="61"/>
-      <c r="AE4" s="61"/>
-      <c r="AF4" s="61"/>
-      <c r="AG4" s="61"/>
-      <c r="AH4" s="61"/>
-      <c r="AI4" s="61"/>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="61"/>
-      <c r="AM4" s="61"/>
-      <c r="AN4" s="61"/>
-      <c r="AO4" s="61"/>
-      <c r="AP4" s="61"/>
-      <c r="AQ4" s="61"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="55"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="55"/>
+      <c r="AH4" s="55"/>
+      <c r="AI4" s="55"/>
+      <c r="AJ4" s="55"/>
+      <c r="AK4" s="55"/>
+      <c r="AL4" s="55"/>
+      <c r="AM4" s="55"/>
+      <c r="AN4" s="55"/>
+      <c r="AO4" s="55"/>
+      <c r="AP4" s="55"/>
+      <c r="AQ4" s="55"/>
     </row>
     <row r="5" spans="1:45" ht="60">
       <c r="A5" s="7">
@@ -4691,41 +4510,41 @@
       <c r="T5" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="U5" s="62" t="s">
+      <c r="U5" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="V5" s="62" t="s">
+      <c r="V5" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="W5" s="62" t="s">
+      <c r="W5" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="X5" s="62" t="s">
+      <c r="X5" s="56" t="s">
         <v>260</v>
       </c>
-      <c r="Y5" s="62" t="s">
+      <c r="Y5" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="Z5" s="62" t="s">
+      <c r="Z5" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="AA5" s="62"/>
-      <c r="AB5" s="62"/>
-      <c r="AC5" s="62"/>
-      <c r="AD5" s="62"/>
-      <c r="AE5" s="62"/>
-      <c r="AF5" s="62"/>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="62"/>
-      <c r="AI5" s="62"/>
-      <c r="AJ5" s="62"/>
-      <c r="AK5" s="62"/>
-      <c r="AL5" s="62"/>
-      <c r="AM5" s="62"/>
-      <c r="AN5" s="62"/>
-      <c r="AO5" s="62"/>
-      <c r="AP5" s="62"/>
-      <c r="AQ5" s="62"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="56"/>
+      <c r="AI5" s="56"/>
+      <c r="AJ5" s="56"/>
+      <c r="AK5" s="56"/>
+      <c r="AL5" s="56"/>
+      <c r="AM5" s="56"/>
+      <c r="AN5" s="56"/>
+      <c r="AO5" s="56"/>
+      <c r="AP5" s="56"/>
+      <c r="AQ5" s="56"/>
     </row>
     <row r="6" spans="1:45" ht="60">
       <c r="A6" s="7">
@@ -4788,37 +4607,37 @@
       <c r="T6" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="U6" s="62" t="s">
+      <c r="U6" s="56" t="s">
         <v>263</v>
       </c>
-      <c r="V6" s="62" t="s">
+      <c r="V6" s="56" t="s">
         <v>264</v>
       </c>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="62"/>
-      <c r="AB6" s="62"/>
-      <c r="AC6" s="62"/>
-      <c r="AD6" s="62"/>
-      <c r="AE6" s="62"/>
-      <c r="AF6" s="62"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
-      <c r="AL6" s="62"/>
-      <c r="AM6" s="62"/>
-      <c r="AN6" s="62"/>
-      <c r="AO6" s="62"/>
-      <c r="AP6" s="62"/>
-      <c r="AQ6" s="62"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="56"/>
+      <c r="AJ6" s="56"/>
+      <c r="AK6" s="56"/>
+      <c r="AL6" s="56"/>
+      <c r="AM6" s="56"/>
+      <c r="AN6" s="56"/>
+      <c r="AO6" s="56"/>
+      <c r="AP6" s="56"/>
+      <c r="AQ6" s="56"/>
     </row>
     <row r="7" spans="1:45" ht="48.75" customHeight="1">
       <c r="A7" s="7">
-        <f t="shared" ref="A6:A23" si="0">A6+1</f>
+        <f t="shared" ref="A7:A23" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -4878,31 +4697,31 @@
       <c r="T7" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="U7" s="62" t="s">
+      <c r="U7" s="56" t="s">
         <v>265</v>
       </c>
-      <c r="V7" s="62"/>
-      <c r="W7" s="62"/>
-      <c r="X7" s="62"/>
-      <c r="Y7" s="62"/>
-      <c r="Z7" s="62"/>
-      <c r="AA7" s="62"/>
-      <c r="AB7" s="62"/>
-      <c r="AC7" s="62"/>
-      <c r="AD7" s="62"/>
-      <c r="AE7" s="62"/>
-      <c r="AF7" s="62"/>
-      <c r="AG7" s="62"/>
-      <c r="AH7" s="62"/>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="62"/>
-      <c r="AL7" s="62"/>
-      <c r="AM7" s="62"/>
-      <c r="AN7" s="62"/>
-      <c r="AO7" s="62"/>
-      <c r="AP7" s="62"/>
-      <c r="AQ7" s="62"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="56"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="56"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="56"/>
+      <c r="AH7" s="56"/>
+      <c r="AI7" s="56"/>
+      <c r="AJ7" s="56"/>
+      <c r="AK7" s="56"/>
+      <c r="AL7" s="56"/>
+      <c r="AM7" s="56"/>
+      <c r="AN7" s="56"/>
+      <c r="AO7" s="56"/>
+      <c r="AP7" s="56"/>
+      <c r="AQ7" s="56"/>
     </row>
     <row r="8" spans="1:45" ht="48.75" customHeight="1">
       <c r="A8" s="7">
@@ -4918,7 +4737,7 @@
       <c r="D8" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="57">
         <v>47.9</v>
       </c>
       <c r="F8" s="24" t="s">
@@ -4939,7 +4758,7 @@
       <c r="K8" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="64">
+      <c r="L8" s="58">
         <v>27102187.760000002</v>
       </c>
       <c r="M8" s="7">
@@ -4964,69 +4783,69 @@
       <c r="T8" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="U8" s="62" t="s">
+      <c r="U8" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="V8" s="62" t="s">
+      <c r="V8" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="W8" s="62" t="s">
+      <c r="W8" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="X8" s="62" t="s">
+      <c r="X8" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="Y8" s="62" t="s">
+      <c r="Y8" s="56" t="s">
         <v>270</v>
       </c>
-      <c r="Z8" s="62" t="s">
+      <c r="Z8" s="56" t="s">
         <v>271</v>
       </c>
-      <c r="AA8" s="62" t="s">
+      <c r="AA8" s="56" t="s">
         <v>272</v>
       </c>
-      <c r="AB8" s="62" t="s">
+      <c r="AB8" s="56" t="s">
         <v>273</v>
       </c>
-      <c r="AC8" s="62" t="s">
+      <c r="AC8" s="56" t="s">
         <v>274</v>
       </c>
-      <c r="AD8" s="62" t="s">
+      <c r="AD8" s="56" t="s">
         <v>275</v>
       </c>
-      <c r="AE8" s="62" t="s">
+      <c r="AE8" s="56" t="s">
         <v>276</v>
       </c>
-      <c r="AF8" s="62" t="s">
+      <c r="AF8" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="AG8" s="62" t="s">
+      <c r="AG8" s="56" t="s">
         <v>278</v>
       </c>
-      <c r="AH8" s="62" t="s">
+      <c r="AH8" s="56" t="s">
         <v>279</v>
       </c>
-      <c r="AI8" s="62" t="s">
+      <c r="AI8" s="56" t="s">
         <v>280</v>
       </c>
-      <c r="AJ8" s="62" t="s">
+      <c r="AJ8" s="56" t="s">
         <v>281</v>
       </c>
-      <c r="AK8" s="62" t="s">
+      <c r="AK8" s="56" t="s">
         <v>282</v>
       </c>
-      <c r="AL8" s="62" t="s">
+      <c r="AL8" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="AM8" s="62" t="s">
+      <c r="AM8" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="AN8" s="62" t="s">
+      <c r="AN8" s="56" t="s">
         <v>285</v>
       </c>
-      <c r="AO8" s="62"/>
-      <c r="AP8" s="62"/>
-      <c r="AQ8" s="62"/>
+      <c r="AO8" s="56"/>
+      <c r="AP8" s="56"/>
+      <c r="AQ8" s="56"/>
     </row>
     <row r="9" spans="1:45" ht="48.75" customHeight="1">
       <c r="A9" s="7">
@@ -5042,7 +4861,7 @@
       <c r="D9" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="57">
         <v>0.97</v>
       </c>
       <c r="F9" s="24" t="s">
@@ -5063,7 +4882,7 @@
       <c r="K9" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="58">
         <v>2815978.8</v>
       </c>
       <c r="M9" s="7">
@@ -5090,31 +4909,31 @@
       <c r="T9" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="U9" s="62" t="s">
+      <c r="U9" s="56" t="s">
         <v>286</v>
       </c>
-      <c r="V9" s="62"/>
-      <c r="W9" s="62"/>
-      <c r="X9" s="62"/>
-      <c r="Y9" s="62"/>
-      <c r="Z9" s="62"/>
-      <c r="AA9" s="62"/>
-      <c r="AB9" s="62"/>
-      <c r="AC9" s="62"/>
-      <c r="AD9" s="62"/>
-      <c r="AE9" s="62"/>
-      <c r="AF9" s="62"/>
-      <c r="AG9" s="62"/>
-      <c r="AH9" s="62"/>
-      <c r="AI9" s="62"/>
-      <c r="AJ9" s="62"/>
-      <c r="AK9" s="62"/>
-      <c r="AL9" s="62"/>
-      <c r="AM9" s="62"/>
-      <c r="AN9" s="62"/>
-      <c r="AO9" s="62"/>
-      <c r="AP9" s="62"/>
-      <c r="AQ9" s="62"/>
+      <c r="V9" s="56"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="56"/>
+      <c r="AA9" s="56"/>
+      <c r="AB9" s="56"/>
+      <c r="AC9" s="56"/>
+      <c r="AD9" s="56"/>
+      <c r="AE9" s="56"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="56"/>
+      <c r="AH9" s="56"/>
+      <c r="AI9" s="56"/>
+      <c r="AJ9" s="56"/>
+      <c r="AK9" s="56"/>
+      <c r="AL9" s="56"/>
+      <c r="AM9" s="56"/>
+      <c r="AN9" s="56"/>
+      <c r="AO9" s="56"/>
+      <c r="AP9" s="56"/>
+      <c r="AQ9" s="56"/>
     </row>
     <row r="10" spans="1:45" ht="48.75" customHeight="1">
       <c r="A10" s="7">
@@ -5130,7 +4949,7 @@
       <c r="D10" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="57">
         <v>8.4</v>
       </c>
       <c r="F10" s="24" t="s">
@@ -5151,7 +4970,7 @@
       <c r="K10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="64">
+      <c r="L10" s="58">
         <v>31587295.43</v>
       </c>
       <c r="M10" s="7">
@@ -5178,35 +4997,35 @@
       <c r="T10" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="U10" s="62" t="s">
+      <c r="U10" s="56" t="s">
         <v>287</v>
       </c>
-      <c r="V10" s="62" t="s">
+      <c r="V10" s="56" t="s">
         <v>288</v>
       </c>
-      <c r="W10" s="62" t="s">
+      <c r="W10" s="56" t="s">
         <v>289</v>
       </c>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="62"/>
-      <c r="AA10" s="62"/>
-      <c r="AB10" s="62"/>
-      <c r="AC10" s="62"/>
-      <c r="AD10" s="62"/>
-      <c r="AE10" s="62"/>
-      <c r="AF10" s="62"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="62"/>
-      <c r="AJ10" s="62"/>
-      <c r="AK10" s="62"/>
-      <c r="AL10" s="62"/>
-      <c r="AM10" s="62"/>
-      <c r="AN10" s="62"/>
-      <c r="AO10" s="62"/>
-      <c r="AP10" s="62"/>
-      <c r="AQ10" s="62"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="56"/>
+      <c r="Z10" s="56"/>
+      <c r="AA10" s="56"/>
+      <c r="AB10" s="56"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="56"/>
+      <c r="AH10" s="56"/>
+      <c r="AI10" s="56"/>
+      <c r="AJ10" s="56"/>
+      <c r="AK10" s="56"/>
+      <c r="AL10" s="56"/>
+      <c r="AM10" s="56"/>
+      <c r="AN10" s="56"/>
+      <c r="AO10" s="56"/>
+      <c r="AP10" s="56"/>
+      <c r="AQ10" s="56"/>
     </row>
     <row r="11" spans="1:45" ht="48.75" customHeight="1">
       <c r="A11" s="7">
@@ -5222,7 +5041,7 @@
       <c r="D11" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="57">
         <v>25.1</v>
       </c>
       <c r="F11" s="24" t="s">
@@ -5243,7 +5062,7 @@
       <c r="K11" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="58">
         <v>19638413.100000001</v>
       </c>
       <c r="M11" s="7">
@@ -5268,33 +5087,33 @@
       <c r="T11" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="U11" s="62" t="s">
+      <c r="U11" s="56" t="s">
         <v>290</v>
       </c>
-      <c r="V11" s="62" t="s">
+      <c r="V11" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="W11" s="62"/>
-      <c r="X11" s="62"/>
-      <c r="Y11" s="62"/>
-      <c r="Z11" s="62"/>
-      <c r="AA11" s="62"/>
-      <c r="AB11" s="62"/>
-      <c r="AC11" s="62"/>
-      <c r="AD11" s="62"/>
-      <c r="AE11" s="62"/>
-      <c r="AF11" s="62"/>
-      <c r="AG11" s="62"/>
-      <c r="AH11" s="62"/>
-      <c r="AI11" s="62"/>
-      <c r="AJ11" s="62"/>
-      <c r="AK11" s="62"/>
-      <c r="AL11" s="62"/>
-      <c r="AM11" s="62"/>
-      <c r="AN11" s="62"/>
-      <c r="AO11" s="62"/>
-      <c r="AP11" s="62"/>
-      <c r="AQ11" s="62"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="56"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="56"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="56"/>
+      <c r="AH11" s="56"/>
+      <c r="AI11" s="56"/>
+      <c r="AJ11" s="56"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="56"/>
+      <c r="AN11" s="56"/>
+      <c r="AO11" s="56"/>
+      <c r="AP11" s="56"/>
+      <c r="AQ11" s="56"/>
     </row>
     <row r="12" spans="1:45" ht="48.75" customHeight="1">
       <c r="A12" s="7">
@@ -5310,7 +5129,7 @@
       <c r="D12" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="57">
         <v>30.34</v>
       </c>
       <c r="F12" s="24" t="s">
@@ -5331,7 +5150,7 @@
       <c r="K12" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="64">
+      <c r="L12" s="58">
         <v>22469055.489999998</v>
       </c>
       <c r="M12" s="7">
@@ -5358,31 +5177,31 @@
       <c r="T12" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="U12" s="62" t="s">
+      <c r="U12" s="56" t="s">
         <v>292</v>
       </c>
-      <c r="V12" s="62"/>
-      <c r="W12" s="62"/>
-      <c r="X12" s="62"/>
-      <c r="Y12" s="62"/>
-      <c r="Z12" s="62"/>
-      <c r="AA12" s="62"/>
-      <c r="AB12" s="62"/>
-      <c r="AC12" s="62"/>
-      <c r="AD12" s="62"/>
-      <c r="AE12" s="62"/>
-      <c r="AF12" s="62"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
-      <c r="AL12" s="62"/>
-      <c r="AM12" s="62"/>
-      <c r="AN12" s="62"/>
-      <c r="AO12" s="62"/>
-      <c r="AP12" s="62"/>
-      <c r="AQ12" s="62"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="56"/>
+      <c r="Z12" s="56"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="56"/>
+      <c r="AC12" s="56"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
+      <c r="AJ12" s="56"/>
+      <c r="AK12" s="56"/>
+      <c r="AL12" s="56"/>
+      <c r="AM12" s="56"/>
+      <c r="AN12" s="56"/>
+      <c r="AO12" s="56"/>
+      <c r="AP12" s="56"/>
+      <c r="AQ12" s="56"/>
     </row>
     <row r="13" spans="1:45" ht="48.75" customHeight="1">
       <c r="A13" s="7">
@@ -5398,7 +5217,7 @@
       <c r="D13" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="57" t="s">
         <v>129</v>
       </c>
       <c r="F13" s="24" t="s">
@@ -5419,7 +5238,7 @@
       <c r="K13" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="64">
+      <c r="L13" s="58">
         <v>3014653.83</v>
       </c>
       <c r="M13" s="7">
@@ -5443,34 +5262,34 @@
       <c r="S13" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="T13" s="65"/>
-      <c r="U13" s="62" t="s">
+      <c r="T13" s="59"/>
+      <c r="U13" s="56" t="s">
         <v>255</v>
       </c>
-      <c r="V13" s="62" t="s">
+      <c r="V13" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="W13" s="62"/>
-      <c r="X13" s="62"/>
-      <c r="Y13" s="62"/>
-      <c r="Z13" s="62"/>
-      <c r="AA13" s="62"/>
-      <c r="AB13" s="62"/>
-      <c r="AC13" s="62"/>
-      <c r="AD13" s="62"/>
-      <c r="AE13" s="62"/>
-      <c r="AF13" s="62"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="62"/>
-      <c r="AJ13" s="62"/>
-      <c r="AK13" s="62"/>
-      <c r="AL13" s="62"/>
-      <c r="AM13" s="62"/>
-      <c r="AN13" s="62"/>
-      <c r="AO13" s="62"/>
-      <c r="AP13" s="62"/>
-      <c r="AQ13" s="62"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="56"/>
+      <c r="Y13" s="56"/>
+      <c r="Z13" s="56"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="56"/>
+      <c r="AC13" s="56"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="56"/>
+      <c r="AH13" s="56"/>
+      <c r="AI13" s="56"/>
+      <c r="AJ13" s="56"/>
+      <c r="AK13" s="56"/>
+      <c r="AL13" s="56"/>
+      <c r="AM13" s="56"/>
+      <c r="AN13" s="56"/>
+      <c r="AO13" s="56"/>
+      <c r="AP13" s="56"/>
+      <c r="AQ13" s="56"/>
     </row>
     <row r="14" spans="1:45" ht="48.75" customHeight="1">
       <c r="A14" s="7">
@@ -5486,7 +5305,7 @@
       <c r="D14" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="57">
         <v>16.600000000000001</v>
       </c>
       <c r="F14" s="24" t="s">
@@ -5507,7 +5326,7 @@
       <c r="K14" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="64">
+      <c r="L14" s="58">
         <v>14394574.65</v>
       </c>
       <c r="M14" s="7">
@@ -5534,31 +5353,31 @@
       <c r="T14" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="U14" s="62" t="s">
+      <c r="U14" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="V14" s="62"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="62"/>
-      <c r="AB14" s="62"/>
-      <c r="AC14" s="62"/>
-      <c r="AD14" s="62"/>
-      <c r="AE14" s="62"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="62"/>
-      <c r="AM14" s="62"/>
-      <c r="AN14" s="62"/>
-      <c r="AO14" s="62"/>
-      <c r="AP14" s="62"/>
-      <c r="AQ14" s="62"/>
+      <c r="V14" s="56"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="56"/>
+      <c r="Y14" s="56"/>
+      <c r="Z14" s="56"/>
+      <c r="AA14" s="56"/>
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="56"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="56"/>
+      <c r="AM14" s="56"/>
+      <c r="AN14" s="56"/>
+      <c r="AO14" s="56"/>
+      <c r="AP14" s="56"/>
+      <c r="AQ14" s="56"/>
     </row>
     <row r="15" spans="1:45" ht="48.75" customHeight="1">
       <c r="A15" s="7">
@@ -5574,7 +5393,7 @@
       <c r="D15" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E15" s="57">
         <v>5.86</v>
       </c>
       <c r="F15" s="24" t="s">
@@ -5595,7 +5414,7 @@
       <c r="K15" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="64">
+      <c r="L15" s="58">
         <v>4965906.38</v>
       </c>
       <c r="M15" s="7">
@@ -5622,33 +5441,33 @@
       <c r="T15" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="U15" s="62" t="s">
+      <c r="U15" s="56" t="s">
         <v>294</v>
       </c>
-      <c r="V15" s="62" t="s">
+      <c r="V15" s="56" t="s">
         <v>295</v>
       </c>
-      <c r="W15" s="62"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62"/>
-      <c r="Z15" s="62"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="62"/>
-      <c r="AC15" s="62"/>
-      <c r="AD15" s="62"/>
-      <c r="AE15" s="62"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="62"/>
-      <c r="AM15" s="62"/>
-      <c r="AN15" s="62"/>
-      <c r="AO15" s="62"/>
-      <c r="AP15" s="62"/>
-      <c r="AQ15" s="62"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="56"/>
+      <c r="Z15" s="56"/>
+      <c r="AA15" s="56"/>
+      <c r="AB15" s="56"/>
+      <c r="AC15" s="56"/>
+      <c r="AD15" s="56"/>
+      <c r="AE15" s="56"/>
+      <c r="AF15" s="56"/>
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="56"/>
+      <c r="AI15" s="56"/>
+      <c r="AJ15" s="56"/>
+      <c r="AK15" s="56"/>
+      <c r="AL15" s="56"/>
+      <c r="AM15" s="56"/>
+      <c r="AN15" s="56"/>
+      <c r="AO15" s="56"/>
+      <c r="AP15" s="56"/>
+      <c r="AQ15" s="56"/>
     </row>
     <row r="16" spans="1:45" ht="48.75" customHeight="1">
       <c r="A16" s="7">
@@ -5664,7 +5483,7 @@
       <c r="D16" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="57">
         <v>16.82</v>
       </c>
       <c r="F16" s="24" t="s">
@@ -5685,7 +5504,7 @@
       <c r="K16" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="64">
+      <c r="L16" s="58">
         <v>8303874.0599999996</v>
       </c>
       <c r="M16" s="7">
@@ -5712,31 +5531,31 @@
       <c r="T16" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="U16" s="62" t="s">
+      <c r="U16" s="56" t="s">
         <v>296</v>
       </c>
-      <c r="V16" s="62"/>
-      <c r="W16" s="62"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="62"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
-      <c r="AL16" s="62"/>
-      <c r="AM16" s="62"/>
-      <c r="AN16" s="62"/>
-      <c r="AO16" s="62"/>
-      <c r="AP16" s="62"/>
-      <c r="AQ16" s="62"/>
+      <c r="V16" s="56"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="56"/>
+      <c r="Y16" s="56"/>
+      <c r="Z16" s="56"/>
+      <c r="AA16" s="56"/>
+      <c r="AB16" s="56"/>
+      <c r="AC16" s="56"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="56"/>
+      <c r="AF16" s="56"/>
+      <c r="AG16" s="56"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="56"/>
+      <c r="AJ16" s="56"/>
+      <c r="AK16" s="56"/>
+      <c r="AL16" s="56"/>
+      <c r="AM16" s="56"/>
+      <c r="AN16" s="56"/>
+      <c r="AO16" s="56"/>
+      <c r="AP16" s="56"/>
+      <c r="AQ16" s="56"/>
     </row>
     <row r="17" spans="1:45" ht="48.75" customHeight="1">
       <c r="A17" s="7">
@@ -5753,7 +5572,7 @@
         <f>UPPER("Iluminação do Acesso ao Geossítio Cachoeira ")</f>
         <v xml:space="preserve">ILUMINAÇÃO DO ACESSO AO GEOSSÍTIO CACHOEIRA </v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="57" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="24" t="s">
@@ -5774,7 +5593,7 @@
       <c r="K17" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="64">
+      <c r="L17" s="58">
         <v>524070.01</v>
       </c>
       <c r="M17" s="7">
@@ -5797,31 +5616,31 @@
       </c>
       <c r="S17" s="24"/>
       <c r="T17" s="34"/>
-      <c r="U17" s="62" t="s">
+      <c r="U17" s="56" t="s">
         <v>297</v>
       </c>
-      <c r="V17" s="62"/>
-      <c r="W17" s="62"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
-      <c r="Z17" s="62"/>
-      <c r="AA17" s="62"/>
-      <c r="AB17" s="62"/>
-      <c r="AC17" s="62"/>
-      <c r="AD17" s="62"/>
-      <c r="AE17" s="62"/>
-      <c r="AF17" s="62"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="62"/>
-      <c r="AK17" s="62"/>
-      <c r="AL17" s="62"/>
-      <c r="AM17" s="62"/>
-      <c r="AN17" s="62"/>
-      <c r="AO17" s="62"/>
-      <c r="AP17" s="62"/>
-      <c r="AQ17" s="62"/>
+      <c r="V17" s="56"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="56"/>
+      <c r="Z17" s="56"/>
+      <c r="AA17" s="56"/>
+      <c r="AB17" s="56"/>
+      <c r="AC17" s="56"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="56"/>
+      <c r="AF17" s="56"/>
+      <c r="AG17" s="56"/>
+      <c r="AH17" s="56"/>
+      <c r="AI17" s="56"/>
+      <c r="AJ17" s="56"/>
+      <c r="AK17" s="56"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="56"/>
+      <c r="AN17" s="56"/>
+      <c r="AO17" s="56"/>
+      <c r="AP17" s="56"/>
+      <c r="AQ17" s="56"/>
     </row>
     <row r="18" spans="1:45" ht="48.75" customHeight="1">
       <c r="A18" s="7">
@@ -5837,7 +5656,7 @@
       <c r="D18" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E18" s="57">
         <v>4.7</v>
       </c>
       <c r="F18" s="24" t="s">
@@ -5858,7 +5677,7 @@
       <c r="K18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="64">
+      <c r="L18" s="58">
         <v>25687719.870000001</v>
       </c>
       <c r="M18" s="7">
@@ -5885,33 +5704,33 @@
       <c r="T18" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="U18" s="62" t="s">
+      <c r="U18" s="56" t="s">
         <v>298</v>
       </c>
-      <c r="V18" s="62" t="s">
+      <c r="V18" s="56" t="s">
         <v>299</v>
       </c>
-      <c r="W18" s="62"/>
-      <c r="X18" s="62"/>
-      <c r="Y18" s="62"/>
-      <c r="Z18" s="62"/>
-      <c r="AA18" s="62"/>
-      <c r="AB18" s="62"/>
-      <c r="AC18" s="62"/>
-      <c r="AD18" s="62"/>
-      <c r="AE18" s="62"/>
-      <c r="AF18" s="62"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="62"/>
-      <c r="AK18" s="62"/>
-      <c r="AL18" s="62"/>
-      <c r="AM18" s="62"/>
-      <c r="AN18" s="62"/>
-      <c r="AO18" s="62"/>
-      <c r="AP18" s="62"/>
-      <c r="AQ18" s="62"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="56"/>
+      <c r="Y18" s="56"/>
+      <c r="Z18" s="56"/>
+      <c r="AA18" s="56"/>
+      <c r="AB18" s="56"/>
+      <c r="AC18" s="56"/>
+      <c r="AD18" s="56"/>
+      <c r="AE18" s="56"/>
+      <c r="AF18" s="56"/>
+      <c r="AG18" s="56"/>
+      <c r="AH18" s="56"/>
+      <c r="AI18" s="56"/>
+      <c r="AJ18" s="56"/>
+      <c r="AK18" s="56"/>
+      <c r="AL18" s="56"/>
+      <c r="AM18" s="56"/>
+      <c r="AN18" s="56"/>
+      <c r="AO18" s="56"/>
+      <c r="AP18" s="56"/>
+      <c r="AQ18" s="56"/>
     </row>
     <row r="19" spans="1:45" ht="48.75" customHeight="1">
       <c r="A19" s="7">
@@ -5927,7 +5746,7 @@
       <c r="D19" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="63">
+      <c r="E19" s="57">
         <v>2.6</v>
       </c>
       <c r="F19" s="24" t="s">
@@ -5948,7 +5767,7 @@
       <c r="K19" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="66">
+      <c r="L19" s="60">
         <v>8203250.1699999999</v>
       </c>
       <c r="M19" s="7">
@@ -5975,31 +5794,31 @@
       <c r="T19" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="U19" s="62" t="s">
+      <c r="U19" s="56" t="s">
         <v>300</v>
       </c>
-      <c r="V19" s="62"/>
-      <c r="W19" s="62"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
-      <c r="Z19" s="62"/>
-      <c r="AA19" s="62"/>
-      <c r="AB19" s="62"/>
-      <c r="AC19" s="62"/>
-      <c r="AD19" s="62"/>
-      <c r="AE19" s="62"/>
-      <c r="AF19" s="62"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="62"/>
-      <c r="AL19" s="62"/>
-      <c r="AM19" s="62"/>
-      <c r="AN19" s="62"/>
-      <c r="AO19" s="62"/>
-      <c r="AP19" s="62"/>
-      <c r="AQ19" s="62"/>
+      <c r="V19" s="56"/>
+      <c r="W19" s="56"/>
+      <c r="X19" s="56"/>
+      <c r="Y19" s="56"/>
+      <c r="Z19" s="56"/>
+      <c r="AA19" s="56"/>
+      <c r="AB19" s="56"/>
+      <c r="AC19" s="56"/>
+      <c r="AD19" s="56"/>
+      <c r="AE19" s="56"/>
+      <c r="AF19" s="56"/>
+      <c r="AG19" s="56"/>
+      <c r="AH19" s="56"/>
+      <c r="AI19" s="56"/>
+      <c r="AJ19" s="56"/>
+      <c r="AK19" s="56"/>
+      <c r="AL19" s="56"/>
+      <c r="AM19" s="56"/>
+      <c r="AN19" s="56"/>
+      <c r="AO19" s="56"/>
+      <c r="AP19" s="56"/>
+      <c r="AQ19" s="56"/>
     </row>
     <row r="20" spans="1:45" ht="48.75" customHeight="1">
       <c r="A20" s="7">
@@ -6015,7 +5834,7 @@
       <c r="D20" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="57">
         <v>28.64</v>
       </c>
       <c r="F20" s="24" t="s">
@@ -6036,7 +5855,7 @@
       <c r="K20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L20" s="60">
         <v>21929959.289999999</v>
       </c>
       <c r="M20" s="7">
@@ -6063,33 +5882,33 @@
       <c r="T20" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="U20" s="62" t="s">
+      <c r="U20" s="56" t="s">
         <v>301</v>
       </c>
-      <c r="V20" s="62" t="s">
+      <c r="V20" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="W20" s="62"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="62"/>
-      <c r="AB20" s="62"/>
-      <c r="AC20" s="62"/>
-      <c r="AD20" s="62"/>
-      <c r="AE20" s="62"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="62"/>
-      <c r="AL20" s="62"/>
-      <c r="AM20" s="62"/>
-      <c r="AN20" s="62"/>
-      <c r="AO20" s="62"/>
-      <c r="AP20" s="62"/>
-      <c r="AQ20" s="62"/>
+      <c r="W20" s="56"/>
+      <c r="X20" s="56"/>
+      <c r="Y20" s="56"/>
+      <c r="Z20" s="56"/>
+      <c r="AA20" s="56"/>
+      <c r="AB20" s="56"/>
+      <c r="AC20" s="56"/>
+      <c r="AD20" s="56"/>
+      <c r="AE20" s="56"/>
+      <c r="AF20" s="56"/>
+      <c r="AG20" s="56"/>
+      <c r="AH20" s="56"/>
+      <c r="AI20" s="56"/>
+      <c r="AJ20" s="56"/>
+      <c r="AK20" s="56"/>
+      <c r="AL20" s="56"/>
+      <c r="AM20" s="56"/>
+      <c r="AN20" s="56"/>
+      <c r="AO20" s="56"/>
+      <c r="AP20" s="56"/>
+      <c r="AQ20" s="56"/>
     </row>
     <row r="21" spans="1:45" ht="48.75" customHeight="1">
       <c r="A21" s="7">
@@ -6105,7 +5924,7 @@
       <c r="D21" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="E21" s="63">
+      <c r="E21" s="57">
         <v>1.42</v>
       </c>
       <c r="F21" s="24" t="s">
@@ -6126,7 +5945,7 @@
       <c r="K21" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="66">
+      <c r="L21" s="60">
         <v>5521746</v>
       </c>
       <c r="M21" s="7">
@@ -6151,33 +5970,33 @@
         <v>235</v>
       </c>
       <c r="T21" s="34"/>
-      <c r="U21" s="62" t="s">
+      <c r="U21" s="56" t="s">
         <v>253</v>
       </c>
-      <c r="V21" s="62" t="s">
+      <c r="V21" s="56" t="s">
         <v>254</v>
       </c>
-      <c r="W21" s="62"/>
-      <c r="X21" s="62"/>
-      <c r="Y21" s="62"/>
-      <c r="Z21" s="62"/>
-      <c r="AA21" s="62"/>
-      <c r="AB21" s="62"/>
-      <c r="AC21" s="62"/>
-      <c r="AD21" s="62"/>
-      <c r="AE21" s="62"/>
-      <c r="AF21" s="62"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="62"/>
-      <c r="AI21" s="62"/>
-      <c r="AJ21" s="62"/>
-      <c r="AK21" s="62"/>
-      <c r="AL21" s="62"/>
-      <c r="AM21" s="62"/>
-      <c r="AN21" s="62"/>
-      <c r="AO21" s="62"/>
-      <c r="AP21" s="62"/>
-      <c r="AQ21" s="62"/>
+      <c r="W21" s="56"/>
+      <c r="X21" s="56"/>
+      <c r="Y21" s="56"/>
+      <c r="Z21" s="56"/>
+      <c r="AA21" s="56"/>
+      <c r="AB21" s="56"/>
+      <c r="AC21" s="56"/>
+      <c r="AD21" s="56"/>
+      <c r="AE21" s="56"/>
+      <c r="AF21" s="56"/>
+      <c r="AG21" s="56"/>
+      <c r="AH21" s="56"/>
+      <c r="AI21" s="56"/>
+      <c r="AJ21" s="56"/>
+      <c r="AK21" s="56"/>
+      <c r="AL21" s="56"/>
+      <c r="AM21" s="56"/>
+      <c r="AN21" s="56"/>
+      <c r="AO21" s="56"/>
+      <c r="AP21" s="56"/>
+      <c r="AQ21" s="56"/>
     </row>
     <row r="22" spans="1:45" ht="48.75" customHeight="1">
       <c r="A22" s="7">
@@ -6193,7 +6012,7 @@
       <c r="D22" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="E22" s="63">
+      <c r="E22" s="57">
         <f>220/1000</f>
         <v>0.22</v>
       </c>
@@ -6215,7 +6034,7 @@
       <c r="K22" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="66">
+      <c r="L22" s="60">
         <v>2769121.2</v>
       </c>
       <c r="M22" s="7">
@@ -6240,33 +6059,33 @@
         <v>242</v>
       </c>
       <c r="T22" s="34"/>
-      <c r="U22" s="62" t="s">
+      <c r="U22" s="56" t="s">
         <v>251</v>
       </c>
-      <c r="V22" s="62" t="s">
+      <c r="V22" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="W22" s="62"/>
-      <c r="X22" s="62"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="62"/>
-      <c r="AA22" s="62"/>
-      <c r="AB22" s="62"/>
-      <c r="AC22" s="62"/>
-      <c r="AD22" s="62"/>
-      <c r="AE22" s="62"/>
-      <c r="AF22" s="62"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="62"/>
-      <c r="AL22" s="62"/>
-      <c r="AM22" s="62"/>
-      <c r="AN22" s="62"/>
-      <c r="AO22" s="62"/>
-      <c r="AP22" s="62"/>
-      <c r="AQ22" s="62"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="56"/>
+      <c r="Y22" s="56"/>
+      <c r="Z22" s="56"/>
+      <c r="AA22" s="56"/>
+      <c r="AB22" s="56"/>
+      <c r="AC22" s="56"/>
+      <c r="AD22" s="56"/>
+      <c r="AE22" s="56"/>
+      <c r="AF22" s="56"/>
+      <c r="AG22" s="56"/>
+      <c r="AH22" s="56"/>
+      <c r="AI22" s="56"/>
+      <c r="AJ22" s="56"/>
+      <c r="AK22" s="56"/>
+      <c r="AL22" s="56"/>
+      <c r="AM22" s="56"/>
+      <c r="AN22" s="56"/>
+      <c r="AO22" s="56"/>
+      <c r="AP22" s="56"/>
+      <c r="AQ22" s="56"/>
     </row>
     <row r="23" spans="1:45" ht="60">
       <c r="A23" s="7">
@@ -6282,7 +6101,7 @@
       <c r="D23" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="E23" s="63">
+      <c r="E23" s="57">
         <v>6.57</v>
       </c>
       <c r="F23" s="24" t="s">
@@ -6303,7 +6122,7 @@
       <c r="K23" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="66">
+      <c r="L23" s="60">
         <v>47366423.520000003</v>
       </c>
       <c r="M23" s="7">
@@ -6330,42 +6149,42 @@
       <c r="T23" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="U23" s="62" t="s">
+      <c r="U23" s="56" t="s">
         <v>303</v>
       </c>
-      <c r="V23" s="62" t="s">
+      <c r="V23" s="56" t="s">
         <v>304</v>
       </c>
-      <c r="W23" s="62"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="62"/>
-      <c r="Z23" s="62"/>
-      <c r="AA23" s="62"/>
-      <c r="AB23" s="62"/>
-      <c r="AC23" s="62"/>
-      <c r="AD23" s="62"/>
-      <c r="AE23" s="62"/>
-      <c r="AF23" s="62"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62"/>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="62"/>
-      <c r="AL23" s="62"/>
-      <c r="AM23" s="62"/>
-      <c r="AN23" s="62"/>
-      <c r="AO23" s="62"/>
-      <c r="AP23" s="62"/>
-      <c r="AQ23" s="62"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="56"/>
+      <c r="Y23" s="56"/>
+      <c r="Z23" s="56"/>
+      <c r="AA23" s="56"/>
+      <c r="AB23" s="56"/>
+      <c r="AC23" s="56"/>
+      <c r="AD23" s="56"/>
+      <c r="AE23" s="56"/>
+      <c r="AF23" s="56"/>
+      <c r="AG23" s="56"/>
+      <c r="AH23" s="56"/>
+      <c r="AI23" s="56"/>
+      <c r="AJ23" s="56"/>
+      <c r="AK23" s="56"/>
+      <c r="AL23" s="56"/>
+      <c r="AM23" s="56"/>
+      <c r="AN23" s="56"/>
+      <c r="AO23" s="56"/>
+      <c r="AP23" s="56"/>
+      <c r="AQ23" s="56"/>
     </row>
     <row r="24" spans="1:45" ht="19.5" customHeight="1">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="61" t="s">
         <v>249</v>
       </c>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="70">
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="64">
         <f>SUM(E5:E23)</f>
         <v>244.78999999999996</v>
       </c>
@@ -6374,55 +6193,48 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71">
+      <c r="K24" s="65"/>
+      <c r="L24" s="65">
         <f>SUM(L5:L23)</f>
         <v>332048225.94999999</v>
       </c>
-      <c r="M24" s="40" t="s">
+      <c r="M24" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="41"/>
-      <c r="S24" s="41"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="41"/>
-      <c r="Y24" s="41"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="41"/>
-      <c r="AB24" s="41"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="41"/>
-      <c r="AE24" s="41"/>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="41"/>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="41"/>
-      <c r="AJ24" s="41"/>
-      <c r="AK24" s="41"/>
-      <c r="AL24" s="41"/>
-      <c r="AM24" s="41"/>
-      <c r="AN24" s="41"/>
-      <c r="AO24" s="41"/>
-      <c r="AP24" s="41"/>
-      <c r="AQ24" s="72"/>
-      <c r="AR24" s="73"/>
-      <c r="AS24" s="73"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="39"/>
+      <c r="V24" s="39"/>
+      <c r="W24" s="39"/>
+      <c r="X24" s="39"/>
+      <c r="Y24" s="39"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="39"/>
+      <c r="AB24" s="39"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="39"/>
+      <c r="AE24" s="39"/>
+      <c r="AF24" s="39"/>
+      <c r="AG24" s="39"/>
+      <c r="AH24" s="39"/>
+      <c r="AI24" s="39"/>
+      <c r="AJ24" s="39"/>
+      <c r="AK24" s="39"/>
+      <c r="AL24" s="39"/>
+      <c r="AM24" s="39"/>
+      <c r="AN24" s="39"/>
+      <c r="AO24" s="39"/>
+      <c r="AP24" s="39"/>
+      <c r="AQ24" s="66"/>
+      <c r="AR24" s="67"/>
+      <c r="AS24" s="67"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="M24:AQ24"/>
-    <mergeCell ref="A1:T2"/>
-    <mergeCell ref="U3:AQ3"/>
-    <mergeCell ref="A4:AQ4"/>
-  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -6432,91 +6244,91 @@
   <dimension ref="A1:AS21"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="56" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="56" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="56" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="56" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="56" customWidth="1"/>
-    <col min="10" max="10" width="15" style="56" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="56" customWidth="1"/>
-    <col min="12" max="12" width="25.5703125" style="56" customWidth="1"/>
-    <col min="13" max="13" width="10" style="56" customWidth="1"/>
-    <col min="14" max="14" width="15" style="56" customWidth="1"/>
-    <col min="15" max="15" width="8" style="56" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" style="56" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="56"/>
-    <col min="18" max="18" width="39.5703125" style="56" customWidth="1"/>
-    <col min="19" max="19" width="51" style="56" customWidth="1"/>
-    <col min="20" max="20" width="42.5703125" style="56" customWidth="1"/>
-    <col min="21" max="21" width="18" style="56" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="17.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="17.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18" style="56" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.85546875" style="56" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="17" style="56" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17" style="56" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.7109375" style="56" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5703125" style="56" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17" style="56" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="14.42578125" style="56"/>
+    <col min="1" max="1" width="4.28515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="50" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" style="50" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="50" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="50" customWidth="1"/>
+    <col min="10" max="10" width="15" style="50" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="50" customWidth="1"/>
+    <col min="12" max="12" width="25.5703125" style="50" customWidth="1"/>
+    <col min="13" max="13" width="10" style="50" customWidth="1"/>
+    <col min="14" max="14" width="15" style="50" customWidth="1"/>
+    <col min="15" max="15" width="8" style="50" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" style="50" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="50"/>
+    <col min="18" max="18" width="39.5703125" style="50" customWidth="1"/>
+    <col min="19" max="19" width="51" style="50" customWidth="1"/>
+    <col min="20" max="20" width="42.5703125" style="50" customWidth="1"/>
+    <col min="21" max="21" width="18" style="50" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18" style="50" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="17.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18" style="50" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.85546875" style="50" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="17" style="50" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17" style="50" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17" style="50" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="14.42578125" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:45" ht="15" customHeight="1">
+      <c r="A1" s="47" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="55"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="49"/>
     </row>
     <row r="2" spans="1:45">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="59"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="53"/>
     </row>
     <row r="3" spans="1:45" ht="45">
       <c r="A3" s="4" t="s">
@@ -6579,57 +6391,57 @@
       <c r="T3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="40" t="s">
+      <c r="U3" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
       <c r="AR3" s="15"/>
       <c r="AS3" s="15"/>
     </row>
     <row r="4" spans="1:45" ht="15" customHeight="1">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="68" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
     </row>
     <row r="5" spans="1:45" ht="48.75" customHeight="1">
       <c r="A5" s="7">
@@ -6644,7 +6456,7 @@
       <c r="D5" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="57">
         <v>9.1999999999999993</v>
       </c>
       <c r="F5" s="24" t="s">
@@ -6665,7 +6477,7 @@
       <c r="K5" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L5" s="64">
+      <c r="L5" s="58">
         <v>8410358.8900000006</v>
       </c>
       <c r="M5" s="7">
@@ -6692,31 +6504,31 @@
       <c r="T5" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="U5" s="76" t="s">
+      <c r="U5" s="70" t="s">
         <v>396</v>
       </c>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="62"/>
-      <c r="AB5" s="62"/>
-      <c r="AC5" s="62"/>
-      <c r="AD5" s="62"/>
-      <c r="AE5" s="62"/>
-      <c r="AF5" s="62"/>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="62"/>
-      <c r="AI5" s="62"/>
-      <c r="AJ5" s="62"/>
-      <c r="AK5" s="62"/>
-      <c r="AL5" s="62"/>
-      <c r="AM5" s="62"/>
-      <c r="AN5" s="62"/>
-      <c r="AO5" s="62"/>
-      <c r="AP5" s="62"/>
-      <c r="AQ5" s="62"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="56"/>
+      <c r="AI5" s="56"/>
+      <c r="AJ5" s="56"/>
+      <c r="AK5" s="56"/>
+      <c r="AL5" s="56"/>
+      <c r="AM5" s="56"/>
+      <c r="AN5" s="56"/>
+      <c r="AO5" s="56"/>
+      <c r="AP5" s="56"/>
+      <c r="AQ5" s="56"/>
     </row>
     <row r="6" spans="1:45" ht="48.75" customHeight="1">
       <c r="A6" s="7">
@@ -6732,7 +6544,7 @@
       <c r="D6" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="57">
         <v>3.52</v>
       </c>
       <c r="F6" s="24" t="s">
@@ -6753,7 +6565,7 @@
       <c r="K6" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="58">
         <v>5895663.1699999999</v>
       </c>
       <c r="M6" s="7">
@@ -6780,31 +6592,31 @@
       <c r="T6" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="U6" s="76" t="s">
+      <c r="U6" s="70" t="s">
         <v>397</v>
       </c>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="62"/>
-      <c r="AB6" s="62"/>
-      <c r="AC6" s="62"/>
-      <c r="AD6" s="62"/>
-      <c r="AE6" s="62"/>
-      <c r="AF6" s="62"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
-      <c r="AL6" s="62"/>
-      <c r="AM6" s="62"/>
-      <c r="AN6" s="62"/>
-      <c r="AO6" s="62"/>
-      <c r="AP6" s="62"/>
-      <c r="AQ6" s="62"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="56"/>
+      <c r="AJ6" s="56"/>
+      <c r="AK6" s="56"/>
+      <c r="AL6" s="56"/>
+      <c r="AM6" s="56"/>
+      <c r="AN6" s="56"/>
+      <c r="AO6" s="56"/>
+      <c r="AP6" s="56"/>
+      <c r="AQ6" s="56"/>
     </row>
     <row r="7" spans="1:45" ht="48.75" customHeight="1">
       <c r="A7" s="7">
@@ -6820,7 +6632,7 @@
       <c r="D7" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="57">
         <v>20.16</v>
       </c>
       <c r="F7" s="24" t="s">
@@ -6841,7 +6653,7 @@
       <c r="K7" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="58">
         <v>23556493.370000001</v>
       </c>
       <c r="M7" s="7">
@@ -6866,31 +6678,31 @@
       <c r="T7" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="U7" s="76" t="s">
+      <c r="U7" s="70" t="s">
         <v>398</v>
       </c>
-      <c r="V7" s="62"/>
-      <c r="W7" s="62"/>
-      <c r="X7" s="62"/>
-      <c r="Y7" s="62"/>
-      <c r="Z7" s="62"/>
-      <c r="AA7" s="62"/>
-      <c r="AB7" s="62"/>
-      <c r="AC7" s="62"/>
-      <c r="AD7" s="62"/>
-      <c r="AE7" s="62"/>
-      <c r="AF7" s="62"/>
-      <c r="AG7" s="62"/>
-      <c r="AH7" s="62"/>
-      <c r="AI7" s="62"/>
-      <c r="AJ7" s="62"/>
-      <c r="AK7" s="62"/>
-      <c r="AL7" s="62"/>
-      <c r="AM7" s="62"/>
-      <c r="AN7" s="62"/>
-      <c r="AO7" s="62"/>
-      <c r="AP7" s="62"/>
-      <c r="AQ7" s="62"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="56"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="56"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="56"/>
+      <c r="AH7" s="56"/>
+      <c r="AI7" s="56"/>
+      <c r="AJ7" s="56"/>
+      <c r="AK7" s="56"/>
+      <c r="AL7" s="56"/>
+      <c r="AM7" s="56"/>
+      <c r="AN7" s="56"/>
+      <c r="AO7" s="56"/>
+      <c r="AP7" s="56"/>
+      <c r="AQ7" s="56"/>
     </row>
     <row r="8" spans="1:45" ht="48.75" customHeight="1">
       <c r="A8" s="7">
@@ -6906,7 +6718,7 @@
       <c r="D8" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="57">
         <v>23.2</v>
       </c>
       <c r="F8" s="24" t="s">
@@ -6927,7 +6739,7 @@
       <c r="K8" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L8" s="64">
+      <c r="L8" s="58">
         <v>30980268.039999999</v>
       </c>
       <c r="M8" s="7">
@@ -6954,31 +6766,31 @@
       <c r="T8" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="U8" s="76" t="s">
+      <c r="U8" s="70" t="s">
         <v>399</v>
       </c>
-      <c r="V8" s="62"/>
-      <c r="W8" s="62"/>
-      <c r="X8" s="62"/>
-      <c r="Y8" s="62"/>
-      <c r="Z8" s="62"/>
-      <c r="AA8" s="62"/>
-      <c r="AB8" s="62"/>
-      <c r="AC8" s="62"/>
-      <c r="AD8" s="62"/>
-      <c r="AE8" s="62"/>
-      <c r="AF8" s="62"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="62"/>
-      <c r="AL8" s="62"/>
-      <c r="AM8" s="62"/>
-      <c r="AN8" s="62"/>
-      <c r="AO8" s="62"/>
-      <c r="AP8" s="62"/>
-      <c r="AQ8" s="62"/>
+      <c r="V8" s="56"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="56"/>
+      <c r="Z8" s="56"/>
+      <c r="AA8" s="56"/>
+      <c r="AB8" s="56"/>
+      <c r="AC8" s="56"/>
+      <c r="AD8" s="56"/>
+      <c r="AE8" s="56"/>
+      <c r="AF8" s="56"/>
+      <c r="AG8" s="56"/>
+      <c r="AH8" s="56"/>
+      <c r="AI8" s="56"/>
+      <c r="AJ8" s="56"/>
+      <c r="AK8" s="56"/>
+      <c r="AL8" s="56"/>
+      <c r="AM8" s="56"/>
+      <c r="AN8" s="56"/>
+      <c r="AO8" s="56"/>
+      <c r="AP8" s="56"/>
+      <c r="AQ8" s="56"/>
     </row>
     <row r="9" spans="1:45" ht="79.5" customHeight="1">
       <c r="A9" s="7">
@@ -6994,7 +6806,7 @@
       <c r="D9" s="29" t="s">
         <v>335</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="57">
         <v>0.34499999999999997</v>
       </c>
       <c r="F9" s="24" t="s">
@@ -7015,7 +6827,7 @@
       <c r="K9" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="58">
         <v>3008187.68</v>
       </c>
       <c r="M9" s="7">
@@ -7040,33 +6852,33 @@
         <v>339</v>
       </c>
       <c r="T9" s="33"/>
-      <c r="U9" s="76" t="s">
+      <c r="U9" s="70" t="s">
         <v>400</v>
       </c>
-      <c r="V9" s="76" t="s">
+      <c r="V9" s="70" t="s">
         <v>401</v>
       </c>
-      <c r="W9" s="62"/>
-      <c r="X9" s="62"/>
-      <c r="Y9" s="62"/>
-      <c r="Z9" s="62"/>
-      <c r="AA9" s="62"/>
-      <c r="AB9" s="62"/>
-      <c r="AC9" s="62"/>
-      <c r="AD9" s="62"/>
-      <c r="AE9" s="62"/>
-      <c r="AF9" s="62"/>
-      <c r="AG9" s="62"/>
-      <c r="AH9" s="62"/>
-      <c r="AI9" s="62"/>
-      <c r="AJ9" s="62"/>
-      <c r="AK9" s="62"/>
-      <c r="AL9" s="62"/>
-      <c r="AM9" s="62"/>
-      <c r="AN9" s="62"/>
-      <c r="AO9" s="62"/>
-      <c r="AP9" s="62"/>
-      <c r="AQ9" s="62"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="56"/>
+      <c r="AA9" s="56"/>
+      <c r="AB9" s="56"/>
+      <c r="AC9" s="56"/>
+      <c r="AD9" s="56"/>
+      <c r="AE9" s="56"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="56"/>
+      <c r="AH9" s="56"/>
+      <c r="AI9" s="56"/>
+      <c r="AJ9" s="56"/>
+      <c r="AK9" s="56"/>
+      <c r="AL9" s="56"/>
+      <c r="AM9" s="56"/>
+      <c r="AN9" s="56"/>
+      <c r="AO9" s="56"/>
+      <c r="AP9" s="56"/>
+      <c r="AQ9" s="56"/>
     </row>
     <row r="10" spans="1:45" ht="48.75" customHeight="1">
       <c r="A10" s="7">
@@ -7082,7 +6894,7 @@
       <c r="D10" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="57">
         <v>0.24</v>
       </c>
       <c r="F10" s="24" t="s">
@@ -7103,7 +6915,7 @@
       <c r="K10" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L10" s="64">
+      <c r="L10" s="58">
         <v>3555318.56</v>
       </c>
       <c r="M10" s="7">
@@ -7128,33 +6940,33 @@
         <v>343</v>
       </c>
       <c r="T10" s="33"/>
-      <c r="U10" s="76" t="s">
+      <c r="U10" s="70" t="s">
         <v>402</v>
       </c>
-      <c r="V10" s="76" t="s">
+      <c r="V10" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="W10" s="62"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="62"/>
-      <c r="AA10" s="62"/>
-      <c r="AB10" s="62"/>
-      <c r="AC10" s="62"/>
-      <c r="AD10" s="62"/>
-      <c r="AE10" s="62"/>
-      <c r="AF10" s="62"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="62"/>
-      <c r="AJ10" s="62"/>
-      <c r="AK10" s="62"/>
-      <c r="AL10" s="62"/>
-      <c r="AM10" s="62"/>
-      <c r="AN10" s="62"/>
-      <c r="AO10" s="62"/>
-      <c r="AP10" s="62"/>
-      <c r="AQ10" s="62"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="56"/>
+      <c r="Z10" s="56"/>
+      <c r="AA10" s="56"/>
+      <c r="AB10" s="56"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="56"/>
+      <c r="AH10" s="56"/>
+      <c r="AI10" s="56"/>
+      <c r="AJ10" s="56"/>
+      <c r="AK10" s="56"/>
+      <c r="AL10" s="56"/>
+      <c r="AM10" s="56"/>
+      <c r="AN10" s="56"/>
+      <c r="AO10" s="56"/>
+      <c r="AP10" s="56"/>
+      <c r="AQ10" s="56"/>
     </row>
     <row r="11" spans="1:45" ht="48.75" customHeight="1">
       <c r="A11" s="7">
@@ -7170,7 +6982,7 @@
       <c r="D11" s="29" t="s">
         <v>345</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="57" t="s">
         <v>129</v>
       </c>
       <c r="F11" s="24" t="s">
@@ -7191,7 +7003,7 @@
       <c r="K11" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="58">
         <v>766987.87</v>
       </c>
       <c r="M11" s="7">
@@ -7216,33 +7028,33 @@
         <v>349</v>
       </c>
       <c r="T11" s="33"/>
-      <c r="U11" s="76" t="s">
+      <c r="U11" s="70" t="s">
         <v>404</v>
       </c>
-      <c r="V11" s="76" t="s">
+      <c r="V11" s="70" t="s">
         <v>405</v>
       </c>
-      <c r="W11" s="62"/>
-      <c r="X11" s="62"/>
-      <c r="Y11" s="62"/>
-      <c r="Z11" s="62"/>
-      <c r="AA11" s="62"/>
-      <c r="AB11" s="62"/>
-      <c r="AC11" s="62"/>
-      <c r="AD11" s="62"/>
-      <c r="AE11" s="62"/>
-      <c r="AF11" s="62"/>
-      <c r="AG11" s="62"/>
-      <c r="AH11" s="62"/>
-      <c r="AI11" s="62"/>
-      <c r="AJ11" s="62"/>
-      <c r="AK11" s="62"/>
-      <c r="AL11" s="62"/>
-      <c r="AM11" s="62"/>
-      <c r="AN11" s="62"/>
-      <c r="AO11" s="62"/>
-      <c r="AP11" s="62"/>
-      <c r="AQ11" s="62"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="56"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="56"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="56"/>
+      <c r="AH11" s="56"/>
+      <c r="AI11" s="56"/>
+      <c r="AJ11" s="56"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="56"/>
+      <c r="AN11" s="56"/>
+      <c r="AO11" s="56"/>
+      <c r="AP11" s="56"/>
+      <c r="AQ11" s="56"/>
     </row>
     <row r="12" spans="1:45" ht="48.75" customHeight="1">
       <c r="A12" s="7">
@@ -7258,7 +7070,7 @@
       <c r="D12" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="57" t="s">
         <v>129</v>
       </c>
       <c r="F12" s="24" t="s">
@@ -7279,7 +7091,7 @@
       <c r="K12" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L12" s="64">
+      <c r="L12" s="58">
         <v>449911.64</v>
       </c>
       <c r="M12" s="7">
@@ -7302,33 +7114,33 @@
       </c>
       <c r="S12" s="24"/>
       <c r="T12" s="33"/>
-      <c r="U12" s="76" t="s">
+      <c r="U12" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="V12" s="76" t="s">
+      <c r="V12" s="70" t="s">
         <v>407</v>
       </c>
-      <c r="W12" s="62"/>
-      <c r="X12" s="62"/>
-      <c r="Y12" s="62"/>
-      <c r="Z12" s="62"/>
-      <c r="AA12" s="62"/>
-      <c r="AB12" s="62"/>
-      <c r="AC12" s="62"/>
-      <c r="AD12" s="62"/>
-      <c r="AE12" s="62"/>
-      <c r="AF12" s="62"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
-      <c r="AL12" s="62"/>
-      <c r="AM12" s="62"/>
-      <c r="AN12" s="62"/>
-      <c r="AO12" s="62"/>
-      <c r="AP12" s="62"/>
-      <c r="AQ12" s="62"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="56"/>
+      <c r="Z12" s="56"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="56"/>
+      <c r="AC12" s="56"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
+      <c r="AJ12" s="56"/>
+      <c r="AK12" s="56"/>
+      <c r="AL12" s="56"/>
+      <c r="AM12" s="56"/>
+      <c r="AN12" s="56"/>
+      <c r="AO12" s="56"/>
+      <c r="AP12" s="56"/>
+      <c r="AQ12" s="56"/>
     </row>
     <row r="13" spans="1:45" ht="48.75" customHeight="1">
       <c r="A13" s="7">
@@ -7344,7 +7156,7 @@
       <c r="D13" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="57">
         <v>6.88</v>
       </c>
       <c r="F13" s="24" t="s">
@@ -7365,7 +7177,7 @@
       <c r="K13" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L13" s="64">
+      <c r="L13" s="58">
         <v>25807464.879999999</v>
       </c>
       <c r="M13" s="7">
@@ -7390,33 +7202,33 @@
         <v>357</v>
       </c>
       <c r="T13" s="33"/>
-      <c r="U13" s="76" t="s">
+      <c r="U13" s="70" t="s">
         <v>408</v>
       </c>
-      <c r="V13" s="76" t="s">
+      <c r="V13" s="70" t="s">
         <v>409</v>
       </c>
-      <c r="W13" s="62"/>
-      <c r="X13" s="62"/>
-      <c r="Y13" s="62"/>
-      <c r="Z13" s="62"/>
-      <c r="AA13" s="62"/>
-      <c r="AB13" s="62"/>
-      <c r="AC13" s="62"/>
-      <c r="AD13" s="62"/>
-      <c r="AE13" s="62"/>
-      <c r="AF13" s="62"/>
-      <c r="AG13" s="62"/>
-      <c r="AH13" s="62"/>
-      <c r="AI13" s="62"/>
-      <c r="AJ13" s="62"/>
-      <c r="AK13" s="62"/>
-      <c r="AL13" s="62"/>
-      <c r="AM13" s="62"/>
-      <c r="AN13" s="62"/>
-      <c r="AO13" s="62"/>
-      <c r="AP13" s="62"/>
-      <c r="AQ13" s="62"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="56"/>
+      <c r="Y13" s="56"/>
+      <c r="Z13" s="56"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="56"/>
+      <c r="AC13" s="56"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="56"/>
+      <c r="AH13" s="56"/>
+      <c r="AI13" s="56"/>
+      <c r="AJ13" s="56"/>
+      <c r="AK13" s="56"/>
+      <c r="AL13" s="56"/>
+      <c r="AM13" s="56"/>
+      <c r="AN13" s="56"/>
+      <c r="AO13" s="56"/>
+      <c r="AP13" s="56"/>
+      <c r="AQ13" s="56"/>
     </row>
     <row r="14" spans="1:45" ht="48.75" customHeight="1">
       <c r="A14" s="7">
@@ -7432,7 +7244,7 @@
       <c r="D14" s="29" t="s">
         <v>359</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="57">
         <v>33.01</v>
       </c>
       <c r="F14" s="24" t="s">
@@ -7453,7 +7265,7 @@
       <c r="K14" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L14" s="64">
+      <c r="L14" s="58">
         <v>45465195.979999997</v>
       </c>
       <c r="M14" s="7">
@@ -7478,31 +7290,31 @@
       <c r="T14" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="U14" s="76" t="s">
+      <c r="U14" s="70" t="s">
         <v>410</v>
       </c>
-      <c r="V14" s="62"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="62"/>
-      <c r="AB14" s="62"/>
-      <c r="AC14" s="62"/>
-      <c r="AD14" s="62"/>
-      <c r="AE14" s="62"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="62"/>
-      <c r="AM14" s="62"/>
-      <c r="AN14" s="62"/>
-      <c r="AO14" s="62"/>
-      <c r="AP14" s="62"/>
-      <c r="AQ14" s="62"/>
+      <c r="V14" s="56"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="56"/>
+      <c r="Y14" s="56"/>
+      <c r="Z14" s="56"/>
+      <c r="AA14" s="56"/>
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="56"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="56"/>
+      <c r="AM14" s="56"/>
+      <c r="AN14" s="56"/>
+      <c r="AO14" s="56"/>
+      <c r="AP14" s="56"/>
+      <c r="AQ14" s="56"/>
     </row>
     <row r="15" spans="1:45" ht="48.75" customHeight="1">
       <c r="A15" s="7">
@@ -7518,7 +7330,7 @@
       <c r="D15" s="29" t="s">
         <v>363</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E15" s="57">
         <v>24.64</v>
       </c>
       <c r="F15" s="24" t="s">
@@ -7539,7 +7351,7 @@
       <c r="K15" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L15" s="64">
+      <c r="L15" s="58">
         <v>31059366.289999999</v>
       </c>
       <c r="M15" s="7">
@@ -7564,31 +7376,31 @@
       <c r="T15" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="U15" s="76" t="s">
+      <c r="U15" s="70" t="s">
         <v>411</v>
       </c>
-      <c r="V15" s="62"/>
-      <c r="W15" s="62"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62"/>
-      <c r="Z15" s="62"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="62"/>
-      <c r="AC15" s="62"/>
-      <c r="AD15" s="62"/>
-      <c r="AE15" s="62"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="62"/>
-      <c r="AM15" s="62"/>
-      <c r="AN15" s="62"/>
-      <c r="AO15" s="62"/>
-      <c r="AP15" s="62"/>
-      <c r="AQ15" s="62"/>
+      <c r="V15" s="56"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="56"/>
+      <c r="Z15" s="56"/>
+      <c r="AA15" s="56"/>
+      <c r="AB15" s="56"/>
+      <c r="AC15" s="56"/>
+      <c r="AD15" s="56"/>
+      <c r="AE15" s="56"/>
+      <c r="AF15" s="56"/>
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="56"/>
+      <c r="AI15" s="56"/>
+      <c r="AJ15" s="56"/>
+      <c r="AK15" s="56"/>
+      <c r="AL15" s="56"/>
+      <c r="AM15" s="56"/>
+      <c r="AN15" s="56"/>
+      <c r="AO15" s="56"/>
+      <c r="AP15" s="56"/>
+      <c r="AQ15" s="56"/>
     </row>
     <row r="16" spans="1:45" ht="48.75" customHeight="1">
       <c r="A16" s="7">
@@ -7604,7 +7416,7 @@
       <c r="D16" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="57">
         <v>5.0999999999999996</v>
       </c>
       <c r="F16" s="24" t="s">
@@ -7625,7 +7437,7 @@
       <c r="K16" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L16" s="64">
+      <c r="L16" s="58">
         <v>5558156.6900000004</v>
       </c>
       <c r="M16" s="7">
@@ -7652,31 +7464,31 @@
       <c r="T16" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="U16" s="76" t="s">
+      <c r="U16" s="70" t="s">
         <v>412</v>
       </c>
-      <c r="V16" s="62"/>
-      <c r="W16" s="62"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="62"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
-      <c r="AL16" s="62"/>
-      <c r="AM16" s="62"/>
-      <c r="AN16" s="62"/>
-      <c r="AO16" s="62"/>
-      <c r="AP16" s="62"/>
-      <c r="AQ16" s="62"/>
+      <c r="V16" s="56"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="56"/>
+      <c r="Y16" s="56"/>
+      <c r="Z16" s="56"/>
+      <c r="AA16" s="56"/>
+      <c r="AB16" s="56"/>
+      <c r="AC16" s="56"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="56"/>
+      <c r="AF16" s="56"/>
+      <c r="AG16" s="56"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="56"/>
+      <c r="AJ16" s="56"/>
+      <c r="AK16" s="56"/>
+      <c r="AL16" s="56"/>
+      <c r="AM16" s="56"/>
+      <c r="AN16" s="56"/>
+      <c r="AO16" s="56"/>
+      <c r="AP16" s="56"/>
+      <c r="AQ16" s="56"/>
     </row>
     <row r="17" spans="1:43" ht="48.75" customHeight="1">
       <c r="A17" s="7">
@@ -7692,7 +7504,7 @@
       <c r="D17" s="29" t="s">
         <v>374</v>
       </c>
-      <c r="E17" s="63">
+      <c r="E17" s="57">
         <v>17.96</v>
       </c>
       <c r="F17" s="24" t="s">
@@ -7713,7 +7525,7 @@
       <c r="K17" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L17" s="64">
+      <c r="L17" s="58">
         <v>13610903.73</v>
       </c>
       <c r="M17" s="7">
@@ -7740,31 +7552,31 @@
       <c r="T17" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="U17" s="76" t="s">
+      <c r="U17" s="70" t="s">
         <v>413</v>
       </c>
-      <c r="V17" s="62"/>
-      <c r="W17" s="62"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
-      <c r="Z17" s="62"/>
-      <c r="AA17" s="62"/>
-      <c r="AB17" s="62"/>
-      <c r="AC17" s="62"/>
-      <c r="AD17" s="62"/>
-      <c r="AE17" s="62"/>
-      <c r="AF17" s="62"/>
-      <c r="AG17" s="62"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="62"/>
-      <c r="AK17" s="62"/>
-      <c r="AL17" s="62"/>
-      <c r="AM17" s="62"/>
-      <c r="AN17" s="62"/>
-      <c r="AO17" s="62"/>
-      <c r="AP17" s="62"/>
-      <c r="AQ17" s="62"/>
+      <c r="V17" s="56"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="56"/>
+      <c r="Z17" s="56"/>
+      <c r="AA17" s="56"/>
+      <c r="AB17" s="56"/>
+      <c r="AC17" s="56"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="56"/>
+      <c r="AF17" s="56"/>
+      <c r="AG17" s="56"/>
+      <c r="AH17" s="56"/>
+      <c r="AI17" s="56"/>
+      <c r="AJ17" s="56"/>
+      <c r="AK17" s="56"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="56"/>
+      <c r="AN17" s="56"/>
+      <c r="AO17" s="56"/>
+      <c r="AP17" s="56"/>
+      <c r="AQ17" s="56"/>
     </row>
     <row r="18" spans="1:43" ht="48.75" customHeight="1">
       <c r="A18" s="7">
@@ -7780,7 +7592,7 @@
       <c r="D18" s="29" t="s">
         <v>379</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E18" s="57">
         <v>26.64</v>
       </c>
       <c r="F18" s="24" t="s">
@@ -7801,7 +7613,7 @@
       <c r="K18" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L18" s="64">
+      <c r="L18" s="58">
         <v>33263573.260000002</v>
       </c>
       <c r="M18" s="7">
@@ -7826,33 +7638,33 @@
       <c r="T18" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="U18" s="76" t="s">
+      <c r="U18" s="70" t="s">
         <v>414</v>
       </c>
-      <c r="V18" s="76" t="s">
+      <c r="V18" s="70" t="s">
         <v>415</v>
       </c>
-      <c r="W18" s="62"/>
-      <c r="X18" s="62"/>
-      <c r="Y18" s="62"/>
-      <c r="Z18" s="62"/>
-      <c r="AA18" s="62"/>
-      <c r="AB18" s="62"/>
-      <c r="AC18" s="62"/>
-      <c r="AD18" s="62"/>
-      <c r="AE18" s="62"/>
-      <c r="AF18" s="62"/>
-      <c r="AG18" s="62"/>
-      <c r="AH18" s="62"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="62"/>
-      <c r="AK18" s="62"/>
-      <c r="AL18" s="62"/>
-      <c r="AM18" s="62"/>
-      <c r="AN18" s="62"/>
-      <c r="AO18" s="62"/>
-      <c r="AP18" s="62"/>
-      <c r="AQ18" s="62"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="56"/>
+      <c r="Y18" s="56"/>
+      <c r="Z18" s="56"/>
+      <c r="AA18" s="56"/>
+      <c r="AB18" s="56"/>
+      <c r="AC18" s="56"/>
+      <c r="AD18" s="56"/>
+      <c r="AE18" s="56"/>
+      <c r="AF18" s="56"/>
+      <c r="AG18" s="56"/>
+      <c r="AH18" s="56"/>
+      <c r="AI18" s="56"/>
+      <c r="AJ18" s="56"/>
+      <c r="AK18" s="56"/>
+      <c r="AL18" s="56"/>
+      <c r="AM18" s="56"/>
+      <c r="AN18" s="56"/>
+      <c r="AO18" s="56"/>
+      <c r="AP18" s="56"/>
+      <c r="AQ18" s="56"/>
     </row>
     <row r="19" spans="1:43" ht="48.75" customHeight="1">
       <c r="A19" s="7">
@@ -7868,7 +7680,7 @@
       <c r="D19" s="29" t="s">
         <v>384</v>
       </c>
-      <c r="E19" s="63">
+      <c r="E19" s="57">
         <v>5.16</v>
       </c>
       <c r="F19" s="24" t="s">
@@ -7889,7 +7701,7 @@
       <c r="K19" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L19" s="64">
+      <c r="L19" s="58">
         <v>5692584.3499999996</v>
       </c>
       <c r="M19" s="7">
@@ -7914,33 +7726,33 @@
         <v>388</v>
       </c>
       <c r="T19" s="33"/>
-      <c r="U19" s="76" t="s">
+      <c r="U19" s="70" t="s">
         <v>416</v>
       </c>
-      <c r="V19" s="76" t="s">
+      <c r="V19" s="70" t="s">
         <v>417</v>
       </c>
-      <c r="W19" s="62"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
-      <c r="Z19" s="62"/>
-      <c r="AA19" s="62"/>
-      <c r="AB19" s="62"/>
-      <c r="AC19" s="62"/>
-      <c r="AD19" s="62"/>
-      <c r="AE19" s="62"/>
-      <c r="AF19" s="62"/>
-      <c r="AG19" s="62"/>
-      <c r="AH19" s="62"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="62"/>
-      <c r="AK19" s="62"/>
-      <c r="AL19" s="62"/>
-      <c r="AM19" s="62"/>
-      <c r="AN19" s="62"/>
-      <c r="AO19" s="62"/>
-      <c r="AP19" s="62"/>
-      <c r="AQ19" s="62"/>
+      <c r="W19" s="56"/>
+      <c r="X19" s="56"/>
+      <c r="Y19" s="56"/>
+      <c r="Z19" s="56"/>
+      <c r="AA19" s="56"/>
+      <c r="AB19" s="56"/>
+      <c r="AC19" s="56"/>
+      <c r="AD19" s="56"/>
+      <c r="AE19" s="56"/>
+      <c r="AF19" s="56"/>
+      <c r="AG19" s="56"/>
+      <c r="AH19" s="56"/>
+      <c r="AI19" s="56"/>
+      <c r="AJ19" s="56"/>
+      <c r="AK19" s="56"/>
+      <c r="AL19" s="56"/>
+      <c r="AM19" s="56"/>
+      <c r="AN19" s="56"/>
+      <c r="AO19" s="56"/>
+      <c r="AP19" s="56"/>
+      <c r="AQ19" s="56"/>
     </row>
     <row r="20" spans="1:43" ht="48.75" customHeight="1">
       <c r="A20" s="7">
@@ -7956,7 +7768,7 @@
       <c r="D20" s="29" t="s">
         <v>389</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="57" t="s">
         <v>390</v>
       </c>
       <c r="F20" s="24" t="s">
@@ -7977,7 +7789,7 @@
       <c r="K20" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L20" s="64">
+      <c r="L20" s="58">
         <v>2670688.4300000002</v>
       </c>
       <c r="M20" s="7">
@@ -8000,42 +7812,42 @@
         <v>394</v>
       </c>
       <c r="T20" s="33"/>
-      <c r="U20" s="76" t="s">
+      <c r="U20" s="70" t="s">
         <v>418</v>
       </c>
-      <c r="V20" s="76" t="s">
+      <c r="V20" s="70" t="s">
         <v>419</v>
       </c>
-      <c r="W20" s="62"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="62"/>
-      <c r="AB20" s="62"/>
-      <c r="AC20" s="62"/>
-      <c r="AD20" s="62"/>
-      <c r="AE20" s="62"/>
-      <c r="AF20" s="62"/>
-      <c r="AG20" s="62"/>
-      <c r="AH20" s="62"/>
-      <c r="AI20" s="62"/>
-      <c r="AJ20" s="62"/>
-      <c r="AK20" s="62"/>
-      <c r="AL20" s="62"/>
-      <c r="AM20" s="62"/>
-      <c r="AN20" s="62"/>
-      <c r="AO20" s="62"/>
-      <c r="AP20" s="62"/>
-      <c r="AQ20" s="62"/>
+      <c r="W20" s="56"/>
+      <c r="X20" s="56"/>
+      <c r="Y20" s="56"/>
+      <c r="Z20" s="56"/>
+      <c r="AA20" s="56"/>
+      <c r="AB20" s="56"/>
+      <c r="AC20" s="56"/>
+      <c r="AD20" s="56"/>
+      <c r="AE20" s="56"/>
+      <c r="AF20" s="56"/>
+      <c r="AG20" s="56"/>
+      <c r="AH20" s="56"/>
+      <c r="AI20" s="56"/>
+      <c r="AJ20" s="56"/>
+      <c r="AK20" s="56"/>
+      <c r="AL20" s="56"/>
+      <c r="AM20" s="56"/>
+      <c r="AN20" s="56"/>
+      <c r="AO20" s="56"/>
+      <c r="AP20" s="56"/>
+      <c r="AQ20" s="56"/>
     </row>
     <row r="21" spans="1:43" ht="15" customHeight="1">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="71" t="s">
         <v>395</v>
       </c>
-      <c r="B21" s="75"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="79">
+      <c r="B21" s="69"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="73">
         <f>SUM(E5:E20)</f>
         <v>176.05499999999998</v>
       </c>
@@ -8044,30 +7856,23 @@
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="80">
+      <c r="K21" s="74"/>
+      <c r="L21" s="74">
         <f>SUM(L5:L20)</f>
         <v>239751122.82999998</v>
       </c>
-      <c r="M21" s="77" t="s">
+      <c r="M21" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="N21" s="75"/>
-      <c r="O21" s="75"/>
-      <c r="P21" s="75"/>
-      <c r="Q21" s="75"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="75"/>
-      <c r="T21" s="78"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="69"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="69"/>
+      <c r="T21" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A4:T4"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="M21:T21"/>
-    <mergeCell ref="A1:T2"/>
-    <mergeCell ref="U3:AQ3"/>
-  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -8077,74 +7882,74 @@
   <dimension ref="A1:BA20"/>
   <sheetFormatPr defaultColWidth="125.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="86" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="86" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="86" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="121.42578125" style="86" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.140625" style="86" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="86" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.7109375" style="86" customWidth="1"/>
-    <col min="8" max="8" width="51" style="86" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" style="86" customWidth="1"/>
-    <col min="10" max="10" width="12" style="86" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" style="86" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="86" customWidth="1"/>
-    <col min="13" max="13" width="24.42578125" style="86" customWidth="1"/>
-    <col min="14" max="14" width="34.7109375" style="86" customWidth="1"/>
-    <col min="15" max="15" width="18.85546875" style="86" customWidth="1"/>
-    <col min="16" max="16" width="20.85546875" style="86" customWidth="1"/>
-    <col min="17" max="17" width="24.85546875" style="86" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" style="86" customWidth="1"/>
-    <col min="19" max="19" width="18.85546875" style="86" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="86" customWidth="1"/>
-    <col min="21" max="21" width="20.5703125" style="86" customWidth="1"/>
-    <col min="22" max="22" width="19.85546875" style="86" customWidth="1"/>
-    <col min="23" max="23" width="11.85546875" style="86" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="86" customWidth="1"/>
-    <col min="25" max="25" width="34.5703125" style="86" customWidth="1"/>
-    <col min="26" max="26" width="19.42578125" style="86" customWidth="1"/>
-    <col min="27" max="27" width="122.140625" style="86" customWidth="1"/>
-    <col min="28" max="28" width="122.42578125" style="86" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="86" customWidth="1"/>
-    <col min="30" max="30" width="22.140625" style="86" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="86" bestFit="1" customWidth="1"/>
-    <col min="32" max="71" width="16" style="86" customWidth="1"/>
-    <col min="72" max="16384" width="125.7109375" style="86"/>
+    <col min="1" max="1" width="5.85546875" style="80" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="80" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="80" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="121.42578125" style="80" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="80" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" style="80" customWidth="1"/>
+    <col min="8" max="8" width="51" style="80" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" style="80" customWidth="1"/>
+    <col min="10" max="10" width="12" style="80" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="80" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="80" customWidth="1"/>
+    <col min="13" max="13" width="24.42578125" style="80" customWidth="1"/>
+    <col min="14" max="14" width="34.7109375" style="80" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" style="80" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" style="80" customWidth="1"/>
+    <col min="17" max="17" width="24.85546875" style="80" customWidth="1"/>
+    <col min="18" max="18" width="7.5703125" style="80" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" style="80" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" style="80" customWidth="1"/>
+    <col min="21" max="21" width="20.5703125" style="80" customWidth="1"/>
+    <col min="22" max="22" width="19.85546875" style="80" customWidth="1"/>
+    <col min="23" max="23" width="11.85546875" style="80" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="80" customWidth="1"/>
+    <col min="25" max="25" width="34.5703125" style="80" customWidth="1"/>
+    <col min="26" max="26" width="19.42578125" style="80" customWidth="1"/>
+    <col min="27" max="27" width="122.140625" style="80" customWidth="1"/>
+    <col min="28" max="28" width="122.42578125" style="80" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="80" customWidth="1"/>
+    <col min="30" max="30" width="22.140625" style="80" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="80" bestFit="1" customWidth="1"/>
+    <col min="32" max="71" width="16" style="80" customWidth="1"/>
+    <col min="72" max="16384" width="125.7109375" style="80"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:53" ht="15" customHeight="1">
+      <c r="A1" s="75" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
+      <c r="Z1" s="76"/>
+      <c r="AA1" s="76"/>
+      <c r="AB1" s="76"/>
+      <c r="AC1" s="76"/>
+      <c r="AD1" s="76"/>
       <c r="AE1" s="14"/>
       <c r="AF1" s="14"/>
       <c r="AG1" s="14"/>
@@ -8152,37 +7957,37 @@
       <c r="AI1" s="14"/>
       <c r="AJ1" s="14"/>
     </row>
-    <row r="2" spans="1:53">
-      <c r="A2" s="83"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="84"/>
-      <c r="S2" s="84"/>
-      <c r="T2" s="84"/>
-      <c r="U2" s="84"/>
-      <c r="V2" s="84"/>
-      <c r="W2" s="84"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="84"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="84"/>
+    <row r="2" spans="1:53" ht="15" customHeight="1">
+      <c r="A2" s="77"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78"/>
+      <c r="Y2" s="78"/>
+      <c r="Z2" s="78"/>
+      <c r="AA2" s="78"/>
+      <c r="AB2" s="78"/>
+      <c r="AC2" s="78"/>
+      <c r="AD2" s="78"/>
       <c r="AE2" s="14"/>
       <c r="AF2" s="14"/>
       <c r="AG2" s="14"/>
@@ -8233,10 +8038,10 @@
       <c r="N3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="87" t="s">
+      <c r="O3" s="81" t="s">
         <v>440</v>
       </c>
-      <c r="P3" s="87" t="s">
+      <c r="P3" s="81" t="s">
         <v>441</v>
       </c>
       <c r="Q3" s="4" t="s">
@@ -8281,31 +8086,31 @@
       <c r="AD3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AE3" s="40" t="s">
+      <c r="AE3" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="41"/>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="41"/>
-      <c r="AV3" s="41"/>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="41"/>
-      <c r="BA3" s="41"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="39"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="39"/>
+      <c r="BA3" s="39"/>
     </row>
     <row r="4" spans="1:53">
       <c r="A4" s="6">
@@ -8320,10 +8125,10 @@
       <c r="D4" s="29" t="s">
         <v>421</v>
       </c>
-      <c r="E4" s="88" t="s">
+      <c r="E4" s="82" t="s">
         <v>422</v>
       </c>
-      <c r="F4" s="89">
+      <c r="F4" s="83">
         <v>21</v>
       </c>
       <c r="G4" s="24" t="s">
@@ -8347,24 +8152,24 @@
       <c r="M4" s="26">
         <v>46243</v>
       </c>
-      <c r="N4" s="90" t="s">
+      <c r="N4" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91">
+      <c r="O4" s="85"/>
+      <c r="P4" s="85">
         <f>ROUND(Q4/440000,0)</f>
         <v>23</v>
       </c>
       <c r="Q4" s="28">
         <v>10274588.380000001</v>
       </c>
-      <c r="R4" s="92">
+      <c r="R4" s="86">
         <v>0.99050000000000005</v>
       </c>
       <c r="S4" s="31">
         <v>8074695.25</v>
       </c>
-      <c r="T4" s="93">
+      <c r="T4" s="87">
         <f t="shared" ref="T4:T7" si="0">S4/Q4</f>
         <v>0.78588990150863824</v>
       </c>
@@ -8391,33 +8196,33 @@
       <c r="AB4" s="24" t="s">
         <v>426</v>
       </c>
-      <c r="AC4" s="94"/>
-      <c r="AD4" s="94"/>
-      <c r="AE4" s="126" t="s">
+      <c r="AC4" s="88"/>
+      <c r="AD4" s="88"/>
+      <c r="AE4" s="120" t="s">
         <v>542</v>
       </c>
-      <c r="AF4" s="124"/>
-      <c r="AG4" s="124"/>
-      <c r="AH4" s="124"/>
-      <c r="AI4" s="124"/>
-      <c r="AJ4" s="124"/>
-      <c r="AK4" s="124"/>
-      <c r="AL4" s="124"/>
-      <c r="AM4" s="124"/>
-      <c r="AN4" s="124"/>
-      <c r="AO4" s="124"/>
-      <c r="AP4" s="124"/>
-      <c r="AQ4" s="124"/>
-      <c r="AR4" s="124"/>
-      <c r="AS4" s="124"/>
-      <c r="AT4" s="124"/>
-      <c r="AU4" s="124"/>
-      <c r="AV4" s="124"/>
-      <c r="AW4" s="124"/>
-      <c r="AX4" s="124"/>
-      <c r="AY4" s="124"/>
-      <c r="AZ4" s="124"/>
-      <c r="BA4" s="124"/>
+      <c r="AF4" s="118"/>
+      <c r="AG4" s="118"/>
+      <c r="AH4" s="118"/>
+      <c r="AI4" s="118"/>
+      <c r="AJ4" s="118"/>
+      <c r="AK4" s="118"/>
+      <c r="AL4" s="118"/>
+      <c r="AM4" s="118"/>
+      <c r="AN4" s="118"/>
+      <c r="AO4" s="118"/>
+      <c r="AP4" s="118"/>
+      <c r="AQ4" s="118"/>
+      <c r="AR4" s="118"/>
+      <c r="AS4" s="118"/>
+      <c r="AT4" s="118"/>
+      <c r="AU4" s="118"/>
+      <c r="AV4" s="118"/>
+      <c r="AW4" s="118"/>
+      <c r="AX4" s="118"/>
+      <c r="AY4" s="118"/>
+      <c r="AZ4" s="118"/>
+      <c r="BA4" s="118"/>
     </row>
     <row r="5" spans="1:53">
       <c r="A5" s="6">
@@ -8433,16 +8238,16 @@
       <c r="D5" s="29" t="s">
         <v>428</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="57" t="s">
         <v>429</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="83">
         <v>17.7</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>430</v>
       </c>
-      <c r="H5" s="95" t="s">
+      <c r="H5" s="89" t="s">
         <v>99</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -8460,21 +8265,21 @@
       <c r="M5" s="27">
         <v>46164</v>
       </c>
-      <c r="N5" s="96" t="s">
+      <c r="N5" s="90" t="s">
         <v>26</v>
       </c>
       <c r="O5" s="24"/>
-      <c r="P5" s="95"/>
+      <c r="P5" s="89"/>
       <c r="Q5" s="28">
         <v>26205254.800000001</v>
       </c>
-      <c r="R5" s="92">
+      <c r="R5" s="86">
         <v>0.9516</v>
       </c>
       <c r="S5" s="31">
         <v>23148933.710000001</v>
       </c>
-      <c r="T5" s="93">
+      <c r="T5" s="87">
         <f t="shared" si="0"/>
         <v>0.88336991518204966</v>
       </c>
@@ -8483,7 +8288,7 @@
         <v>3056321.09</v>
       </c>
       <c r="V5" s="23"/>
-      <c r="W5" s="97" t="s">
+      <c r="W5" s="91" t="s">
         <v>431</v>
       </c>
       <c r="X5" s="23">
@@ -8492,10 +8297,10 @@
       <c r="Y5" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="Z5" s="98" t="s">
+      <c r="Z5" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="AA5" s="98" t="s">
+      <c r="AA5" s="92" t="s">
         <v>94</v>
       </c>
       <c r="AB5" s="24"/>
@@ -8503,31 +8308,31 @@
       <c r="AD5" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="AE5" s="126" t="s">
+      <c r="AE5" s="120" t="s">
         <v>543</v>
       </c>
-      <c r="AF5" s="124"/>
-      <c r="AG5" s="124"/>
-      <c r="AH5" s="124"/>
-      <c r="AI5" s="124"/>
-      <c r="AJ5" s="124"/>
-      <c r="AK5" s="124"/>
-      <c r="AL5" s="124"/>
-      <c r="AM5" s="124"/>
-      <c r="AN5" s="124"/>
-      <c r="AO5" s="124"/>
-      <c r="AP5" s="124"/>
-      <c r="AQ5" s="124"/>
-      <c r="AR5" s="124"/>
-      <c r="AS5" s="124"/>
-      <c r="AT5" s="124"/>
-      <c r="AU5" s="124"/>
-      <c r="AV5" s="125"/>
-      <c r="AW5" s="125"/>
-      <c r="AX5" s="125"/>
-      <c r="AY5" s="125"/>
-      <c r="AZ5" s="125"/>
-      <c r="BA5" s="125"/>
+      <c r="AF5" s="118"/>
+      <c r="AG5" s="118"/>
+      <c r="AH5" s="118"/>
+      <c r="AI5" s="118"/>
+      <c r="AJ5" s="118"/>
+      <c r="AK5" s="118"/>
+      <c r="AL5" s="118"/>
+      <c r="AM5" s="118"/>
+      <c r="AN5" s="118"/>
+      <c r="AO5" s="118"/>
+      <c r="AP5" s="118"/>
+      <c r="AQ5" s="118"/>
+      <c r="AR5" s="118"/>
+      <c r="AS5" s="118"/>
+      <c r="AT5" s="118"/>
+      <c r="AU5" s="118"/>
+      <c r="AV5" s="119"/>
+      <c r="AW5" s="119"/>
+      <c r="AX5" s="119"/>
+      <c r="AY5" s="119"/>
+      <c r="AZ5" s="119"/>
+      <c r="BA5" s="119"/>
     </row>
     <row r="6" spans="1:53" ht="30">
       <c r="A6" s="6">
@@ -8543,10 +8348,10 @@
       <c r="D6" s="29" t="s">
         <v>448</v>
       </c>
-      <c r="E6" s="99" t="s">
+      <c r="E6" s="93" t="s">
         <v>449</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="83">
         <v>27.4</v>
       </c>
       <c r="G6" s="24" t="s">
@@ -8571,21 +8376,21 @@
       <c r="N6" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="O6" s="95"/>
-      <c r="P6" s="91">
+      <c r="O6" s="89"/>
+      <c r="P6" s="85">
         <f t="shared" ref="P6:P11" si="3">ROUND(Q6/440000,0)</f>
         <v>291</v>
       </c>
       <c r="Q6" s="28">
         <v>127907115.28</v>
       </c>
-      <c r="R6" s="100">
+      <c r="R6" s="94">
         <v>0.89380000000000004</v>
       </c>
       <c r="S6" s="31">
         <v>95059747.680000007</v>
       </c>
-      <c r="T6" s="93">
+      <c r="T6" s="87">
         <f t="shared" si="0"/>
         <v>0.74319358600110563</v>
       </c>
@@ -8612,43 +8417,43 @@
       <c r="AB6" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="AC6" s="94"/>
-      <c r="AD6" s="94"/>
-      <c r="AE6" s="126" t="s">
+      <c r="AC6" s="88"/>
+      <c r="AD6" s="88"/>
+      <c r="AE6" s="120" t="s">
         <v>544</v>
       </c>
-      <c r="AF6" s="126" t="s">
+      <c r="AF6" s="120" t="s">
         <v>545</v>
       </c>
-      <c r="AG6" s="126" t="s">
+      <c r="AG6" s="120" t="s">
         <v>546</v>
       </c>
-      <c r="AH6" s="126" t="s">
+      <c r="AH6" s="120" t="s">
         <v>547</v>
       </c>
-      <c r="AI6" s="126" t="s">
+      <c r="AI6" s="120" t="s">
         <v>548</v>
       </c>
-      <c r="AJ6" s="126" t="s">
+      <c r="AJ6" s="120" t="s">
         <v>549</v>
       </c>
-      <c r="AK6" s="124"/>
-      <c r="AL6" s="124"/>
-      <c r="AM6" s="124"/>
-      <c r="AN6" s="124"/>
-      <c r="AO6" s="124"/>
-      <c r="AP6" s="124"/>
-      <c r="AQ6" s="124"/>
-      <c r="AR6" s="124"/>
-      <c r="AS6" s="124"/>
-      <c r="AT6" s="124"/>
-      <c r="AU6" s="124"/>
-      <c r="AV6" s="125"/>
-      <c r="AW6" s="125"/>
-      <c r="AX6" s="125"/>
-      <c r="AY6" s="125"/>
-      <c r="AZ6" s="125"/>
-      <c r="BA6" s="125"/>
+      <c r="AK6" s="118"/>
+      <c r="AL6" s="118"/>
+      <c r="AM6" s="118"/>
+      <c r="AN6" s="118"/>
+      <c r="AO6" s="118"/>
+      <c r="AP6" s="118"/>
+      <c r="AQ6" s="118"/>
+      <c r="AR6" s="118"/>
+      <c r="AS6" s="118"/>
+      <c r="AT6" s="118"/>
+      <c r="AU6" s="118"/>
+      <c r="AV6" s="119"/>
+      <c r="AW6" s="119"/>
+      <c r="AX6" s="119"/>
+      <c r="AY6" s="119"/>
+      <c r="AZ6" s="119"/>
+      <c r="BA6" s="119"/>
     </row>
     <row r="7" spans="1:53" ht="45">
       <c r="A7" s="6">
@@ -8664,10 +8469,10 @@
       <c r="D7" s="29" t="s">
         <v>456</v>
       </c>
-      <c r="E7" s="99" t="s">
+      <c r="E7" s="93" t="s">
         <v>457</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="83">
         <v>7.45</v>
       </c>
       <c r="G7" s="24" t="s">
@@ -8685,7 +8490,7 @@
       <c r="K7" s="11">
         <v>46151</v>
       </c>
-      <c r="L7" s="101">
+      <c r="L7" s="95">
         <v>46243</v>
       </c>
       <c r="M7" s="11">
@@ -8694,23 +8499,23 @@
       <c r="N7" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="O7" s="95">
+      <c r="O7" s="89">
         <v>123</v>
       </c>
-      <c r="P7" s="91">
+      <c r="P7" s="85">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="Q7" s="28">
         <v>46954308.259999998</v>
       </c>
-      <c r="R7" s="100">
+      <c r="R7" s="94">
         <v>0.90639999999999998</v>
       </c>
       <c r="S7" s="31">
         <v>40304273.969999999</v>
       </c>
-      <c r="T7" s="93">
+      <c r="T7" s="87">
         <f t="shared" si="0"/>
         <v>0.85837222320097284</v>
       </c>
@@ -8741,37 +8546,37 @@
       <c r="AD7" s="23" t="s">
         <v>461</v>
       </c>
-      <c r="AE7" s="126" t="s">
+      <c r="AE7" s="120" t="s">
         <v>550</v>
       </c>
-      <c r="AF7" s="126" t="s">
+      <c r="AF7" s="120" t="s">
         <v>551</v>
       </c>
-      <c r="AG7" s="126" t="s">
+      <c r="AG7" s="120" t="s">
         <v>552</v>
       </c>
-      <c r="AH7" s="126" t="s">
+      <c r="AH7" s="120" t="s">
         <v>553</v>
       </c>
-      <c r="AI7" s="124"/>
-      <c r="AJ7" s="124"/>
-      <c r="AK7" s="124"/>
-      <c r="AL7" s="124"/>
-      <c r="AM7" s="124"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="124"/>
-      <c r="AP7" s="124"/>
-      <c r="AQ7" s="124"/>
-      <c r="AR7" s="124"/>
-      <c r="AS7" s="124"/>
-      <c r="AT7" s="124"/>
-      <c r="AU7" s="124"/>
-      <c r="AV7" s="125"/>
-      <c r="AW7" s="125"/>
-      <c r="AX7" s="125"/>
-      <c r="AY7" s="125"/>
-      <c r="AZ7" s="125"/>
-      <c r="BA7" s="125"/>
+      <c r="AI7" s="118"/>
+      <c r="AJ7" s="118"/>
+      <c r="AK7" s="118"/>
+      <c r="AL7" s="118"/>
+      <c r="AM7" s="118"/>
+      <c r="AN7" s="118"/>
+      <c r="AO7" s="118"/>
+      <c r="AP7" s="118"/>
+      <c r="AQ7" s="118"/>
+      <c r="AR7" s="118"/>
+      <c r="AS7" s="118"/>
+      <c r="AT7" s="118"/>
+      <c r="AU7" s="118"/>
+      <c r="AV7" s="119"/>
+      <c r="AW7" s="119"/>
+      <c r="AX7" s="119"/>
+      <c r="AY7" s="119"/>
+      <c r="AZ7" s="119"/>
+      <c r="BA7" s="119"/>
     </row>
     <row r="8" spans="1:53">
       <c r="A8" s="6">
@@ -8787,10 +8592,10 @@
       <c r="D8" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="E8" s="88" t="s">
+      <c r="E8" s="82" t="s">
         <v>463</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="83">
         <v>26.2</v>
       </c>
       <c r="G8" s="24" t="s">
@@ -8814,18 +8619,18 @@
       <c r="M8" s="26">
         <v>46022</v>
       </c>
-      <c r="N8" s="102" t="s">
+      <c r="N8" s="96" t="s">
         <v>466</v>
       </c>
-      <c r="O8" s="91"/>
-      <c r="P8" s="91">
+      <c r="O8" s="85"/>
+      <c r="P8" s="85">
         <f t="shared" si="3"/>
         <v>195</v>
       </c>
       <c r="Q8" s="28">
         <v>85744229.950000003</v>
       </c>
-      <c r="R8" s="100">
+      <c r="R8" s="94">
         <v>0.39419999999999999</v>
       </c>
       <c r="S8" s="31"/>
@@ -8853,45 +8658,45 @@
       <c r="AB8" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="AC8" s="103"/>
-      <c r="AD8" s="103" t="s">
+      <c r="AC8" s="97"/>
+      <c r="AD8" s="97" t="s">
         <v>471</v>
       </c>
-      <c r="AE8" s="126" t="s">
+      <c r="AE8" s="120" t="s">
         <v>554</v>
       </c>
-      <c r="AF8" s="126" t="s">
+      <c r="AF8" s="120" t="s">
         <v>555</v>
       </c>
-      <c r="AG8" s="126" t="s">
+      <c r="AG8" s="120" t="s">
         <v>556</v>
       </c>
-      <c r="AH8" s="126" t="s">
+      <c r="AH8" s="120" t="s">
         <v>557</v>
       </c>
-      <c r="AI8" s="126" t="s">
+      <c r="AI8" s="120" t="s">
         <v>558</v>
       </c>
-      <c r="AJ8" s="126" t="s">
+      <c r="AJ8" s="120" t="s">
         <v>559</v>
       </c>
-      <c r="AK8" s="124"/>
-      <c r="AL8" s="124"/>
-      <c r="AM8" s="124"/>
-      <c r="AN8" s="124"/>
-      <c r="AO8" s="124"/>
-      <c r="AP8" s="124"/>
-      <c r="AQ8" s="124"/>
-      <c r="AR8" s="124"/>
-      <c r="AS8" s="124"/>
-      <c r="AT8" s="124"/>
-      <c r="AU8" s="124"/>
-      <c r="AV8" s="125"/>
-      <c r="AW8" s="125"/>
-      <c r="AX8" s="125"/>
-      <c r="AY8" s="125"/>
-      <c r="AZ8" s="125"/>
-      <c r="BA8" s="125"/>
+      <c r="AK8" s="118"/>
+      <c r="AL8" s="118"/>
+      <c r="AM8" s="118"/>
+      <c r="AN8" s="118"/>
+      <c r="AO8" s="118"/>
+      <c r="AP8" s="118"/>
+      <c r="AQ8" s="118"/>
+      <c r="AR8" s="118"/>
+      <c r="AS8" s="118"/>
+      <c r="AT8" s="118"/>
+      <c r="AU8" s="118"/>
+      <c r="AV8" s="119"/>
+      <c r="AW8" s="119"/>
+      <c r="AX8" s="119"/>
+      <c r="AY8" s="119"/>
+      <c r="AZ8" s="119"/>
+      <c r="BA8" s="119"/>
     </row>
     <row r="9" spans="1:53" ht="45">
       <c r="A9" s="6">
@@ -8907,10 +8712,10 @@
       <c r="D9" s="29" t="s">
         <v>473</v>
       </c>
-      <c r="E9" s="88" t="s">
+      <c r="E9" s="82" t="s">
         <v>463</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="83">
         <f>1.24+7.4</f>
         <v>8.64</v>
       </c>
@@ -8933,26 +8738,26 @@
         <v>46213</v>
       </c>
       <c r="M9" s="26"/>
-      <c r="N9" s="90" t="s">
+      <c r="N9" s="84" t="s">
         <v>451</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="89">
         <v>28</v>
       </c>
-      <c r="P9" s="91">
+      <c r="P9" s="85">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="98">
         <v>15066305.51</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="94">
         <v>0.68659999999999999</v>
       </c>
       <c r="S9" s="31">
         <v>7842260.7599999998</v>
       </c>
-      <c r="T9" s="93">
+      <c r="T9" s="87">
         <f t="shared" ref="T9:T11" si="4">S9/Q9</f>
         <v>0.52051650982351549</v>
       </c>
@@ -8979,33 +8784,33 @@
       <c r="AB9" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="AC9" s="94"/>
-      <c r="AD9" s="94"/>
-      <c r="AE9" s="126" t="s">
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="120" t="s">
         <v>560</v>
       </c>
-      <c r="AF9" s="124"/>
-      <c r="AG9" s="124"/>
-      <c r="AH9" s="124"/>
-      <c r="AI9" s="124"/>
-      <c r="AJ9" s="124"/>
-      <c r="AK9" s="124"/>
-      <c r="AL9" s="124"/>
-      <c r="AM9" s="124"/>
-      <c r="AN9" s="124"/>
-      <c r="AO9" s="124"/>
-      <c r="AP9" s="124"/>
-      <c r="AQ9" s="124"/>
-      <c r="AR9" s="124"/>
-      <c r="AS9" s="124"/>
-      <c r="AT9" s="124"/>
-      <c r="AU9" s="124"/>
-      <c r="AV9" s="125"/>
-      <c r="AW9" s="125"/>
-      <c r="AX9" s="125"/>
-      <c r="AY9" s="125"/>
-      <c r="AZ9" s="125"/>
-      <c r="BA9" s="125"/>
+      <c r="AF9" s="118"/>
+      <c r="AG9" s="118"/>
+      <c r="AH9" s="118"/>
+      <c r="AI9" s="118"/>
+      <c r="AJ9" s="118"/>
+      <c r="AK9" s="118"/>
+      <c r="AL9" s="118"/>
+      <c r="AM9" s="118"/>
+      <c r="AN9" s="118"/>
+      <c r="AO9" s="118"/>
+      <c r="AP9" s="118"/>
+      <c r="AQ9" s="118"/>
+      <c r="AR9" s="118"/>
+      <c r="AS9" s="118"/>
+      <c r="AT9" s="118"/>
+      <c r="AU9" s="118"/>
+      <c r="AV9" s="119"/>
+      <c r="AW9" s="119"/>
+      <c r="AX9" s="119"/>
+      <c r="AY9" s="119"/>
+      <c r="AZ9" s="119"/>
+      <c r="BA9" s="119"/>
     </row>
     <row r="10" spans="1:53" ht="45">
       <c r="A10" s="6">
@@ -9021,10 +8826,10 @@
       <c r="D10" s="29" t="s">
         <v>477</v>
       </c>
-      <c r="E10" s="88" t="s">
+      <c r="E10" s="82" t="s">
         <v>478</v>
       </c>
-      <c r="F10" s="89">
+      <c r="F10" s="83">
         <v>1.62</v>
       </c>
       <c r="G10" s="24" t="s">
@@ -9049,23 +8854,23 @@
       <c r="N10" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="O10" s="95">
+      <c r="O10" s="89">
         <v>22</v>
       </c>
-      <c r="P10" s="91">
+      <c r="P10" s="85">
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="99">
         <v>16172108.65</v>
       </c>
-      <c r="R10" s="100">
+      <c r="R10" s="94">
         <v>0.96209999999999996</v>
       </c>
       <c r="S10" s="31">
         <v>13441036.810000001</v>
       </c>
-      <c r="T10" s="93">
+      <c r="T10" s="87">
         <f t="shared" si="4"/>
         <v>0.83112456766730913</v>
       </c>
@@ -9094,31 +8899,31 @@
       </c>
       <c r="AC10" s="24"/>
       <c r="AD10" s="24"/>
-      <c r="AE10" s="126" t="s">
+      <c r="AE10" s="120" t="s">
         <v>561</v>
       </c>
-      <c r="AF10" s="124"/>
-      <c r="AG10" s="124"/>
-      <c r="AH10" s="124"/>
-      <c r="AI10" s="124"/>
-      <c r="AJ10" s="124"/>
-      <c r="AK10" s="124"/>
-      <c r="AL10" s="124"/>
-      <c r="AM10" s="124"/>
-      <c r="AN10" s="124"/>
-      <c r="AO10" s="124"/>
-      <c r="AP10" s="124"/>
-      <c r="AQ10" s="124"/>
-      <c r="AR10" s="124"/>
-      <c r="AS10" s="124"/>
-      <c r="AT10" s="124"/>
-      <c r="AU10" s="124"/>
-      <c r="AV10" s="125"/>
-      <c r="AW10" s="125"/>
-      <c r="AX10" s="125"/>
-      <c r="AY10" s="125"/>
-      <c r="AZ10" s="125"/>
-      <c r="BA10" s="125"/>
+      <c r="AF10" s="118"/>
+      <c r="AG10" s="118"/>
+      <c r="AH10" s="118"/>
+      <c r="AI10" s="118"/>
+      <c r="AJ10" s="118"/>
+      <c r="AK10" s="118"/>
+      <c r="AL10" s="118"/>
+      <c r="AM10" s="118"/>
+      <c r="AN10" s="118"/>
+      <c r="AO10" s="118"/>
+      <c r="AP10" s="118"/>
+      <c r="AQ10" s="118"/>
+      <c r="AR10" s="118"/>
+      <c r="AS10" s="118"/>
+      <c r="AT10" s="118"/>
+      <c r="AU10" s="118"/>
+      <c r="AV10" s="119"/>
+      <c r="AW10" s="119"/>
+      <c r="AX10" s="119"/>
+      <c r="AY10" s="119"/>
+      <c r="AZ10" s="119"/>
+      <c r="BA10" s="119"/>
     </row>
     <row r="11" spans="1:53" ht="45">
       <c r="A11" s="6">
@@ -9128,19 +8933,19 @@
       <c r="B11" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="91" t="s">
         <v>482</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="100" t="s">
         <v>483</v>
       </c>
-      <c r="E11" s="88" t="s">
+      <c r="E11" s="82" t="s">
         <v>478</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="83">
         <v>32.299999999999997</v>
       </c>
-      <c r="G11" s="107" t="s">
+      <c r="G11" s="101" t="s">
         <v>385</v>
       </c>
       <c r="H11" s="6" t="s">
@@ -9162,21 +8967,21 @@
       <c r="N11" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="O11" s="95"/>
-      <c r="P11" s="91">
+      <c r="O11" s="89"/>
+      <c r="P11" s="85">
         <f t="shared" si="3"/>
         <v>231</v>
       </c>
-      <c r="Q11" s="108">
+      <c r="Q11" s="102">
         <v>101477225.48</v>
       </c>
-      <c r="R11" s="100">
+      <c r="R11" s="94">
         <v>0.22720000000000001</v>
       </c>
       <c r="S11" s="31">
         <v>23053445.82</v>
       </c>
-      <c r="T11" s="93">
+      <c r="T11" s="87">
         <f t="shared" si="4"/>
         <v>0.22717851922886451</v>
       </c>
@@ -9185,73 +8990,73 @@
         <v>78423779.659999996</v>
       </c>
       <c r="V11" s="28"/>
-      <c r="W11" s="97" t="s">
+      <c r="W11" s="91" t="s">
         <v>484</v>
       </c>
-      <c r="X11" s="97">
+      <c r="X11" s="91">
         <v>12</v>
       </c>
       <c r="Y11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="96" t="s">
+      <c r="Z11" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="AA11" s="96" t="s">
+      <c r="AA11" s="90" t="s">
         <v>485</v>
       </c>
       <c r="AB11" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="AC11" s="107"/>
-      <c r="AD11" s="107"/>
-      <c r="AE11" s="126" t="s">
+      <c r="AC11" s="101"/>
+      <c r="AD11" s="101"/>
+      <c r="AE11" s="120" t="s">
         <v>565</v>
       </c>
-      <c r="AF11" s="126" t="s">
+      <c r="AF11" s="120" t="s">
         <v>566</v>
       </c>
-      <c r="AG11" s="126" t="s">
+      <c r="AG11" s="120" t="s">
         <v>567</v>
       </c>
-      <c r="AH11" s="126" t="s">
+      <c r="AH11" s="120" t="s">
         <v>568</v>
       </c>
-      <c r="AI11" s="126" t="s">
+      <c r="AI11" s="120" t="s">
         <v>569</v>
       </c>
-      <c r="AJ11" s="126" t="s">
+      <c r="AJ11" s="120" t="s">
         <v>570</v>
       </c>
-      <c r="AK11" s="126" t="s">
+      <c r="AK11" s="120" t="s">
         <v>572</v>
       </c>
-      <c r="AL11" s="126" t="s">
+      <c r="AL11" s="120" t="s">
         <v>571</v>
       </c>
-      <c r="AM11" s="126" t="s">
+      <c r="AM11" s="120" t="s">
         <v>573</v>
       </c>
-      <c r="AN11" s="126" t="s">
+      <c r="AN11" s="120" t="s">
         <v>574</v>
       </c>
-      <c r="AO11" s="126" t="s">
+      <c r="AO11" s="120" t="s">
         <v>576</v>
       </c>
-      <c r="AP11" s="126" t="s">
+      <c r="AP11" s="120" t="s">
         <v>575</v>
       </c>
-      <c r="AQ11" s="124"/>
-      <c r="AR11" s="124"/>
-      <c r="AS11" s="124"/>
-      <c r="AT11" s="124"/>
-      <c r="AU11" s="124"/>
-      <c r="AV11" s="125"/>
-      <c r="AW11" s="125"/>
-      <c r="AX11" s="125"/>
-      <c r="AY11" s="125"/>
-      <c r="AZ11" s="125"/>
-      <c r="BA11" s="125"/>
+      <c r="AQ11" s="118"/>
+      <c r="AR11" s="118"/>
+      <c r="AS11" s="118"/>
+      <c r="AT11" s="118"/>
+      <c r="AU11" s="118"/>
+      <c r="AV11" s="119"/>
+      <c r="AW11" s="119"/>
+      <c r="AX11" s="119"/>
+      <c r="AY11" s="119"/>
+      <c r="AZ11" s="119"/>
+      <c r="BA11" s="119"/>
     </row>
     <row r="12" spans="1:53" ht="30">
       <c r="A12" s="6">
@@ -9261,16 +9066,16 @@
       <c r="B12" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="C12" s="107" t="s">
+      <c r="C12" s="101" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="106" t="s">
+      <c r="D12" s="100" t="s">
         <v>487</v>
       </c>
-      <c r="E12" s="109" t="s">
+      <c r="E12" s="103" t="s">
         <v>488</v>
       </c>
-      <c r="F12" s="89">
+      <c r="F12" s="83">
         <v>5.19</v>
       </c>
       <c r="G12" s="7" t="s">
@@ -9285,22 +9090,22 @@
       <c r="J12" s="10">
         <v>45797</v>
       </c>
-      <c r="K12" s="110">
+      <c r="K12" s="104">
         <v>46312</v>
       </c>
-      <c r="L12" s="111">
+      <c r="L12" s="105">
         <v>46312</v>
       </c>
-      <c r="M12" s="110"/>
+      <c r="M12" s="104"/>
       <c r="N12" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="O12" s="112"/>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="113">
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="107">
         <v>41900000</v>
       </c>
-      <c r="R12" s="100">
+      <c r="R12" s="94">
         <v>4.1000000000000003E-3</v>
       </c>
       <c r="S12" s="31">
@@ -9313,52 +9118,52 @@
         <f t="shared" si="1"/>
         <v>41900000</v>
       </c>
-      <c r="V12" s="114"/>
-      <c r="W12" s="114" t="s">
+      <c r="V12" s="108"/>
+      <c r="W12" s="108" t="s">
         <v>489</v>
       </c>
-      <c r="X12" s="114">
+      <c r="X12" s="108">
         <v>3025</v>
       </c>
       <c r="Y12" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="Z12" s="115"/>
-      <c r="AA12" s="115" t="s">
+      <c r="Z12" s="109"/>
+      <c r="AA12" s="109" t="s">
         <v>318</v>
       </c>
       <c r="AB12" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="AC12" s="115"/>
-      <c r="AD12" s="115"/>
-      <c r="AE12" s="127" t="s">
+      <c r="AC12" s="109"/>
+      <c r="AD12" s="109"/>
+      <c r="AE12" s="121" t="s">
         <v>577</v>
       </c>
-      <c r="AF12" s="127" t="s">
+      <c r="AF12" s="121" t="s">
         <v>578</v>
       </c>
-      <c r="AG12" s="124"/>
-      <c r="AH12" s="124"/>
-      <c r="AI12" s="124"/>
-      <c r="AJ12" s="124"/>
-      <c r="AK12" s="124"/>
-      <c r="AL12" s="124"/>
-      <c r="AM12" s="124"/>
-      <c r="AN12" s="124"/>
-      <c r="AO12" s="124"/>
-      <c r="AP12" s="124"/>
-      <c r="AQ12" s="124"/>
-      <c r="AR12" s="124"/>
-      <c r="AS12" s="124"/>
-      <c r="AT12" s="124"/>
-      <c r="AU12" s="124"/>
-      <c r="AV12" s="125"/>
-      <c r="AW12" s="125"/>
-      <c r="AX12" s="125"/>
-      <c r="AY12" s="125"/>
-      <c r="AZ12" s="125"/>
-      <c r="BA12" s="125"/>
+      <c r="AG12" s="118"/>
+      <c r="AH12" s="118"/>
+      <c r="AI12" s="118"/>
+      <c r="AJ12" s="118"/>
+      <c r="AK12" s="118"/>
+      <c r="AL12" s="118"/>
+      <c r="AM12" s="118"/>
+      <c r="AN12" s="118"/>
+      <c r="AO12" s="118"/>
+      <c r="AP12" s="118"/>
+      <c r="AQ12" s="118"/>
+      <c r="AR12" s="118"/>
+      <c r="AS12" s="118"/>
+      <c r="AT12" s="118"/>
+      <c r="AU12" s="118"/>
+      <c r="AV12" s="119"/>
+      <c r="AW12" s="119"/>
+      <c r="AX12" s="119"/>
+      <c r="AY12" s="119"/>
+      <c r="AZ12" s="119"/>
+      <c r="BA12" s="119"/>
     </row>
     <row r="13" spans="1:53" ht="28.5">
       <c r="A13" s="6">
@@ -9374,10 +9179,10 @@
       <c r="D13" s="29" t="s">
         <v>492</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="E13" s="82" t="s">
         <v>493</v>
       </c>
-      <c r="F13" s="89">
+      <c r="F13" s="83">
         <v>5.56</v>
       </c>
       <c r="G13" s="24" t="s">
@@ -9402,21 +9207,21 @@
       <c r="N13" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="O13" s="95"/>
-      <c r="P13" s="91">
+      <c r="O13" s="89"/>
+      <c r="P13" s="85">
         <f t="shared" ref="P13:P16" si="5">ROUND(Q13/440000,0)</f>
         <v>19</v>
       </c>
       <c r="Q13" s="28">
         <v>8472744.1500000004</v>
       </c>
-      <c r="R13" s="116">
+      <c r="R13" s="110">
         <v>21.62</v>
       </c>
       <c r="S13" s="31">
         <v>1831407.42</v>
       </c>
-      <c r="T13" s="93">
+      <c r="T13" s="87">
         <f t="shared" ref="T13:T20" si="6">S13/Q13</f>
         <v>0.21615280569991008</v>
       </c>
@@ -9443,37 +9248,37 @@
       <c r="AB13" s="24" t="s">
         <v>497</v>
       </c>
-      <c r="AC13" s="85"/>
-      <c r="AD13" s="85" t="s">
+      <c r="AC13" s="79"/>
+      <c r="AD13" s="79" t="s">
         <v>498</v>
       </c>
-      <c r="AE13" s="126" t="s">
+      <c r="AE13" s="120" t="s">
         <v>579</v>
       </c>
-      <c r="AF13" s="126" t="s">
+      <c r="AF13" s="120" t="s">
         <v>562</v>
       </c>
-      <c r="AG13" s="124"/>
-      <c r="AH13" s="124"/>
-      <c r="AI13" s="124"/>
-      <c r="AJ13" s="124"/>
-      <c r="AK13" s="124"/>
-      <c r="AL13" s="124"/>
-      <c r="AM13" s="124"/>
-      <c r="AN13" s="124"/>
-      <c r="AO13" s="124"/>
-      <c r="AP13" s="124"/>
-      <c r="AQ13" s="124"/>
-      <c r="AR13" s="124"/>
-      <c r="AS13" s="124"/>
-      <c r="AT13" s="124"/>
-      <c r="AU13" s="124"/>
-      <c r="AV13" s="125"/>
-      <c r="AW13" s="125"/>
-      <c r="AX13" s="125"/>
-      <c r="AY13" s="125"/>
-      <c r="AZ13" s="125"/>
-      <c r="BA13" s="125"/>
+      <c r="AG13" s="118"/>
+      <c r="AH13" s="118"/>
+      <c r="AI13" s="118"/>
+      <c r="AJ13" s="118"/>
+      <c r="AK13" s="118"/>
+      <c r="AL13" s="118"/>
+      <c r="AM13" s="118"/>
+      <c r="AN13" s="118"/>
+      <c r="AO13" s="118"/>
+      <c r="AP13" s="118"/>
+      <c r="AQ13" s="118"/>
+      <c r="AR13" s="118"/>
+      <c r="AS13" s="118"/>
+      <c r="AT13" s="118"/>
+      <c r="AU13" s="118"/>
+      <c r="AV13" s="119"/>
+      <c r="AW13" s="119"/>
+      <c r="AX13" s="119"/>
+      <c r="AY13" s="119"/>
+      <c r="AZ13" s="119"/>
+      <c r="BA13" s="119"/>
     </row>
     <row r="14" spans="1:53">
       <c r="A14" s="6">
@@ -9489,10 +9294,10 @@
       <c r="D14" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="E14" s="117" t="s">
+      <c r="E14" s="111" t="s">
         <v>429</v>
       </c>
-      <c r="F14" s="89">
+      <c r="F14" s="83">
         <v>25.7</v>
       </c>
       <c r="G14" s="7" t="s">
@@ -9517,21 +9322,21 @@
       <c r="N14" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="O14" s="118"/>
-      <c r="P14" s="91">
+      <c r="O14" s="112"/>
+      <c r="P14" s="85">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
       <c r="Q14" s="28">
         <v>23085365.16</v>
       </c>
-      <c r="R14" s="92">
+      <c r="R14" s="86">
         <v>0.85729999999999995</v>
       </c>
       <c r="S14" s="31">
         <v>19790619.449999999</v>
       </c>
-      <c r="T14" s="93">
+      <c r="T14" s="87">
         <f t="shared" si="6"/>
         <v>0.85727989628213441</v>
       </c>
@@ -9540,7 +9345,7 @@
         <v>3294745.7100000009</v>
       </c>
       <c r="V14" s="28"/>
-      <c r="W14" s="119" t="s">
+      <c r="W14" s="113" t="s">
         <v>503</v>
       </c>
       <c r="X14" s="6">
@@ -9556,35 +9361,35 @@
         <v>504</v>
       </c>
       <c r="AB14" s="7"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="96" t="s">
+      <c r="AC14" s="90"/>
+      <c r="AD14" s="90" t="s">
         <v>505</v>
       </c>
-      <c r="AE14" s="126" t="s">
+      <c r="AE14" s="120" t="s">
         <v>563</v>
       </c>
-      <c r="AF14" s="124"/>
-      <c r="AG14" s="124"/>
-      <c r="AH14" s="124"/>
-      <c r="AI14" s="124"/>
-      <c r="AJ14" s="124"/>
-      <c r="AK14" s="124"/>
-      <c r="AL14" s="124"/>
-      <c r="AM14" s="124"/>
-      <c r="AN14" s="124"/>
-      <c r="AO14" s="124"/>
-      <c r="AP14" s="124"/>
-      <c r="AQ14" s="124"/>
-      <c r="AR14" s="124"/>
-      <c r="AS14" s="124"/>
-      <c r="AT14" s="124"/>
-      <c r="AU14" s="124"/>
-      <c r="AV14" s="125"/>
-      <c r="AW14" s="125"/>
-      <c r="AX14" s="125"/>
-      <c r="AY14" s="125"/>
-      <c r="AZ14" s="125"/>
-      <c r="BA14" s="125"/>
+      <c r="AF14" s="118"/>
+      <c r="AG14" s="118"/>
+      <c r="AH14" s="118"/>
+      <c r="AI14" s="118"/>
+      <c r="AJ14" s="118"/>
+      <c r="AK14" s="118"/>
+      <c r="AL14" s="118"/>
+      <c r="AM14" s="118"/>
+      <c r="AN14" s="118"/>
+      <c r="AO14" s="118"/>
+      <c r="AP14" s="118"/>
+      <c r="AQ14" s="118"/>
+      <c r="AR14" s="118"/>
+      <c r="AS14" s="118"/>
+      <c r="AT14" s="118"/>
+      <c r="AU14" s="118"/>
+      <c r="AV14" s="119"/>
+      <c r="AW14" s="119"/>
+      <c r="AX14" s="119"/>
+      <c r="AY14" s="119"/>
+      <c r="AZ14" s="119"/>
+      <c r="BA14" s="119"/>
     </row>
     <row r="15" spans="1:53">
       <c r="A15" s="6">
@@ -9600,10 +9405,10 @@
       <c r="D15" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="E15" s="117" t="s">
+      <c r="E15" s="111" t="s">
         <v>507</v>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="83">
         <v>36.61</v>
       </c>
       <c r="G15" s="7" t="s">
@@ -9625,26 +9430,26 @@
         <v>46147</v>
       </c>
       <c r="M15" s="26"/>
-      <c r="N15" s="120" t="s">
+      <c r="N15" s="114" t="s">
         <v>451</v>
       </c>
-      <c r="O15" s="118">
+      <c r="O15" s="112">
         <v>15</v>
       </c>
-      <c r="P15" s="91">
+      <c r="P15" s="85">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
       <c r="Q15" s="12">
         <v>39663580.009999998</v>
       </c>
-      <c r="R15" s="92">
+      <c r="R15" s="86">
         <v>0.94550000000000001</v>
       </c>
       <c r="S15" s="31">
         <v>37501021.159999996</v>
       </c>
-      <c r="T15" s="93">
+      <c r="T15" s="87">
         <f t="shared" si="6"/>
         <v>0.94547746699983271</v>
       </c>
@@ -9673,31 +9478,31 @@
       <c r="AD15" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="AE15" s="126" t="s">
+      <c r="AE15" s="120" t="s">
         <v>580</v>
       </c>
-      <c r="AF15" s="124"/>
-      <c r="AG15" s="124"/>
-      <c r="AH15" s="124"/>
-      <c r="AI15" s="124"/>
-      <c r="AJ15" s="124"/>
-      <c r="AK15" s="124"/>
-      <c r="AL15" s="124"/>
-      <c r="AM15" s="124"/>
-      <c r="AN15" s="124"/>
-      <c r="AO15" s="124"/>
-      <c r="AP15" s="124"/>
-      <c r="AQ15" s="124"/>
-      <c r="AR15" s="124"/>
-      <c r="AS15" s="124"/>
-      <c r="AT15" s="124"/>
-      <c r="AU15" s="124"/>
-      <c r="AV15" s="125"/>
-      <c r="AW15" s="125"/>
-      <c r="AX15" s="125"/>
-      <c r="AY15" s="125"/>
-      <c r="AZ15" s="125"/>
-      <c r="BA15" s="125"/>
+      <c r="AF15" s="118"/>
+      <c r="AG15" s="118"/>
+      <c r="AH15" s="118"/>
+      <c r="AI15" s="118"/>
+      <c r="AJ15" s="118"/>
+      <c r="AK15" s="118"/>
+      <c r="AL15" s="118"/>
+      <c r="AM15" s="118"/>
+      <c r="AN15" s="118"/>
+      <c r="AO15" s="118"/>
+      <c r="AP15" s="118"/>
+      <c r="AQ15" s="118"/>
+      <c r="AR15" s="118"/>
+      <c r="AS15" s="118"/>
+      <c r="AT15" s="118"/>
+      <c r="AU15" s="118"/>
+      <c r="AV15" s="119"/>
+      <c r="AW15" s="119"/>
+      <c r="AX15" s="119"/>
+      <c r="AY15" s="119"/>
+      <c r="AZ15" s="119"/>
+      <c r="BA15" s="119"/>
     </row>
     <row r="16" spans="1:53" ht="30">
       <c r="A16" s="6">
@@ -9713,10 +9518,10 @@
       <c r="D16" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="E16" s="117" t="s">
+      <c r="E16" s="111" t="s">
         <v>463</v>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="83">
         <v>16.75</v>
       </c>
       <c r="G16" s="7" t="s">
@@ -9741,21 +9546,21 @@
       <c r="N16" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="O16" s="118"/>
-      <c r="P16" s="91">
+      <c r="O16" s="112"/>
+      <c r="P16" s="85">
         <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="Q16" s="12">
         <v>21525552.93</v>
       </c>
-      <c r="R16" s="92">
+      <c r="R16" s="86">
         <v>0.92110000000000003</v>
       </c>
       <c r="S16" s="31">
         <v>19473393.359999999</v>
       </c>
-      <c r="T16" s="93">
+      <c r="T16" s="87">
         <f t="shared" si="6"/>
         <v>0.90466402527853673</v>
       </c>
@@ -9779,40 +9584,40 @@
       <c r="AA16" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="AB16" s="96" t="s">
+      <c r="AB16" s="90" t="s">
         <v>517</v>
       </c>
       <c r="AC16" s="24"/>
       <c r="AD16" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="AE16" s="126" t="s">
+      <c r="AE16" s="120" t="s">
         <v>582</v>
       </c>
-      <c r="AF16" s="126" t="s">
+      <c r="AF16" s="120" t="s">
         <v>581</v>
       </c>
-      <c r="AG16" s="124"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="124"/>
-      <c r="AJ16" s="124"/>
-      <c r="AK16" s="124"/>
-      <c r="AL16" s="124"/>
-      <c r="AM16" s="124"/>
-      <c r="AN16" s="124"/>
-      <c r="AO16" s="124"/>
-      <c r="AP16" s="124"/>
-      <c r="AQ16" s="124"/>
-      <c r="AR16" s="124"/>
-      <c r="AS16" s="124"/>
-      <c r="AT16" s="124"/>
-      <c r="AU16" s="124"/>
-      <c r="AV16" s="125"/>
-      <c r="AW16" s="125"/>
-      <c r="AX16" s="125"/>
-      <c r="AY16" s="125"/>
-      <c r="AZ16" s="125"/>
-      <c r="BA16" s="125"/>
+      <c r="AG16" s="118"/>
+      <c r="AH16" s="118"/>
+      <c r="AI16" s="118"/>
+      <c r="AJ16" s="118"/>
+      <c r="AK16" s="118"/>
+      <c r="AL16" s="118"/>
+      <c r="AM16" s="118"/>
+      <c r="AN16" s="118"/>
+      <c r="AO16" s="118"/>
+      <c r="AP16" s="118"/>
+      <c r="AQ16" s="118"/>
+      <c r="AR16" s="118"/>
+      <c r="AS16" s="118"/>
+      <c r="AT16" s="118"/>
+      <c r="AU16" s="118"/>
+      <c r="AV16" s="119"/>
+      <c r="AW16" s="119"/>
+      <c r="AX16" s="119"/>
+      <c r="AY16" s="119"/>
+      <c r="AZ16" s="119"/>
+      <c r="BA16" s="119"/>
     </row>
     <row r="17" spans="1:53" ht="45">
       <c r="A17" s="6">
@@ -9828,10 +9633,10 @@
       <c r="D17" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="E17" s="117" t="s">
+      <c r="E17" s="111" t="s">
         <v>488</v>
       </c>
-      <c r="F17" s="89">
+      <c r="F17" s="83">
         <v>2.2000000000000002</v>
       </c>
       <c r="G17" s="7" t="s">
@@ -9856,18 +9661,18 @@
       <c r="N17" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="O17" s="118"/>
-      <c r="P17" s="91"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="85"/>
       <c r="Q17" s="12">
         <v>104400000</v>
       </c>
-      <c r="R17" s="116">
+      <c r="R17" s="110">
         <v>32.81</v>
       </c>
       <c r="S17" s="31">
         <v>34252744.659999996</v>
       </c>
-      <c r="T17" s="93">
+      <c r="T17" s="87">
         <f t="shared" si="6"/>
         <v>0.32809142394636009</v>
       </c>
@@ -9891,36 +9696,36 @@
       <c r="AA17" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="AB17" s="96" t="s">
+      <c r="AB17" s="90" t="s">
         <v>522</v>
       </c>
       <c r="AC17" s="7"/>
       <c r="AD17" s="7"/>
-      <c r="AE17" s="126" t="s">
+      <c r="AE17" s="120" t="s">
         <v>583</v>
       </c>
-      <c r="AF17" s="124"/>
-      <c r="AG17" s="124"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="124"/>
-      <c r="AJ17" s="124"/>
-      <c r="AK17" s="124"/>
-      <c r="AL17" s="124"/>
-      <c r="AM17" s="124"/>
-      <c r="AN17" s="124"/>
-      <c r="AO17" s="124"/>
-      <c r="AP17" s="124"/>
-      <c r="AQ17" s="124"/>
-      <c r="AR17" s="124"/>
-      <c r="AS17" s="124"/>
-      <c r="AT17" s="124"/>
-      <c r="AU17" s="124"/>
-      <c r="AV17" s="125"/>
-      <c r="AW17" s="125"/>
-      <c r="AX17" s="125"/>
-      <c r="AY17" s="125"/>
-      <c r="AZ17" s="125"/>
-      <c r="BA17" s="125"/>
+      <c r="AF17" s="118"/>
+      <c r="AG17" s="118"/>
+      <c r="AH17" s="118"/>
+      <c r="AI17" s="118"/>
+      <c r="AJ17" s="118"/>
+      <c r="AK17" s="118"/>
+      <c r="AL17" s="118"/>
+      <c r="AM17" s="118"/>
+      <c r="AN17" s="118"/>
+      <c r="AO17" s="118"/>
+      <c r="AP17" s="118"/>
+      <c r="AQ17" s="118"/>
+      <c r="AR17" s="118"/>
+      <c r="AS17" s="118"/>
+      <c r="AT17" s="118"/>
+      <c r="AU17" s="118"/>
+      <c r="AV17" s="119"/>
+      <c r="AW17" s="119"/>
+      <c r="AX17" s="119"/>
+      <c r="AY17" s="119"/>
+      <c r="AZ17" s="119"/>
+      <c r="BA17" s="119"/>
     </row>
     <row r="18" spans="1:53" ht="30">
       <c r="A18" s="6">
@@ -9936,10 +9741,10 @@
       <c r="D18" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="E18" s="117" t="s">
+      <c r="E18" s="111" t="s">
         <v>525</v>
       </c>
-      <c r="F18" s="89">
+      <c r="F18" s="83">
         <v>10.86</v>
       </c>
       <c r="G18" s="7" t="s">
@@ -9961,21 +9766,21 @@
         <v>46182</v>
       </c>
       <c r="M18" s="11"/>
-      <c r="N18" s="120" t="s">
+      <c r="N18" s="114" t="s">
         <v>451</v>
       </c>
-      <c r="O18" s="118"/>
-      <c r="P18" s="91"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="85"/>
       <c r="Q18" s="12">
         <v>17572129.800000001</v>
       </c>
-      <c r="R18" s="92">
+      <c r="R18" s="86">
         <v>0.67700000000000005</v>
       </c>
       <c r="S18" s="31">
         <v>10721227.48</v>
       </c>
-      <c r="T18" s="93">
+      <c r="T18" s="87">
         <f t="shared" si="6"/>
         <v>0.61012680887435744</v>
       </c>
@@ -10004,37 +9809,37 @@
       <c r="AD18" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="AE18" s="126" t="s">
+      <c r="AE18" s="120" t="s">
         <v>585</v>
       </c>
-      <c r="AF18" s="126" t="s">
+      <c r="AF18" s="120" t="s">
         <v>584</v>
       </c>
-      <c r="AG18" s="126" t="s">
+      <c r="AG18" s="120" t="s">
         <v>586</v>
       </c>
-      <c r="AH18" s="126" t="s">
+      <c r="AH18" s="120" t="s">
         <v>587</v>
       </c>
-      <c r="AI18" s="124"/>
-      <c r="AJ18" s="124"/>
-      <c r="AK18" s="124"/>
-      <c r="AL18" s="124"/>
-      <c r="AM18" s="124"/>
-      <c r="AN18" s="124"/>
-      <c r="AO18" s="124"/>
-      <c r="AP18" s="124"/>
-      <c r="AQ18" s="124"/>
-      <c r="AR18" s="124"/>
-      <c r="AS18" s="124"/>
-      <c r="AT18" s="124"/>
-      <c r="AU18" s="124"/>
-      <c r="AV18" s="125"/>
-      <c r="AW18" s="125"/>
-      <c r="AX18" s="125"/>
-      <c r="AY18" s="125"/>
-      <c r="AZ18" s="125"/>
-      <c r="BA18" s="125"/>
+      <c r="AI18" s="118"/>
+      <c r="AJ18" s="118"/>
+      <c r="AK18" s="118"/>
+      <c r="AL18" s="118"/>
+      <c r="AM18" s="118"/>
+      <c r="AN18" s="118"/>
+      <c r="AO18" s="118"/>
+      <c r="AP18" s="118"/>
+      <c r="AQ18" s="118"/>
+      <c r="AR18" s="118"/>
+      <c r="AS18" s="118"/>
+      <c r="AT18" s="118"/>
+      <c r="AU18" s="118"/>
+      <c r="AV18" s="119"/>
+      <c r="AW18" s="119"/>
+      <c r="AX18" s="119"/>
+      <c r="AY18" s="119"/>
+      <c r="AZ18" s="119"/>
+      <c r="BA18" s="119"/>
     </row>
     <row r="19" spans="1:53">
       <c r="A19" s="6">
@@ -10050,10 +9855,10 @@
       <c r="D19" s="29" t="s">
         <v>541</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="57" t="s">
         <v>530</v>
       </c>
-      <c r="F19" s="89">
+      <c r="F19" s="83">
         <v>17.66</v>
       </c>
       <c r="G19" s="24" t="s">
@@ -10078,18 +9883,18 @@
       <c r="N19" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="O19" s="121"/>
-      <c r="P19" s="121"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="115"/>
       <c r="Q19" s="12">
         <v>30599099.800000001</v>
       </c>
-      <c r="R19" s="92">
+      <c r="R19" s="86">
         <v>0.39090000000000003</v>
       </c>
       <c r="S19" s="31">
         <v>12420076.130000001</v>
       </c>
-      <c r="T19" s="93">
+      <c r="T19" s="87">
         <f t="shared" si="6"/>
         <v>0.40589678164322995</v>
       </c>
@@ -10116,31 +9921,31 @@
       <c r="AB19" s="24"/>
       <c r="AC19" s="24"/>
       <c r="AD19" s="24"/>
-      <c r="AE19" s="126" t="s">
+      <c r="AE19" s="120" t="s">
         <v>564</v>
       </c>
-      <c r="AF19" s="124"/>
-      <c r="AG19" s="124"/>
-      <c r="AH19" s="124"/>
-      <c r="AI19" s="124"/>
-      <c r="AJ19" s="124"/>
-      <c r="AK19" s="124"/>
-      <c r="AL19" s="124"/>
-      <c r="AM19" s="124"/>
-      <c r="AN19" s="124"/>
-      <c r="AO19" s="124"/>
-      <c r="AP19" s="124"/>
-      <c r="AQ19" s="124"/>
-      <c r="AR19" s="124"/>
-      <c r="AS19" s="124"/>
-      <c r="AT19" s="124"/>
-      <c r="AU19" s="124"/>
-      <c r="AV19" s="125"/>
-      <c r="AW19" s="125"/>
-      <c r="AX19" s="125"/>
-      <c r="AY19" s="125"/>
-      <c r="AZ19" s="125"/>
-      <c r="BA19" s="125"/>
+      <c r="AF19" s="118"/>
+      <c r="AG19" s="118"/>
+      <c r="AH19" s="118"/>
+      <c r="AI19" s="118"/>
+      <c r="AJ19" s="118"/>
+      <c r="AK19" s="118"/>
+      <c r="AL19" s="118"/>
+      <c r="AM19" s="118"/>
+      <c r="AN19" s="118"/>
+      <c r="AO19" s="118"/>
+      <c r="AP19" s="118"/>
+      <c r="AQ19" s="118"/>
+      <c r="AR19" s="118"/>
+      <c r="AS19" s="118"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="119"/>
+      <c r="AW19" s="119"/>
+      <c r="AX19" s="119"/>
+      <c r="AY19" s="119"/>
+      <c r="AZ19" s="119"/>
+      <c r="BA19" s="119"/>
     </row>
     <row r="20" spans="1:53">
       <c r="A20" s="6">
@@ -10156,10 +9961,10 @@
       <c r="D20" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="57" t="s">
         <v>536</v>
       </c>
-      <c r="F20" s="89">
+      <c r="F20" s="83">
         <v>4.12</v>
       </c>
       <c r="G20" s="24" t="s">
@@ -10181,21 +9986,21 @@
         <v>46144</v>
       </c>
       <c r="M20" s="27"/>
-      <c r="N20" s="96" t="s">
+      <c r="N20" s="90" t="s">
         <v>451</v>
       </c>
-      <c r="O20" s="95"/>
-      <c r="P20" s="95"/>
+      <c r="O20" s="89"/>
+      <c r="P20" s="89"/>
       <c r="Q20" s="28">
         <v>4704789.5599999996</v>
       </c>
-      <c r="R20" s="92">
+      <c r="R20" s="86">
         <v>0.86129999999999995</v>
       </c>
       <c r="S20" s="31">
         <v>4052093.97</v>
       </c>
-      <c r="T20" s="93">
+      <c r="T20" s="87">
         <f t="shared" si="6"/>
         <v>0.86126997144586437</v>
       </c>
@@ -10204,7 +10009,7 @@
         <v>652695.58999999939</v>
       </c>
       <c r="V20" s="23"/>
-      <c r="W20" s="122" t="s">
+      <c r="W20" s="116" t="s">
         <v>538</v>
       </c>
       <c r="X20" s="23">
@@ -10213,89 +10018,65 @@
       <c r="Y20" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="Z20" s="123"/>
-      <c r="AA20" s="123" t="s">
+      <c r="Z20" s="117"/>
+      <c r="AA20" s="117" t="s">
         <v>539</v>
       </c>
       <c r="AB20" s="7"/>
       <c r="AC20" s="24"/>
       <c r="AD20" s="24"/>
-      <c r="AE20" s="126" t="s">
+      <c r="AE20" s="120" t="s">
         <v>588</v>
       </c>
-      <c r="AF20" s="124"/>
-      <c r="AG20" s="124"/>
-      <c r="AH20" s="124"/>
-      <c r="AI20" s="124"/>
-      <c r="AJ20" s="124"/>
-      <c r="AK20" s="124"/>
-      <c r="AL20" s="124"/>
-      <c r="AM20" s="124"/>
-      <c r="AN20" s="124"/>
-      <c r="AO20" s="124"/>
-      <c r="AP20" s="124"/>
-      <c r="AQ20" s="124"/>
-      <c r="AR20" s="124"/>
-      <c r="AS20" s="124"/>
-      <c r="AT20" s="124"/>
-      <c r="AU20" s="124"/>
-      <c r="AV20" s="125"/>
-      <c r="AW20" s="125"/>
-      <c r="AX20" s="125"/>
-      <c r="AY20" s="125"/>
-      <c r="AZ20" s="125"/>
-      <c r="BA20" s="125"/>
+      <c r="AF20" s="118"/>
+      <c r="AG20" s="118"/>
+      <c r="AH20" s="118"/>
+      <c r="AI20" s="118"/>
+      <c r="AJ20" s="118"/>
+      <c r="AK20" s="118"/>
+      <c r="AL20" s="118"/>
+      <c r="AM20" s="118"/>
+      <c r="AN20" s="118"/>
+      <c r="AO20" s="118"/>
+      <c r="AP20" s="118"/>
+      <c r="AQ20" s="118"/>
+      <c r="AR20" s="118"/>
+      <c r="AS20" s="118"/>
+      <c r="AT20" s="118"/>
+      <c r="AU20" s="118"/>
+      <c r="AV20" s="119"/>
+      <c r="AW20" s="119"/>
+      <c r="AX20" s="119"/>
+      <c r="AY20" s="119"/>
+      <c r="AZ20" s="119"/>
+      <c r="BA20" s="119"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AD2"/>
-    <mergeCell ref="AE3:BA3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="K4:K5 M4:M5">
-    <cfRule type="expression" dxfId="19" priority="17">
+  <conditionalFormatting sqref="K4:K11 M4:M11">
+    <cfRule type="expression" dxfId="7" priority="13">
       <formula>AND(K4&lt;&gt;"", K4&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="6" priority="14">
       <formula>AND(K4&lt;&gt;"", K4-TODAY()&lt;=60)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K5 M4:M5">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="5" priority="15">
       <formula>AND(K4&lt;&gt;"", K4-TODAY()&gt;60, K4-TODAY()&lt;=180)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20">
+    <cfRule type="expression" dxfId="4" priority="16">
       <formula>AND(K4&lt;&gt;"", K4-TODAY()&gt;180)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K11 M6:M11">
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>AND(K6&lt;&gt;"", K6&lt;TODAY())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>AND(K6&lt;&gt;"", K6-TODAY()&lt;=60)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K11 M6:M11">
-    <cfRule type="expression" dxfId="13" priority="15">
-      <formula>AND(K6&lt;&gt;"", K6-TODAY()&gt;60, K6-TODAY()&lt;=180)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16">
-      <formula>AND(K6&lt;&gt;"", K6-TODAY()&gt;180)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K13:K20 M14:M20">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="3" priority="9">
       <formula>AND(K13&lt;&gt;"", K13&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>AND(K13&lt;&gt;"", K13-TODAY()&lt;=60)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13:K20 M14:M20">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="1" priority="11">
       <formula>AND(K13&lt;&gt;"", K13-TODAY()&gt;60, K13-TODAY()&lt;=180)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>AND(K13&lt;&gt;"", K13-TODAY()&gt;180)</formula>
     </cfRule>
   </conditionalFormatting>
